--- a/output/2024-08-21.xlsx
+++ b/output/2024-08-21.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1</v>
+        <v>2.56</v>
       </c>
       <c r="F14" t="n">
-        <v>7.69</v>
+        <v>6.98</v>
       </c>
       <c r="G14" t="n">
-        <v>90.59999999999999</v>
+        <v>101</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="I14" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>2.25</v>
+        <v>61.22</v>
       </c>
       <c r="K14" t="n">
-        <v>32.58</v>
+        <v>-133.12</v>
       </c>
       <c r="L14" t="n">
-        <v>32.65</v>
+        <v>146.52</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:00:08</t>
+          <t>06:00:53</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.39</v>
+        <v>2.72</v>
       </c>
       <c r="F15" t="n">
-        <v>7.84</v>
+        <v>7.06</v>
       </c>
       <c r="G15" t="n">
-        <v>102</v>
+        <v>102.8</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7</v>
+        <v>8.1</v>
       </c>
       <c r="I15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>2.43</v>
+        <v>176.41</v>
       </c>
       <c r="K15" t="n">
-        <v>-54.38</v>
+        <v>267.48</v>
       </c>
       <c r="L15" t="n">
-        <v>54.44</v>
+        <v>320.41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:01:38</t>
+          <t>06:03:07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="F16" t="n">
-        <v>7.49</v>
+        <v>7.73</v>
       </c>
       <c r="G16" t="n">
-        <v>90.8</v>
+        <v>109.4</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="I16" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>-51.47</v>
+        <v>-82.97</v>
       </c>
       <c r="K16" t="n">
-        <v>-78.27</v>
+        <v>36.97</v>
       </c>
       <c r="L16" t="n">
-        <v>93.68000000000001</v>
+        <v>90.84</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:06:32</t>
+          <t>06:07:52</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.54</v>
+        <v>2.02</v>
       </c>
       <c r="F17" t="n">
-        <v>8.02</v>
+        <v>7.6</v>
       </c>
       <c r="G17" t="n">
-        <v>84.3</v>
+        <v>86.2</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>13.59</v>
+        <v>-17.48</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.98</v>
+        <v>17.81</v>
       </c>
       <c r="L17" t="n">
-        <v>13.73</v>
+        <v>24.96</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:08:07</t>
+          <t>06:08:49</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.29</v>
+        <v>3.48</v>
       </c>
       <c r="F18" t="n">
-        <v>7.91</v>
+        <v>8.25</v>
       </c>
       <c r="G18" t="n">
-        <v>87.90000000000001</v>
+        <v>112</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.52</v>
+        <v>-50.46</v>
       </c>
       <c r="K18" t="n">
-        <v>29.88</v>
+        <v>38.55</v>
       </c>
       <c r="L18" t="n">
-        <v>30.22</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:09:32</t>
+          <t>06:11:15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
       <c r="F19" t="n">
-        <v>7.67</v>
+        <v>7.73</v>
       </c>
       <c r="G19" t="n">
-        <v>108</v>
+        <v>79.7</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4</v>
+        <v>3.4</v>
       </c>
       <c r="I19" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>25.78</v>
+        <v>-165.54</v>
       </c>
       <c r="K19" t="n">
-        <v>-37.26</v>
+        <v>-190.58</v>
       </c>
       <c r="L19" t="n">
-        <v>45.3</v>
+        <v>252.44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:15:14</t>
+          <t>06:17:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="F20" t="n">
-        <v>7.26</v>
+        <v>7.13</v>
       </c>
       <c r="G20" t="n">
-        <v>105</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>5.9</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-59.86</v>
+        <v>-223.22</v>
       </c>
       <c r="K20" t="n">
-        <v>-78.43000000000001</v>
+        <v>29.43</v>
       </c>
       <c r="L20" t="n">
-        <v>98.66</v>
+        <v>225.15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:17:07</t>
+          <t>06:19:35</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.02</v>
+        <v>2.73</v>
       </c>
       <c r="F21" t="n">
-        <v>8.18</v>
+        <v>8.17</v>
       </c>
       <c r="G21" t="n">
-        <v>92.40000000000001</v>
+        <v>106.3</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="I21" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J21" t="n">
-        <v>-124.49</v>
+        <v>-29.08</v>
       </c>
       <c r="K21" t="n">
-        <v>-71.31</v>
+        <v>-70.81</v>
       </c>
       <c r="L21" t="n">
-        <v>143.47</v>
+        <v>76.55</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:17:52</t>
+          <t>06:21:32</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="F22" t="n">
-        <v>7.72</v>
+        <v>7.89</v>
       </c>
       <c r="G22" t="n">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="I22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>-80.62</v>
+        <v>-66.78</v>
       </c>
       <c r="K22" t="n">
-        <v>-104.45</v>
+        <v>381.21</v>
       </c>
       <c r="L22" t="n">
-        <v>131.95</v>
+        <v>387.01</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:21:07</t>
+          <t>06:26:17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.01</v>
+        <v>2.59</v>
       </c>
       <c r="F23" t="n">
-        <v>7.54</v>
+        <v>7.35</v>
       </c>
       <c r="G23" t="n">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="I23" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>5.3</v>
+        <v>149.39</v>
       </c>
       <c r="K23" t="n">
-        <v>-83.59999999999999</v>
+        <v>215.63</v>
       </c>
       <c r="L23" t="n">
-        <v>83.77</v>
+        <v>262.32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:23:10</t>
+          <t>06:28:40</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.54</v>
+        <v>2.71</v>
       </c>
       <c r="F24" t="n">
-        <v>8.220000000000001</v>
+        <v>7.43</v>
       </c>
       <c r="G24" t="n">
-        <v>109.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>110.88</v>
+        <v>-145.44</v>
       </c>
       <c r="K24" t="n">
-        <v>-132.06</v>
+        <v>217.14</v>
       </c>
       <c r="L24" t="n">
-        <v>172.44</v>
+        <v>261.35</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:24:12</t>
+          <t>06:29:34</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.29</v>
+        <v>2.6</v>
       </c>
       <c r="F25" t="n">
-        <v>8.050000000000001</v>
+        <v>7.91</v>
       </c>
       <c r="G25" t="n">
-        <v>98</v>
+        <v>89.2</v>
       </c>
       <c r="H25" t="n">
-        <v>2.3</v>
+        <v>6.7</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-106.35</v>
+        <v>68.8</v>
       </c>
       <c r="K25" t="n">
-        <v>-34.35</v>
+        <v>103.12</v>
       </c>
       <c r="L25" t="n">
-        <v>111.76</v>
+        <v>123.96</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:27:49</t>
+          <t>06:36:02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="F26" t="n">
-        <v>7.86</v>
+        <v>7.82</v>
       </c>
       <c r="G26" t="n">
-        <v>91.09999999999999</v>
+        <v>110.6</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>278.62</v>
+        <v>275.16</v>
       </c>
       <c r="K26" t="n">
-        <v>211.66</v>
+        <v>124.03</v>
       </c>
       <c r="L26" t="n">
-        <v>349.9</v>
+        <v>301.82</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:29:37</t>
+          <t>06:38:20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="F27" t="n">
-        <v>7.94</v>
+        <v>7.57</v>
       </c>
       <c r="G27" t="n">
-        <v>87.5</v>
+        <v>109.8</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-71.7</v>
+        <v>-520.42</v>
       </c>
       <c r="K27" t="n">
-        <v>-289.61</v>
+        <v>-385.37</v>
       </c>
       <c r="L27" t="n">
-        <v>298.35</v>
+        <v>647.5700000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:30:37</t>
+          <t>06:40:28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.65</v>
+        <v>2.91</v>
       </c>
       <c r="F28" t="n">
-        <v>7.78</v>
+        <v>7.72</v>
       </c>
       <c r="G28" t="n">
-        <v>98.3</v>
+        <v>96.5</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="I28" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>29.35</v>
+        <v>-348.58</v>
       </c>
       <c r="K28" t="n">
-        <v>-430.31</v>
+        <v>459.56</v>
       </c>
       <c r="L28" t="n">
-        <v>431.31</v>
+        <v>576.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:40:46</t>
+          <t>06:49:39</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.01</v>
+        <v>3.16</v>
       </c>
       <c r="F29" t="n">
-        <v>7.5</v>
+        <v>7.73</v>
       </c>
       <c r="G29" t="n">
-        <v>88.3</v>
+        <v>99.3</v>
       </c>
       <c r="H29" t="n">
-        <v>6.3</v>
+        <v>0.3</v>
       </c>
       <c r="I29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-121.24</v>
+        <v>-6.83</v>
       </c>
       <c r="K29" t="n">
-        <v>-54.52</v>
+        <v>-30.84</v>
       </c>
       <c r="L29" t="n">
-        <v>132.93</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:43:22</t>
+          <t>06:51:38</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.77</v>
+        <v>3.38</v>
       </c>
       <c r="F30" t="n">
-        <v>7.96</v>
+        <v>8</v>
       </c>
       <c r="G30" t="n">
-        <v>95.7</v>
+        <v>108.2</v>
       </c>
       <c r="H30" t="n">
-        <v>1.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-23.86</v>
+        <v>8.75</v>
       </c>
       <c r="K30" t="n">
-        <v>-107.08</v>
+        <v>-83.48999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>109.71</v>
+        <v>83.95</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:45:02</t>
+          <t>06:53:41</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.66</v>
+        <v>2.79</v>
       </c>
       <c r="F31" t="n">
-        <v>7.79</v>
+        <v>7.65</v>
       </c>
       <c r="G31" t="n">
-        <v>97.59999999999999</v>
+        <v>106</v>
       </c>
       <c r="H31" t="n">
-        <v>1.5</v>
+        <v>5.6</v>
       </c>
       <c r="I31" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>13.92</v>
+        <v>40.21</v>
       </c>
       <c r="K31" t="n">
-        <v>-19.34</v>
+        <v>189.46</v>
       </c>
       <c r="L31" t="n">
-        <v>23.83</v>
+        <v>193.68</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:49:33</t>
+          <t>06:58:39</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.56</v>
+        <v>2.82</v>
       </c>
       <c r="F32" t="n">
-        <v>8.09</v>
+        <v>8.06</v>
       </c>
       <c r="G32" t="n">
-        <v>102.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="I32" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>42.69</v>
+        <v>61.64</v>
       </c>
       <c r="K32" t="n">
-        <v>167.46</v>
+        <v>71.17</v>
       </c>
       <c r="L32" t="n">
-        <v>172.82</v>
+        <v>94.15000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:50:22</t>
+          <t>07:00:18</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="F33" t="n">
-        <v>7.86</v>
+        <v>7.79</v>
       </c>
       <c r="G33" t="n">
-        <v>79.5</v>
+        <v>96.3</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>41.17</v>
+        <v>39.09</v>
       </c>
       <c r="K33" t="n">
-        <v>47.83</v>
+        <v>127.92</v>
       </c>
       <c r="L33" t="n">
-        <v>63.11</v>
+        <v>133.76</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:51:39</t>
+          <t>07:01:25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="F34" t="n">
-        <v>7.75</v>
+        <v>7.33</v>
       </c>
       <c r="G34" t="n">
-        <v>101.3</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>1.7</v>
+        <v>6.9</v>
       </c>
       <c r="I34" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>32.1</v>
+        <v>22.14</v>
       </c>
       <c r="K34" t="n">
-        <v>116.23</v>
+        <v>-44.12</v>
       </c>
       <c r="L34" t="n">
-        <v>120.58</v>
+        <v>49.36</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:55:51</t>
+          <t>07:05:17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.76</v>
+        <v>3.19</v>
       </c>
       <c r="F35" t="n">
-        <v>8.09</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>106.9</v>
+        <v>96.8</v>
       </c>
       <c r="H35" t="n">
-        <v>7.4</v>
+        <v>11.1</v>
       </c>
       <c r="I35" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>2.77</v>
+        <v>146.23</v>
       </c>
       <c r="K35" t="n">
-        <v>284.21</v>
+        <v>20.35</v>
       </c>
       <c r="L35" t="n">
-        <v>284.22</v>
+        <v>147.64</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:57:27</t>
+          <t>07:07:23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.52</v>
+        <v>3.04</v>
       </c>
       <c r="F36" t="n">
-        <v>8.140000000000001</v>
+        <v>8.18</v>
       </c>
       <c r="G36" t="n">
-        <v>90.5</v>
+        <v>84.7</v>
       </c>
       <c r="H36" t="n">
-        <v>0.2</v>
+        <v>7.9</v>
       </c>
       <c r="I36" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>81.98</v>
+        <v>-174.78</v>
       </c>
       <c r="K36" t="n">
-        <v>-163.42</v>
+        <v>362.78</v>
       </c>
       <c r="L36" t="n">
-        <v>182.83</v>
+        <v>402.69</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:58:40</t>
+          <t>07:08:39</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.6</v>
+        <v>3.29</v>
       </c>
       <c r="F37" t="n">
-        <v>7.71</v>
+        <v>8.41</v>
       </c>
       <c r="G37" t="n">
-        <v>92</v>
+        <v>100.1</v>
       </c>
       <c r="H37" t="n">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="I37" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>195.6</v>
+        <v>67.44</v>
       </c>
       <c r="K37" t="n">
-        <v>169.14</v>
+        <v>442.43</v>
       </c>
       <c r="L37" t="n">
-        <v>258.59</v>
+        <v>447.54</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:03:23</t>
+          <t>07:13:26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.7</v>
+        <v>3.07</v>
       </c>
       <c r="F38" t="n">
-        <v>7.72</v>
+        <v>7.48</v>
       </c>
       <c r="G38" t="n">
-        <v>101</v>
+        <v>106.5</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>-15.66</v>
+        <v>-42.66</v>
       </c>
       <c r="K38" t="n">
-        <v>127.51</v>
+        <v>105.43</v>
       </c>
       <c r="L38" t="n">
-        <v>128.47</v>
+        <v>113.74</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:05:19</t>
+          <t>07:15:10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="F39" t="n">
-        <v>7.64</v>
+        <v>7.92</v>
       </c>
       <c r="G39" t="n">
-        <v>87.7</v>
+        <v>112.8</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I39" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-258.57</v>
+        <v>174.46</v>
       </c>
       <c r="K39" t="n">
-        <v>-425.5</v>
+        <v>306.31</v>
       </c>
       <c r="L39" t="n">
-        <v>497.9</v>
+        <v>352.51</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:06:07</t>
+          <t>07:16:33</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.61</v>
+        <v>2.99</v>
       </c>
       <c r="F40" t="n">
-        <v>7.46</v>
+        <v>7.69</v>
       </c>
       <c r="G40" t="n">
-        <v>88.90000000000001</v>
+        <v>116.5</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="I40" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>-76.48999999999999</v>
+        <v>30.38</v>
       </c>
       <c r="K40" t="n">
-        <v>537.77</v>
+        <v>148.33</v>
       </c>
       <c r="L40" t="n">
-        <v>543.1900000000001</v>
+        <v>151.41</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:10:05</t>
+          <t>07:21:29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>3.14</v>
+        <v>2.87</v>
       </c>
       <c r="F41" t="n">
-        <v>8.02</v>
+        <v>8.17</v>
       </c>
       <c r="G41" t="n">
-        <v>91.40000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="H41" t="n">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="I41" t="n">
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>-201.56</v>
+        <v>-18</v>
       </c>
       <c r="K41" t="n">
-        <v>181.47</v>
+        <v>324.3</v>
       </c>
       <c r="L41" t="n">
-        <v>271.22</v>
+        <v>324.8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:10:58</t>
+          <t>07:23:12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="F42" t="n">
-        <v>7.91</v>
+        <v>7.14</v>
       </c>
       <c r="G42" t="n">
-        <v>97</v>
+        <v>98.2</v>
       </c>
       <c r="H42" t="n">
-        <v>2.2</v>
+        <v>5.8</v>
       </c>
       <c r="I42" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>-4.73</v>
+        <v>-581.9299999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>-29.23</v>
+        <v>223.46</v>
       </c>
       <c r="L42" t="n">
-        <v>29.61</v>
+        <v>623.36</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:13:33</t>
+          <t>07:25:01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="F43" t="n">
-        <v>7.78</v>
+        <v>7.76</v>
       </c>
       <c r="G43" t="n">
-        <v>103.1</v>
+        <v>84</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="I43" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-147.4</v>
+        <v>-73.95</v>
       </c>
       <c r="K43" t="n">
-        <v>150.38</v>
+        <v>584.4</v>
       </c>
       <c r="L43" t="n">
-        <v>210.57</v>
+        <v>589.0599999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:21:26</t>
+          <t>07:36:45</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="F44" t="n">
-        <v>8.18</v>
+        <v>7.87</v>
       </c>
       <c r="G44" t="n">
-        <v>114.7</v>
+        <v>88.7</v>
       </c>
       <c r="H44" t="n">
-        <v>8.5</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>-6.5</v>
+        <v>46.28</v>
       </c>
       <c r="K44" t="n">
-        <v>78.27</v>
+        <v>-169.29</v>
       </c>
       <c r="L44" t="n">
-        <v>78.54000000000001</v>
+        <v>175.51</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:23:05</t>
+          <t>07:38:10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.63</v>
+        <v>2.94</v>
       </c>
       <c r="F45" t="n">
-        <v>7.71</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G45" t="n">
-        <v>89.7</v>
+        <v>86.8</v>
       </c>
       <c r="H45" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-80.56999999999999</v>
+        <v>28.05</v>
       </c>
       <c r="K45" t="n">
-        <v>10.41</v>
+        <v>242.09</v>
       </c>
       <c r="L45" t="n">
-        <v>81.23999999999999</v>
+        <v>243.71</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:24:21</t>
+          <t>07:39:40</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.99</v>
+        <v>3.07</v>
       </c>
       <c r="F46" t="n">
-        <v>7.46</v>
+        <v>8.31</v>
       </c>
       <c r="G46" t="n">
-        <v>91.59999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="H46" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="I46" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J46" t="n">
-        <v>30.41</v>
+        <v>43.16</v>
       </c>
       <c r="K46" t="n">
-        <v>108.37</v>
+        <v>-154.82</v>
       </c>
       <c r="L46" t="n">
-        <v>112.56</v>
+        <v>160.72</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:28:35</t>
+          <t>07:42:35</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.77</v>
+        <v>2.94</v>
       </c>
       <c r="F47" t="n">
-        <v>7.43</v>
+        <v>7.8</v>
       </c>
       <c r="G47" t="n">
-        <v>100.6</v>
+        <v>100.1</v>
       </c>
       <c r="H47" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="I47" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>57.58</v>
+        <v>-35.8</v>
       </c>
       <c r="K47" t="n">
-        <v>22.76</v>
+        <v>-71.48</v>
       </c>
       <c r="L47" t="n">
-        <v>61.91</v>
+        <v>79.95</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:30:18</t>
+          <t>07:45:20</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="F48" t="n">
-        <v>8.130000000000001</v>
+        <v>7.83</v>
       </c>
       <c r="G48" t="n">
-        <v>95.5</v>
+        <v>93</v>
       </c>
       <c r="H48" t="n">
-        <v>3.8</v>
+        <v>0.1</v>
       </c>
       <c r="I48" t="n">
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>-168.62</v>
+        <v>41.57</v>
       </c>
       <c r="K48" t="n">
-        <v>54.84</v>
+        <v>187.38</v>
       </c>
       <c r="L48" t="n">
-        <v>177.31</v>
+        <v>191.94</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:31:08</t>
+          <t>07:47:09</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="F49" t="n">
-        <v>7.89</v>
+        <v>8.06</v>
       </c>
       <c r="G49" t="n">
-        <v>93.5</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>0.8</v>
+        <v>8</v>
       </c>
       <c r="I49" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>66.47</v>
+        <v>188.16</v>
       </c>
       <c r="K49" t="n">
-        <v>22.21</v>
+        <v>-100.57</v>
       </c>
       <c r="L49" t="n">
-        <v>70.08</v>
+        <v>213.35</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:36:02</t>
+          <t>07:52:04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.8</v>
+        <v>3.11</v>
       </c>
       <c r="F50" t="n">
-        <v>7.62</v>
+        <v>7.49</v>
       </c>
       <c r="G50" t="n">
-        <v>105.8</v>
+        <v>85.5</v>
       </c>
       <c r="H50" t="n">
-        <v>0.8</v>
+        <v>9.1</v>
       </c>
       <c r="I50" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>156.8</v>
+        <v>39.91</v>
       </c>
       <c r="K50" t="n">
-        <v>175.32</v>
+        <v>410.03</v>
       </c>
       <c r="L50" t="n">
-        <v>235.21</v>
+        <v>411.97</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:37:25</t>
+          <t>07:53:43</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.28</v>
+        <v>2.94</v>
       </c>
       <c r="F51" t="n">
-        <v>7.56</v>
+        <v>7.96</v>
       </c>
       <c r="G51" t="n">
-        <v>87.59999999999999</v>
+        <v>99.5</v>
       </c>
       <c r="H51" t="n">
-        <v>8.199999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="I51" t="n">
         <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-275.51</v>
+        <v>-4.75</v>
       </c>
       <c r="K51" t="n">
-        <v>-187.54</v>
+        <v>153.05</v>
       </c>
       <c r="L51" t="n">
-        <v>333.28</v>
+        <v>153.12</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:38:48</t>
+          <t>07:55:52</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.48</v>
+        <v>3.19</v>
       </c>
       <c r="F52" t="n">
-        <v>7.78</v>
+        <v>8.1</v>
       </c>
       <c r="G52" t="n">
-        <v>83.09999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I52" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-24.34</v>
+        <v>-134.1</v>
       </c>
       <c r="K52" t="n">
-        <v>-57.92</v>
+        <v>-33.06</v>
       </c>
       <c r="L52" t="n">
-        <v>62.83</v>
+        <v>138.11</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:45:05</t>
+          <t>08:00:29</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="F53" t="n">
-        <v>7.71</v>
+        <v>7.55</v>
       </c>
       <c r="G53" t="n">
-        <v>86</v>
+        <v>100.1</v>
       </c>
       <c r="H53" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>589.54</v>
+        <v>483.19</v>
       </c>
       <c r="K53" t="n">
-        <v>-448.29</v>
+        <v>-228.9</v>
       </c>
       <c r="L53" t="n">
-        <v>740.62</v>
+        <v>534.67</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:47:19</t>
+          <t>08:02:08</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.81</v>
+        <v>2.66</v>
       </c>
       <c r="F54" t="n">
-        <v>8.050000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="G54" t="n">
-        <v>102.9</v>
+        <v>101.9</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="I54" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-355.47</v>
+        <v>-117.35</v>
       </c>
       <c r="K54" t="n">
-        <v>-147.82</v>
+        <v>386.48</v>
       </c>
       <c r="L54" t="n">
-        <v>384.98</v>
+        <v>403.91</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:49:05</t>
+          <t>08:04:37</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.49</v>
+        <v>3.22</v>
       </c>
       <c r="F55" t="n">
-        <v>8.15</v>
+        <v>7.88</v>
       </c>
       <c r="G55" t="n">
-        <v>85.8</v>
+        <v>103</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="I55" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>-493.54</v>
+        <v>55.14</v>
       </c>
       <c r="K55" t="n">
-        <v>160.25</v>
+        <v>401.84</v>
       </c>
       <c r="L55" t="n">
-        <v>518.9</v>
+        <v>405.6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:54:46</t>
+          <t>08:10:07</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.89</v>
+        <v>2.72</v>
       </c>
       <c r="F56" t="n">
-        <v>7.72</v>
+        <v>7.79</v>
       </c>
       <c r="G56" t="n">
-        <v>101.2</v>
+        <v>93.3</v>
       </c>
       <c r="H56" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>18.4</v>
+        <v>215.26</v>
       </c>
       <c r="K56" t="n">
-        <v>214.94</v>
+        <v>19.22</v>
       </c>
       <c r="L56" t="n">
-        <v>215.73</v>
+        <v>216.11</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:57:06</t>
+          <t>08:11:38</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.22</v>
+        <v>3.71</v>
       </c>
       <c r="F57" t="n">
-        <v>7.52</v>
+        <v>7.94</v>
       </c>
       <c r="G57" t="n">
-        <v>100.3</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>-612.3099999999999</v>
+        <v>283.12</v>
       </c>
       <c r="K57" t="n">
-        <v>589.6</v>
+        <v>55.82</v>
       </c>
       <c r="L57" t="n">
-        <v>850.03</v>
+        <v>288.57</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:59:36</t>
+          <t>08:13:31</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.26</v>
+        <v>2.93</v>
       </c>
       <c r="F58" t="n">
-        <v>7.54</v>
+        <v>8.08</v>
       </c>
       <c r="G58" t="n">
-        <v>99.7</v>
+        <v>99</v>
       </c>
       <c r="H58" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="I58" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>718.4</v>
+        <v>726.24</v>
       </c>
       <c r="K58" t="n">
-        <v>-7.84</v>
+        <v>-347.94</v>
       </c>
       <c r="L58" t="n">
-        <v>718.4400000000001</v>
+        <v>805.28</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:10:44</t>
+          <t>08:22:52</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="F59" t="n">
-        <v>7.72</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="G59" t="n">
-        <v>97.3</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>26.19</v>
+        <v>123.61</v>
       </c>
       <c r="K59" t="n">
-        <v>44.56</v>
+        <v>79.66</v>
       </c>
       <c r="L59" t="n">
-        <v>51.69</v>
+        <v>147.05</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:11:24</t>
+          <t>08:23:46</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="F60" t="n">
-        <v>7.05</v>
+        <v>7.36</v>
       </c>
       <c r="G60" t="n">
-        <v>89</v>
+        <v>87.8</v>
       </c>
       <c r="H60" t="n">
-        <v>7.6</v>
+        <v>1.1</v>
       </c>
       <c r="I60" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>52.37</v>
+        <v>77.42</v>
       </c>
       <c r="K60" t="n">
-        <v>-12.14</v>
+        <v>30.07</v>
       </c>
       <c r="L60" t="n">
-        <v>53.76</v>
+        <v>83.05</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:14:18</t>
+          <t>08:24:53</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.69</v>
+        <v>2.94</v>
       </c>
       <c r="F61" t="n">
-        <v>7.91</v>
+        <v>8.01</v>
       </c>
       <c r="G61" t="n">
-        <v>81.5</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H61" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>85.18000000000001</v>
+        <v>181.82</v>
       </c>
       <c r="K61" t="n">
-        <v>-26.28</v>
+        <v>-102.27</v>
       </c>
       <c r="L61" t="n">
-        <v>89.14</v>
+        <v>208.61</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:18:31</t>
+          <t>08:29:39</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="F62" t="n">
-        <v>7.38</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="G62" t="n">
-        <v>82</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H62" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="I62" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>-26.74</v>
+        <v>-262.92</v>
       </c>
       <c r="K62" t="n">
-        <v>50.66</v>
+        <v>-14.05</v>
       </c>
       <c r="L62" t="n">
-        <v>57.29</v>
+        <v>263.3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:20:46</t>
+          <t>08:31:53</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.51</v>
+        <v>2.85</v>
       </c>
       <c r="F63" t="n">
-        <v>7.78</v>
+        <v>7.91</v>
       </c>
       <c r="G63" t="n">
-        <v>92.3</v>
+        <v>110.7</v>
       </c>
       <c r="H63" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="I63" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>31.18</v>
+        <v>53.44</v>
       </c>
       <c r="K63" t="n">
-        <v>53.87</v>
+        <v>-34.75</v>
       </c>
       <c r="L63" t="n">
-        <v>62.24</v>
+        <v>63.75</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:22:29</t>
+          <t>08:33:12</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.46</v>
+        <v>3.42</v>
       </c>
       <c r="F64" t="n">
-        <v>7.16</v>
+        <v>7</v>
       </c>
       <c r="G64" t="n">
-        <v>91.2</v>
+        <v>83.5</v>
       </c>
       <c r="H64" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-106.5</v>
+        <v>-19.58</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-88.06</v>
       </c>
       <c r="L64" t="n">
-        <v>106.5</v>
+        <v>90.20999999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:27:47</t>
+          <t>08:38:05</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.14</v>
+        <v>2.9</v>
       </c>
       <c r="F65" t="n">
-        <v>8.41</v>
+        <v>7.54</v>
       </c>
       <c r="G65" t="n">
-        <v>105.2</v>
+        <v>103.1</v>
       </c>
       <c r="H65" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="I65" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-172.48</v>
+        <v>-99.22</v>
       </c>
       <c r="K65" t="n">
-        <v>288.82</v>
+        <v>-133.12</v>
       </c>
       <c r="L65" t="n">
-        <v>336.4</v>
+        <v>166.03</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:29:25</t>
+          <t>08:40:10</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.38</v>
+        <v>2.56</v>
       </c>
       <c r="F66" t="n">
-        <v>7.38</v>
+        <v>8.01</v>
       </c>
       <c r="G66" t="n">
-        <v>79.7</v>
+        <v>103</v>
       </c>
       <c r="H66" t="n">
-        <v>4.4</v>
+        <v>6.1</v>
       </c>
       <c r="I66" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-47.44</v>
+        <v>256.77</v>
       </c>
       <c r="K66" t="n">
-        <v>93.65000000000001</v>
+        <v>-182.65</v>
       </c>
       <c r="L66" t="n">
-        <v>104.98</v>
+        <v>315.1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:31:43</t>
+          <t>08:42:18</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.01</v>
+        <v>2.83</v>
       </c>
       <c r="F67" t="n">
-        <v>8.08</v>
+        <v>7.62</v>
       </c>
       <c r="G67" t="n">
-        <v>94.59999999999999</v>
+        <v>101</v>
       </c>
       <c r="H67" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>251.15</v>
+        <v>-147.97</v>
       </c>
       <c r="K67" t="n">
-        <v>-336.29</v>
+        <v>57.23</v>
       </c>
       <c r="L67" t="n">
-        <v>419.72</v>
+        <v>158.66</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:36:16</t>
+          <t>08:46:32</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="F68" t="n">
-        <v>8.16</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G68" t="n">
-        <v>105.9</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I68" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-188.27</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="K68" t="n">
-        <v>-222.01</v>
+        <v>-408.03</v>
       </c>
       <c r="L68" t="n">
-        <v>291.09</v>
+        <v>413.61</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:37:32</t>
+          <t>08:47:43</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.67</v>
+        <v>2.89</v>
       </c>
       <c r="F69" t="n">
-        <v>7.38</v>
+        <v>7.17</v>
       </c>
       <c r="G69" t="n">
-        <v>98.8</v>
+        <v>109.4</v>
       </c>
       <c r="H69" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-349.02</v>
+        <v>95.48</v>
       </c>
       <c r="K69" t="n">
-        <v>126.09</v>
+        <v>134.39</v>
       </c>
       <c r="L69" t="n">
-        <v>371.09</v>
+        <v>164.86</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:38:50</t>
+          <t>08:49:11</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.18</v>
+        <v>2.45</v>
       </c>
       <c r="F70" t="n">
-        <v>7.25</v>
+        <v>8.56</v>
       </c>
       <c r="G70" t="n">
-        <v>98</v>
+        <v>107.4</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I70" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-472.52</v>
+        <v>-19.73</v>
       </c>
       <c r="K70" t="n">
-        <v>-304.04</v>
+        <v>-202.18</v>
       </c>
       <c r="L70" t="n">
-        <v>561.89</v>
+        <v>203.14</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:44:25</t>
+          <t>08:54:59</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.99</v>
+        <v>3.26</v>
       </c>
       <c r="F71" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="G71" t="n">
-        <v>98.59999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="H71" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="I71" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>413.81</v>
+        <v>-79.08</v>
       </c>
       <c r="K71" t="n">
-        <v>444.09</v>
+        <v>-598.0599999999999</v>
       </c>
       <c r="L71" t="n">
-        <v>607</v>
+        <v>603.26</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:45:19</t>
+          <t>08:56:27</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.29</v>
+        <v>3.02</v>
       </c>
       <c r="F72" t="n">
-        <v>7.68</v>
+        <v>8</v>
       </c>
       <c r="G72" t="n">
-        <v>89</v>
+        <v>98.5</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>120.77</v>
+        <v>-393.49</v>
       </c>
       <c r="K72" t="n">
-        <v>129.57</v>
+        <v>235.21</v>
       </c>
       <c r="L72" t="n">
-        <v>177.12</v>
+        <v>458.44</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:47:03</t>
+          <t>08:58:05</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.08</v>
+        <v>4.4</v>
       </c>
       <c r="F73" t="n">
-        <v>7.05</v>
+        <v>7.58</v>
       </c>
       <c r="G73" t="n">
-        <v>91.7</v>
+        <v>97.3</v>
       </c>
       <c r="H73" t="n">
-        <v>6.8</v>
+        <v>2.1</v>
       </c>
       <c r="I73" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>394.78</v>
+        <v>-75.22</v>
       </c>
       <c r="K73" t="n">
-        <v>-304.92</v>
+        <v>-777.45</v>
       </c>
       <c r="L73" t="n">
-        <v>498.83</v>
+        <v>781.08</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:00:16</t>
+          <t>09:08:50</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="F74" t="n">
-        <v>7.85</v>
+        <v>8.4</v>
       </c>
       <c r="G74" t="n">
-        <v>79.8</v>
+        <v>99.3</v>
       </c>
       <c r="H74" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="I74" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>80</v>
+        <v>-48.11</v>
       </c>
       <c r="K74" t="n">
-        <v>-195.42</v>
+        <v>184.8</v>
       </c>
       <c r="L74" t="n">
-        <v>211.16</v>
+        <v>190.96</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:01:47</t>
+          <t>09:11:05</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.52</v>
+        <v>2.65</v>
       </c>
       <c r="F75" t="n">
-        <v>8.51</v>
+        <v>8.07</v>
       </c>
       <c r="G75" t="n">
-        <v>82.59999999999999</v>
+        <v>101.9</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="I75" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>68.83</v>
+        <v>136.3</v>
       </c>
       <c r="K75" t="n">
-        <v>100.12</v>
+        <v>-117.88</v>
       </c>
       <c r="L75" t="n">
-        <v>121.5</v>
+        <v>180.2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:03:40</t>
+          <t>09:12:10</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.18</v>
+        <v>2.86</v>
       </c>
       <c r="F76" t="n">
-        <v>7.07</v>
+        <v>7.97</v>
       </c>
       <c r="G76" t="n">
-        <v>102.4</v>
+        <v>98.3</v>
       </c>
       <c r="H76" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>-51.7</v>
+        <v>54.77</v>
       </c>
       <c r="K76" t="n">
-        <v>51.76</v>
+        <v>-74.88</v>
       </c>
       <c r="L76" t="n">
-        <v>73.16</v>
+        <v>92.77</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:07:33</t>
+          <t>09:17:37</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.26</v>
+        <v>3.32</v>
       </c>
       <c r="F77" t="n">
-        <v>8.67</v>
+        <v>7.09</v>
       </c>
       <c r="G77" t="n">
-        <v>102.3</v>
+        <v>99.8</v>
       </c>
       <c r="H77" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="I77" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-63.91</v>
+        <v>-187.73</v>
       </c>
       <c r="K77" t="n">
-        <v>-39.84</v>
+        <v>223.41</v>
       </c>
       <c r="L77" t="n">
-        <v>75.31</v>
+        <v>291.81</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:09:49</t>
+          <t>09:18:37</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="F78" t="n">
-        <v>8.06</v>
+        <v>7.78</v>
       </c>
       <c r="G78" t="n">
-        <v>100.2</v>
+        <v>94.7</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>7.87</v>
+        <v>91.27</v>
       </c>
       <c r="K78" t="n">
-        <v>-29.14</v>
+        <v>56.28</v>
       </c>
       <c r="L78" t="n">
-        <v>30.18</v>
+        <v>107.23</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:12:07</t>
+          <t>09:20:14</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.26</v>
+        <v>3.48</v>
       </c>
       <c r="F79" t="n">
-        <v>7.37</v>
+        <v>7.74</v>
       </c>
       <c r="G79" t="n">
-        <v>95.09999999999999</v>
+        <v>103.7</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="I79" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-68.84999999999999</v>
+        <v>-135.09</v>
       </c>
       <c r="K79" t="n">
-        <v>58.19</v>
+        <v>-133.31</v>
       </c>
       <c r="L79" t="n">
-        <v>90.15000000000001</v>
+        <v>189.79</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:18:05</t>
+          <t>09:24:48</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.12</v>
+        <v>2.94</v>
       </c>
       <c r="F80" t="n">
-        <v>7.89</v>
+        <v>8</v>
       </c>
       <c r="G80" t="n">
-        <v>104.6</v>
+        <v>100.1</v>
       </c>
       <c r="H80" t="n">
-        <v>8.800000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="I80" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>-95.88</v>
+        <v>-219.57</v>
       </c>
       <c r="K80" t="n">
-        <v>-105.97</v>
+        <v>-52.03</v>
       </c>
       <c r="L80" t="n">
-        <v>142.91</v>
+        <v>225.65</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:20:02</t>
+          <t>09:26:12</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.16</v>
+        <v>2.98</v>
       </c>
       <c r="F81" t="n">
-        <v>8.06</v>
+        <v>7.92</v>
       </c>
       <c r="G81" t="n">
-        <v>98.3</v>
+        <v>112.8</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-174.03</v>
+        <v>192.4</v>
       </c>
       <c r="K81" t="n">
-        <v>-23.93</v>
+        <v>120.98</v>
       </c>
       <c r="L81" t="n">
-        <v>175.67</v>
+        <v>227.27</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:21:42</t>
+          <t>09:27:30</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.29</v>
+        <v>3.59</v>
       </c>
       <c r="F82" t="n">
-        <v>8.4</v>
+        <v>7.12</v>
       </c>
       <c r="G82" t="n">
-        <v>94.7</v>
+        <v>89.8</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="I82" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J82" t="n">
-        <v>-126.61</v>
+        <v>410.17</v>
       </c>
       <c r="K82" t="n">
-        <v>-7.94</v>
+        <v>-36.22</v>
       </c>
       <c r="L82" t="n">
-        <v>126.86</v>
+        <v>411.76</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:27:25</t>
+          <t>09:31:41</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.24</v>
+        <v>3.68</v>
       </c>
       <c r="F83" t="n">
-        <v>8.619999999999999</v>
+        <v>8.74</v>
       </c>
       <c r="G83" t="n">
-        <v>92.5</v>
+        <v>111.8</v>
       </c>
       <c r="H83" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J83" t="n">
-        <v>-115.24</v>
+        <v>124.79</v>
       </c>
       <c r="K83" t="n">
-        <v>238.64</v>
+        <v>86.03</v>
       </c>
       <c r="L83" t="n">
-        <v>265.01</v>
+        <v>151.57</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:28:25</t>
+          <t>09:32:38</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.03</v>
+        <v>3.18</v>
       </c>
       <c r="F84" t="n">
-        <v>7.5</v>
+        <v>7.25</v>
       </c>
       <c r="G84" t="n">
-        <v>105.5</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H84" t="n">
-        <v>1.7</v>
+        <v>4.7</v>
       </c>
       <c r="I84" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J84" t="n">
-        <v>-45.79</v>
+        <v>-173.04</v>
       </c>
       <c r="K84" t="n">
-        <v>84.45999999999999</v>
+        <v>-178.96</v>
       </c>
       <c r="L84" t="n">
-        <v>96.06999999999999</v>
+        <v>248.94</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:30:57</t>
+          <t>09:34:07</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.33</v>
+        <v>3.15</v>
       </c>
       <c r="F85" t="n">
-        <v>7.96</v>
+        <v>7.88</v>
       </c>
       <c r="G85" t="n">
-        <v>92.8</v>
+        <v>105.9</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I85" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>-292.77</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="K85" t="n">
-        <v>122.16</v>
+        <v>-378.07</v>
       </c>
       <c r="L85" t="n">
-        <v>317.23</v>
+        <v>385.86</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:36:25</t>
+          <t>09:39:08</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.39</v>
+        <v>3.28</v>
       </c>
       <c r="F86" t="n">
-        <v>7.24</v>
+        <v>7.19</v>
       </c>
       <c r="G86" t="n">
-        <v>99.40000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="I86" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>-261.89</v>
+        <v>635.87</v>
       </c>
       <c r="K86" t="n">
-        <v>-846.22</v>
+        <v>95.77</v>
       </c>
       <c r="L86" t="n">
-        <v>885.8200000000001</v>
+        <v>643.05</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:38:22</t>
+          <t>09:40:17</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="F87" t="n">
-        <v>8.140000000000001</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="G87" t="n">
-        <v>87.90000000000001</v>
+        <v>104.1</v>
       </c>
       <c r="H87" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J87" t="n">
-        <v>43.28</v>
+        <v>312.14</v>
       </c>
       <c r="K87" t="n">
-        <v>374.28</v>
+        <v>214.07</v>
       </c>
       <c r="L87" t="n">
-        <v>376.77</v>
+        <v>378.5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:40:42</t>
+          <t>09:41:39</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.47</v>
+        <v>2.91</v>
       </c>
       <c r="F88" t="n">
-        <v>7.66</v>
+        <v>7.12</v>
       </c>
       <c r="G88" t="n">
-        <v>76.59999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="I88" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-71.59</v>
+        <v>294.51</v>
       </c>
       <c r="K88" t="n">
-        <v>281.23</v>
+        <v>590.36</v>
       </c>
       <c r="L88" t="n">
-        <v>290.19</v>
+        <v>659.75</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-08-21.xlsx
+++ b/output/2024-08-21.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>61.22</v>
+        <v>53.12</v>
       </c>
       <c r="K14" t="n">
-        <v>-133.12</v>
+        <v>-115.52</v>
       </c>
       <c r="L14" t="n">
-        <v>146.52</v>
+        <v>127.15</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>176.41</v>
+        <v>121.52</v>
       </c>
       <c r="K15" t="n">
-        <v>267.48</v>
+        <v>184.25</v>
       </c>
       <c r="L15" t="n">
-        <v>320.41</v>
+        <v>220.71</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>-82.97</v>
+        <v>-74.20999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>36.97</v>
+        <v>33.07</v>
       </c>
       <c r="L16" t="n">
-        <v>90.84</v>
+        <v>81.25</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-17.48</v>
+        <v>-40.04</v>
       </c>
       <c r="K17" t="n">
-        <v>17.81</v>
+        <v>40.8</v>
       </c>
       <c r="L17" t="n">
-        <v>24.96</v>
+        <v>57.17</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-50.46</v>
+        <v>-87.31</v>
       </c>
       <c r="K18" t="n">
-        <v>38.55</v>
+        <v>66.7</v>
       </c>
       <c r="L18" t="n">
-        <v>63.5</v>
+        <v>109.87</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-165.54</v>
+        <v>-134.24</v>
       </c>
       <c r="K19" t="n">
-        <v>-190.58</v>
+        <v>-154.55</v>
       </c>
       <c r="L19" t="n">
-        <v>252.44</v>
+        <v>204.72</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-223.22</v>
+        <v>-249.33</v>
       </c>
       <c r="K20" t="n">
-        <v>29.43</v>
+        <v>32.88</v>
       </c>
       <c r="L20" t="n">
-        <v>225.15</v>
+        <v>251.49</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>28</v>
       </c>
       <c r="J21" t="n">
-        <v>-29.08</v>
+        <v>-43.26</v>
       </c>
       <c r="K21" t="n">
-        <v>-70.81</v>
+        <v>-105.35</v>
       </c>
       <c r="L21" t="n">
-        <v>76.55</v>
+        <v>113.89</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>-66.78</v>
+        <v>-57.2</v>
       </c>
       <c r="K22" t="n">
-        <v>381.21</v>
+        <v>326.53</v>
       </c>
       <c r="L22" t="n">
-        <v>387.01</v>
+        <v>331.5</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>149.39</v>
+        <v>144.22</v>
       </c>
       <c r="K23" t="n">
-        <v>215.63</v>
+        <v>208.16</v>
       </c>
       <c r="L23" t="n">
-        <v>262.32</v>
+        <v>253.24</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>-145.44</v>
+        <v>-164.04</v>
       </c>
       <c r="K24" t="n">
-        <v>217.14</v>
+        <v>244.91</v>
       </c>
       <c r="L24" t="n">
-        <v>261.35</v>
+        <v>294.77</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>68.8</v>
+        <v>126.4</v>
       </c>
       <c r="K25" t="n">
-        <v>103.12</v>
+        <v>189.45</v>
       </c>
       <c r="L25" t="n">
-        <v>123.96</v>
+        <v>227.74</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>275.16</v>
+        <v>364.02</v>
       </c>
       <c r="K26" t="n">
-        <v>124.03</v>
+        <v>164.08</v>
       </c>
       <c r="L26" t="n">
-        <v>301.82</v>
+        <v>399.29</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-520.42</v>
+        <v>-581.22</v>
       </c>
       <c r="K27" t="n">
-        <v>-385.37</v>
+        <v>-430.39</v>
       </c>
       <c r="L27" t="n">
-        <v>647.5700000000001</v>
+        <v>723.22</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-348.58</v>
+        <v>-363.64</v>
       </c>
       <c r="K28" t="n">
-        <v>459.56</v>
+        <v>479.41</v>
       </c>
       <c r="L28" t="n">
-        <v>576.8</v>
+        <v>601.72</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-6.83</v>
+        <v>-15.76</v>
       </c>
       <c r="K29" t="n">
-        <v>-30.84</v>
+        <v>-71.19</v>
       </c>
       <c r="L29" t="n">
-        <v>31.59</v>
+        <v>72.91</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>8.75</v>
+        <v>12.65</v>
       </c>
       <c r="K30" t="n">
-        <v>-83.48999999999999</v>
+        <v>-120.7</v>
       </c>
       <c r="L30" t="n">
-        <v>83.95</v>
+        <v>121.36</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>40.21</v>
+        <v>33.79</v>
       </c>
       <c r="K31" t="n">
-        <v>189.46</v>
+        <v>159.23</v>
       </c>
       <c r="L31" t="n">
-        <v>193.68</v>
+        <v>162.78</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>61.64</v>
+        <v>71.84</v>
       </c>
       <c r="K32" t="n">
-        <v>71.17</v>
+        <v>82.94</v>
       </c>
       <c r="L32" t="n">
-        <v>94.15000000000001</v>
+        <v>109.72</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>39.09</v>
+        <v>42.67</v>
       </c>
       <c r="K33" t="n">
-        <v>127.92</v>
+        <v>139.62</v>
       </c>
       <c r="L33" t="n">
-        <v>133.76</v>
+        <v>145.99</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>22.14</v>
+        <v>36.67</v>
       </c>
       <c r="K34" t="n">
-        <v>-44.12</v>
+        <v>-73.06</v>
       </c>
       <c r="L34" t="n">
-        <v>49.36</v>
+        <v>81.73999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>146.23</v>
+        <v>191.45</v>
       </c>
       <c r="K35" t="n">
-        <v>20.35</v>
+        <v>26.65</v>
       </c>
       <c r="L35" t="n">
-        <v>147.64</v>
+        <v>193.3</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-174.78</v>
+        <v>-154.18</v>
       </c>
       <c r="K36" t="n">
-        <v>362.78</v>
+        <v>320.02</v>
       </c>
       <c r="L36" t="n">
-        <v>402.69</v>
+        <v>355.22</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>67.44</v>
+        <v>60.77</v>
       </c>
       <c r="K37" t="n">
-        <v>442.43</v>
+        <v>398.69</v>
       </c>
       <c r="L37" t="n">
-        <v>447.54</v>
+        <v>403.3</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>-42.66</v>
+        <v>-73.58</v>
       </c>
       <c r="K38" t="n">
-        <v>105.43</v>
+        <v>181.85</v>
       </c>
       <c r="L38" t="n">
-        <v>113.74</v>
+        <v>196.17</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>174.46</v>
+        <v>181.49</v>
       </c>
       <c r="K39" t="n">
-        <v>306.31</v>
+        <v>318.65</v>
       </c>
       <c r="L39" t="n">
-        <v>352.51</v>
+        <v>366.71</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>30.38</v>
+        <v>51.41</v>
       </c>
       <c r="K40" t="n">
-        <v>148.33</v>
+        <v>251.02</v>
       </c>
       <c r="L40" t="n">
-        <v>151.41</v>
+        <v>256.23</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>-18</v>
+        <v>-22.83</v>
       </c>
       <c r="K41" t="n">
-        <v>324.3</v>
+        <v>411.44</v>
       </c>
       <c r="L41" t="n">
-        <v>324.8</v>
+        <v>412.07</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>-581.9299999999999</v>
+        <v>-629.0599999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>223.46</v>
+        <v>241.56</v>
       </c>
       <c r="L42" t="n">
-        <v>623.36</v>
+        <v>673.85</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-73.95</v>
+        <v>-82.06999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>584.4</v>
+        <v>648.51</v>
       </c>
       <c r="L43" t="n">
-        <v>589.0599999999999</v>
+        <v>653.6799999999999</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>46.28</v>
+        <v>37.32</v>
       </c>
       <c r="K44" t="n">
-        <v>-169.29</v>
+        <v>-136.5</v>
       </c>
       <c r="L44" t="n">
-        <v>175.51</v>
+        <v>141.51</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>28.05</v>
+        <v>23.18</v>
       </c>
       <c r="K45" t="n">
-        <v>242.09</v>
+        <v>200.07</v>
       </c>
       <c r="L45" t="n">
-        <v>243.71</v>
+        <v>201.4</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>27</v>
       </c>
       <c r="J46" t="n">
-        <v>43.16</v>
+        <v>36.21</v>
       </c>
       <c r="K46" t="n">
-        <v>-154.82</v>
+        <v>-129.89</v>
       </c>
       <c r="L46" t="n">
-        <v>160.72</v>
+        <v>134.85</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-35.8</v>
+        <v>-46.62</v>
       </c>
       <c r="K47" t="n">
-        <v>-71.48</v>
+        <v>-93.09</v>
       </c>
       <c r="L47" t="n">
-        <v>79.95</v>
+        <v>104.11</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>41.57</v>
+        <v>39.2</v>
       </c>
       <c r="K48" t="n">
-        <v>187.38</v>
+        <v>176.7</v>
       </c>
       <c r="L48" t="n">
-        <v>191.94</v>
+        <v>180.99</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>188.16</v>
+        <v>168.05</v>
       </c>
       <c r="K49" t="n">
-        <v>-100.57</v>
+        <v>-89.81999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>213.35</v>
+        <v>190.55</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>39.91</v>
+        <v>34.2</v>
       </c>
       <c r="K50" t="n">
-        <v>410.03</v>
+        <v>351.34</v>
       </c>
       <c r="L50" t="n">
-        <v>411.97</v>
+        <v>353</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-4.75</v>
+        <v>-5.95</v>
       </c>
       <c r="K51" t="n">
-        <v>153.05</v>
+        <v>191.64</v>
       </c>
       <c r="L51" t="n">
-        <v>153.12</v>
+        <v>191.73</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-134.1</v>
+        <v>-195.8</v>
       </c>
       <c r="K52" t="n">
-        <v>-33.06</v>
+        <v>-48.26</v>
       </c>
       <c r="L52" t="n">
-        <v>138.11</v>
+        <v>201.66</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>483.19</v>
+        <v>446.42</v>
       </c>
       <c r="K53" t="n">
-        <v>-228.9</v>
+        <v>-211.48</v>
       </c>
       <c r="L53" t="n">
-        <v>534.67</v>
+        <v>493.97</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-117.35</v>
+        <v>-124.21</v>
       </c>
       <c r="K54" t="n">
-        <v>386.48</v>
+        <v>409.08</v>
       </c>
       <c r="L54" t="n">
-        <v>403.91</v>
+        <v>427.52</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>55.14</v>
+        <v>55.74</v>
       </c>
       <c r="K55" t="n">
-        <v>401.84</v>
+        <v>406.2</v>
       </c>
       <c r="L55" t="n">
-        <v>405.6</v>
+        <v>410.01</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>215.26</v>
+        <v>304.67</v>
       </c>
       <c r="K56" t="n">
-        <v>19.22</v>
+        <v>27.2</v>
       </c>
       <c r="L56" t="n">
-        <v>216.11</v>
+        <v>305.88</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>283.12</v>
+        <v>417.46</v>
       </c>
       <c r="K57" t="n">
-        <v>55.82</v>
+        <v>82.3</v>
       </c>
       <c r="L57" t="n">
-        <v>288.57</v>
+        <v>425.5</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>726.24</v>
+        <v>672.75</v>
       </c>
       <c r="K58" t="n">
-        <v>-347.94</v>
+        <v>-322.32</v>
       </c>
       <c r="L58" t="n">
-        <v>805.28</v>
+        <v>745.97</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>123.61</v>
+        <v>126.6</v>
       </c>
       <c r="K59" t="n">
-        <v>79.66</v>
+        <v>81.58</v>
       </c>
       <c r="L59" t="n">
-        <v>147.05</v>
+        <v>150.61</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>77.42</v>
+        <v>90.7</v>
       </c>
       <c r="K60" t="n">
-        <v>30.07</v>
+        <v>35.23</v>
       </c>
       <c r="L60" t="n">
-        <v>83.05</v>
+        <v>97.3</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>181.82</v>
+        <v>141.67</v>
       </c>
       <c r="K61" t="n">
-        <v>-102.27</v>
+        <v>-79.69</v>
       </c>
       <c r="L61" t="n">
-        <v>208.61</v>
+        <v>162.54</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>-262.92</v>
+        <v>-228.3</v>
       </c>
       <c r="K62" t="n">
-        <v>-14.05</v>
+        <v>-12.2</v>
       </c>
       <c r="L62" t="n">
-        <v>263.3</v>
+        <v>228.62</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>53.44</v>
+        <v>82.78</v>
       </c>
       <c r="K63" t="n">
-        <v>-34.75</v>
+        <v>-53.82</v>
       </c>
       <c r="L63" t="n">
-        <v>63.75</v>
+        <v>98.73999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-19.58</v>
+        <v>-28.18</v>
       </c>
       <c r="K64" t="n">
-        <v>-88.06</v>
+        <v>-126.73</v>
       </c>
       <c r="L64" t="n">
-        <v>90.20999999999999</v>
+        <v>129.82</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-99.22</v>
+        <v>-131.27</v>
       </c>
       <c r="K65" t="n">
-        <v>-133.12</v>
+        <v>-176.12</v>
       </c>
       <c r="L65" t="n">
-        <v>166.03</v>
+        <v>219.66</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>256.77</v>
+        <v>229.99</v>
       </c>
       <c r="K66" t="n">
-        <v>-182.65</v>
+        <v>-163.6</v>
       </c>
       <c r="L66" t="n">
-        <v>315.1</v>
+        <v>282.24</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>-147.97</v>
+        <v>-162.48</v>
       </c>
       <c r="K67" t="n">
-        <v>57.23</v>
+        <v>62.85</v>
       </c>
       <c r="L67" t="n">
-        <v>158.66</v>
+        <v>174.22</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>67.73999999999999</v>
+        <v>74.55</v>
       </c>
       <c r="K68" t="n">
-        <v>-408.03</v>
+        <v>-449.02</v>
       </c>
       <c r="L68" t="n">
-        <v>413.61</v>
+        <v>455.16</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>95.48</v>
+        <v>138.08</v>
       </c>
       <c r="K69" t="n">
-        <v>134.39</v>
+        <v>194.36</v>
       </c>
       <c r="L69" t="n">
-        <v>164.86</v>
+        <v>238.41</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-19.73</v>
+        <v>-23.58</v>
       </c>
       <c r="K70" t="n">
-        <v>-202.18</v>
+        <v>-241.61</v>
       </c>
       <c r="L70" t="n">
-        <v>203.14</v>
+        <v>242.76</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>-79.08</v>
+        <v>-79.44</v>
       </c>
       <c r="K71" t="n">
-        <v>-598.0599999999999</v>
+        <v>-600.78</v>
       </c>
       <c r="L71" t="n">
-        <v>603.26</v>
+        <v>606.01</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>-393.49</v>
+        <v>-431.28</v>
       </c>
       <c r="K72" t="n">
-        <v>235.21</v>
+        <v>257.8</v>
       </c>
       <c r="L72" t="n">
-        <v>458.44</v>
+        <v>502.45</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-75.22</v>
+        <v>-83.27</v>
       </c>
       <c r="K73" t="n">
-        <v>-777.45</v>
+        <v>-860.64</v>
       </c>
       <c r="L73" t="n">
-        <v>781.08</v>
+        <v>864.66</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>-48.11</v>
+        <v>-42.96</v>
       </c>
       <c r="K74" t="n">
-        <v>184.8</v>
+        <v>165.02</v>
       </c>
       <c r="L74" t="n">
-        <v>190.96</v>
+        <v>170.52</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>136.3</v>
+        <v>101.18</v>
       </c>
       <c r="K75" t="n">
-        <v>-117.88</v>
+        <v>-87.5</v>
       </c>
       <c r="L75" t="n">
-        <v>180.2</v>
+        <v>133.77</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>54.77</v>
+        <v>57.83</v>
       </c>
       <c r="K76" t="n">
-        <v>-74.88</v>
+        <v>-79.06</v>
       </c>
       <c r="L76" t="n">
-        <v>92.77</v>
+        <v>97.95</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-187.73</v>
+        <v>-146</v>
       </c>
       <c r="K77" t="n">
-        <v>223.41</v>
+        <v>173.74</v>
       </c>
       <c r="L77" t="n">
-        <v>291.81</v>
+        <v>226.94</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>91.27</v>
+        <v>106.06</v>
       </c>
       <c r="K78" t="n">
-        <v>56.28</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>107.23</v>
+        <v>124.6</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-135.09</v>
+        <v>-148.61</v>
       </c>
       <c r="K79" t="n">
-        <v>-133.31</v>
+        <v>-146.66</v>
       </c>
       <c r="L79" t="n">
-        <v>189.79</v>
+        <v>208.79</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>-219.57</v>
+        <v>-252.55</v>
       </c>
       <c r="K80" t="n">
-        <v>-52.03</v>
+        <v>-59.85</v>
       </c>
       <c r="L80" t="n">
-        <v>225.65</v>
+        <v>259.54</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>192.4</v>
+        <v>207.98</v>
       </c>
       <c r="K81" t="n">
-        <v>120.98</v>
+        <v>130.78</v>
       </c>
       <c r="L81" t="n">
-        <v>227.27</v>
+        <v>245.68</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>27</v>
       </c>
       <c r="J82" t="n">
-        <v>410.17</v>
+        <v>380.89</v>
       </c>
       <c r="K82" t="n">
-        <v>-36.22</v>
+        <v>-33.63</v>
       </c>
       <c r="L82" t="n">
-        <v>411.76</v>
+        <v>382.37</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>28</v>
       </c>
       <c r="J83" t="n">
-        <v>124.79</v>
+        <v>204.01</v>
       </c>
       <c r="K83" t="n">
-        <v>86.03</v>
+        <v>140.64</v>
       </c>
       <c r="L83" t="n">
-        <v>151.57</v>
+        <v>247.79</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>24</v>
       </c>
       <c r="J84" t="n">
-        <v>-173.04</v>
+        <v>-233.78</v>
       </c>
       <c r="K84" t="n">
-        <v>-178.96</v>
+        <v>-241.77</v>
       </c>
       <c r="L84" t="n">
-        <v>248.94</v>
+        <v>336.31</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>77.15000000000001</v>
+        <v>90.41</v>
       </c>
       <c r="K85" t="n">
-        <v>-378.07</v>
+        <v>-443.04</v>
       </c>
       <c r="L85" t="n">
-        <v>385.86</v>
+        <v>452.17</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>635.87</v>
+        <v>779.05</v>
       </c>
       <c r="K86" t="n">
-        <v>95.77</v>
+        <v>117.33</v>
       </c>
       <c r="L86" t="n">
-        <v>643.05</v>
+        <v>787.84</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>28</v>
       </c>
       <c r="J87" t="n">
-        <v>312.14</v>
+        <v>352.54</v>
       </c>
       <c r="K87" t="n">
-        <v>214.07</v>
+        <v>241.78</v>
       </c>
       <c r="L87" t="n">
-        <v>378.5</v>
+        <v>427.48</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>294.51</v>
+        <v>337.47</v>
       </c>
       <c r="K88" t="n">
-        <v>590.36</v>
+        <v>676.49</v>
       </c>
       <c r="L88" t="n">
-        <v>659.75</v>
+        <v>755.99</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-08-21.xlsx
+++ b/output/2024-08-21.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>53.12</v>
+        <v>43.18</v>
       </c>
       <c r="K14" t="n">
-        <v>-115.52</v>
+        <v>-93.90000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>127.15</v>
+        <v>103.36</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>121.52</v>
+        <v>106.78</v>
       </c>
       <c r="K15" t="n">
-        <v>184.25</v>
+        <v>161.9</v>
       </c>
       <c r="L15" t="n">
-        <v>220.71</v>
+        <v>193.94</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>-74.20999999999999</v>
+        <v>-73.59999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>33.07</v>
+        <v>32.8</v>
       </c>
       <c r="L16" t="n">
-        <v>81.25</v>
+        <v>80.58</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-40.04</v>
+        <v>-31.38</v>
       </c>
       <c r="K17" t="n">
-        <v>40.8</v>
+        <v>31.98</v>
       </c>
       <c r="L17" t="n">
-        <v>57.17</v>
+        <v>44.81</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-87.31</v>
+        <v>-67.88</v>
       </c>
       <c r="K18" t="n">
-        <v>66.7</v>
+        <v>51.85</v>
       </c>
       <c r="L18" t="n">
-        <v>109.87</v>
+        <v>85.42</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-134.24</v>
+        <v>-110</v>
       </c>
       <c r="K19" t="n">
-        <v>-154.55</v>
+        <v>-126.64</v>
       </c>
       <c r="L19" t="n">
-        <v>204.72</v>
+        <v>167.75</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-249.33</v>
+        <v>-160.94</v>
       </c>
       <c r="K20" t="n">
-        <v>32.88</v>
+        <v>21.22</v>
       </c>
       <c r="L20" t="n">
-        <v>251.49</v>
+        <v>162.33</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>28</v>
       </c>
       <c r="J21" t="n">
-        <v>-43.26</v>
+        <v>-35.04</v>
       </c>
       <c r="K21" t="n">
-        <v>-105.35</v>
+        <v>-85.33</v>
       </c>
       <c r="L21" t="n">
-        <v>113.89</v>
+        <v>92.23999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>-57.2</v>
+        <v>-41.97</v>
       </c>
       <c r="K22" t="n">
-        <v>326.53</v>
+        <v>239.59</v>
       </c>
       <c r="L22" t="n">
-        <v>331.5</v>
+        <v>243.23</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>144.22</v>
+        <v>104.6</v>
       </c>
       <c r="K23" t="n">
-        <v>208.16</v>
+        <v>150.98</v>
       </c>
       <c r="L23" t="n">
-        <v>253.24</v>
+        <v>183.68</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>-164.04</v>
+        <v>-103.76</v>
       </c>
       <c r="K24" t="n">
-        <v>244.91</v>
+        <v>154.91</v>
       </c>
       <c r="L24" t="n">
-        <v>294.77</v>
+        <v>186.45</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>126.4</v>
+        <v>75.34</v>
       </c>
       <c r="K25" t="n">
-        <v>189.45</v>
+        <v>112.93</v>
       </c>
       <c r="L25" t="n">
-        <v>227.74</v>
+        <v>135.76</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>364.02</v>
+        <v>207.46</v>
       </c>
       <c r="K26" t="n">
-        <v>164.08</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>399.29</v>
+        <v>227.57</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-581.22</v>
+        <v>-298.95</v>
       </c>
       <c r="K27" t="n">
-        <v>-430.39</v>
+        <v>-221.37</v>
       </c>
       <c r="L27" t="n">
-        <v>723.22</v>
+        <v>371.99</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-363.64</v>
+        <v>-213.08</v>
       </c>
       <c r="K28" t="n">
-        <v>479.41</v>
+        <v>280.92</v>
       </c>
       <c r="L28" t="n">
-        <v>601.72</v>
+        <v>352.59</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-15.76</v>
+        <v>-12.71</v>
       </c>
       <c r="K29" t="n">
-        <v>-71.19</v>
+        <v>-57.41</v>
       </c>
       <c r="L29" t="n">
-        <v>72.91</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>12.65</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>-120.7</v>
+        <v>-89.53</v>
       </c>
       <c r="L30" t="n">
-        <v>121.36</v>
+        <v>90.02</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>33.79</v>
+        <v>27.43</v>
       </c>
       <c r="K31" t="n">
-        <v>159.23</v>
+        <v>129.24</v>
       </c>
       <c r="L31" t="n">
-        <v>162.78</v>
+        <v>132.11</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>71.84</v>
+        <v>58.76</v>
       </c>
       <c r="K32" t="n">
-        <v>82.94</v>
+        <v>67.84</v>
       </c>
       <c r="L32" t="n">
-        <v>109.72</v>
+        <v>89.75</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>42.67</v>
+        <v>32.34</v>
       </c>
       <c r="K33" t="n">
-        <v>139.62</v>
+        <v>105.84</v>
       </c>
       <c r="L33" t="n">
-        <v>145.99</v>
+        <v>110.67</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>36.67</v>
+        <v>31.78</v>
       </c>
       <c r="K34" t="n">
-        <v>-73.06</v>
+        <v>-63.33</v>
       </c>
       <c r="L34" t="n">
-        <v>81.73999999999999</v>
+        <v>70.84999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>191.45</v>
+        <v>136.76</v>
       </c>
       <c r="K35" t="n">
-        <v>26.65</v>
+        <v>19.03</v>
       </c>
       <c r="L35" t="n">
-        <v>193.3</v>
+        <v>138.07</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-154.18</v>
+        <v>-111.4</v>
       </c>
       <c r="K36" t="n">
-        <v>320.02</v>
+        <v>231.22</v>
       </c>
       <c r="L36" t="n">
-        <v>355.22</v>
+        <v>256.65</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>60.77</v>
+        <v>43.12</v>
       </c>
       <c r="K37" t="n">
-        <v>398.69</v>
+        <v>282.9</v>
       </c>
       <c r="L37" t="n">
-        <v>403.3</v>
+        <v>286.17</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>-73.58</v>
+        <v>-48.95</v>
       </c>
       <c r="K38" t="n">
-        <v>181.85</v>
+        <v>120.96</v>
       </c>
       <c r="L38" t="n">
-        <v>196.17</v>
+        <v>130.49</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>181.49</v>
+        <v>113.85</v>
       </c>
       <c r="K39" t="n">
-        <v>318.65</v>
+        <v>199.9</v>
       </c>
       <c r="L39" t="n">
-        <v>366.71</v>
+        <v>230.05</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>51.41</v>
+        <v>29.6</v>
       </c>
       <c r="K40" t="n">
-        <v>251.02</v>
+        <v>144.53</v>
       </c>
       <c r="L40" t="n">
-        <v>256.23</v>
+        <v>147.53</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>-22.83</v>
+        <v>-13.41</v>
       </c>
       <c r="K41" t="n">
-        <v>411.44</v>
+        <v>241.69</v>
       </c>
       <c r="L41" t="n">
-        <v>412.07</v>
+        <v>242.06</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>-629.0599999999999</v>
+        <v>-351.87</v>
       </c>
       <c r="K42" t="n">
-        <v>241.56</v>
+        <v>135.12</v>
       </c>
       <c r="L42" t="n">
-        <v>673.85</v>
+        <v>376.93</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-82.06999999999999</v>
+        <v>-45.75</v>
       </c>
       <c r="K43" t="n">
-        <v>648.51</v>
+        <v>361.52</v>
       </c>
       <c r="L43" t="n">
-        <v>653.6799999999999</v>
+        <v>364.41</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>37.32</v>
+        <v>35.3</v>
       </c>
       <c r="K44" t="n">
-        <v>-136.5</v>
+        <v>-129.11</v>
       </c>
       <c r="L44" t="n">
-        <v>141.51</v>
+        <v>133.85</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>23.18</v>
+        <v>18.48</v>
       </c>
       <c r="K45" t="n">
-        <v>200.07</v>
+        <v>159.48</v>
       </c>
       <c r="L45" t="n">
-        <v>201.4</v>
+        <v>160.55</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>27</v>
       </c>
       <c r="J46" t="n">
-        <v>36.21</v>
+        <v>33.09</v>
       </c>
       <c r="K46" t="n">
-        <v>-129.89</v>
+        <v>-118.71</v>
       </c>
       <c r="L46" t="n">
-        <v>134.85</v>
+        <v>123.23</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-46.62</v>
+        <v>-37.75</v>
       </c>
       <c r="K47" t="n">
-        <v>-93.09</v>
+        <v>-75.38</v>
       </c>
       <c r="L47" t="n">
-        <v>104.11</v>
+        <v>84.3</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>39.2</v>
+        <v>30.52</v>
       </c>
       <c r="K48" t="n">
-        <v>176.7</v>
+        <v>137.56</v>
       </c>
       <c r="L48" t="n">
-        <v>180.99</v>
+        <v>140.9</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>168.05</v>
+        <v>138.57</v>
       </c>
       <c r="K49" t="n">
-        <v>-89.81999999999999</v>
+        <v>-74.06</v>
       </c>
       <c r="L49" t="n">
-        <v>190.55</v>
+        <v>157.12</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>34.2</v>
+        <v>25.62</v>
       </c>
       <c r="K50" t="n">
-        <v>351.34</v>
+        <v>263.17</v>
       </c>
       <c r="L50" t="n">
-        <v>353</v>
+        <v>264.42</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-5.95</v>
+        <v>-4.17</v>
       </c>
       <c r="K51" t="n">
-        <v>191.64</v>
+        <v>134.32</v>
       </c>
       <c r="L51" t="n">
-        <v>191.73</v>
+        <v>134.38</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-195.8</v>
+        <v>-129.77</v>
       </c>
       <c r="K52" t="n">
-        <v>-48.26</v>
+        <v>-31.99</v>
       </c>
       <c r="L52" t="n">
-        <v>201.66</v>
+        <v>133.65</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>446.42</v>
+        <v>273.91</v>
       </c>
       <c r="K53" t="n">
-        <v>-211.48</v>
+        <v>-129.76</v>
       </c>
       <c r="L53" t="n">
-        <v>493.97</v>
+        <v>303.09</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-124.21</v>
+        <v>-71.29000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>409.08</v>
+        <v>234.79</v>
       </c>
       <c r="L54" t="n">
-        <v>427.52</v>
+        <v>245.38</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>55.74</v>
+        <v>36.69</v>
       </c>
       <c r="K55" t="n">
-        <v>406.2</v>
+        <v>267.38</v>
       </c>
       <c r="L55" t="n">
-        <v>410.01</v>
+        <v>269.88</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>304.67</v>
+        <v>188.41</v>
       </c>
       <c r="K56" t="n">
-        <v>27.2</v>
+        <v>16.82</v>
       </c>
       <c r="L56" t="n">
-        <v>305.88</v>
+        <v>189.16</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>417.46</v>
+        <v>245.46</v>
       </c>
       <c r="K57" t="n">
-        <v>82.3</v>
+        <v>48.39</v>
       </c>
       <c r="L57" t="n">
-        <v>425.5</v>
+        <v>250.19</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>672.75</v>
+        <v>410.44</v>
       </c>
       <c r="K58" t="n">
-        <v>-322.32</v>
+        <v>-196.64</v>
       </c>
       <c r="L58" t="n">
-        <v>745.97</v>
+        <v>455.11</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>126.6</v>
+        <v>96.52</v>
       </c>
       <c r="K59" t="n">
-        <v>81.58</v>
+        <v>62.2</v>
       </c>
       <c r="L59" t="n">
-        <v>150.61</v>
+        <v>114.83</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>90.7</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>35.23</v>
+        <v>29.05</v>
       </c>
       <c r="L60" t="n">
-        <v>97.3</v>
+        <v>80.23999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>141.67</v>
+        <v>125.91</v>
       </c>
       <c r="K61" t="n">
-        <v>-79.69</v>
+        <v>-70.81999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>162.54</v>
+        <v>144.46</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>-228.3</v>
+        <v>-173.21</v>
       </c>
       <c r="K62" t="n">
-        <v>-12.2</v>
+        <v>-9.26</v>
       </c>
       <c r="L62" t="n">
-        <v>228.62</v>
+        <v>173.45</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>82.78</v>
+        <v>62.96</v>
       </c>
       <c r="K63" t="n">
-        <v>-53.82</v>
+        <v>-40.94</v>
       </c>
       <c r="L63" t="n">
-        <v>98.73999999999999</v>
+        <v>75.09999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-28.18</v>
+        <v>-21.22</v>
       </c>
       <c r="K64" t="n">
-        <v>-126.73</v>
+        <v>-95.44</v>
       </c>
       <c r="L64" t="n">
-        <v>129.82</v>
+        <v>97.77</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-131.27</v>
+        <v>-83.38</v>
       </c>
       <c r="K65" t="n">
-        <v>-176.12</v>
+        <v>-111.86</v>
       </c>
       <c r="L65" t="n">
-        <v>219.66</v>
+        <v>139.52</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>229.99</v>
+        <v>161.48</v>
       </c>
       <c r="K66" t="n">
-        <v>-163.6</v>
+        <v>-114.87</v>
       </c>
       <c r="L66" t="n">
-        <v>282.24</v>
+        <v>198.16</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>-162.48</v>
+        <v>-124.63</v>
       </c>
       <c r="K67" t="n">
-        <v>62.85</v>
+        <v>48.2</v>
       </c>
       <c r="L67" t="n">
-        <v>174.22</v>
+        <v>133.62</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>74.55</v>
+        <v>43.91</v>
       </c>
       <c r="K68" t="n">
-        <v>-449.02</v>
+        <v>-264.51</v>
       </c>
       <c r="L68" t="n">
-        <v>455.16</v>
+        <v>268.13</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>138.08</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>194.36</v>
+        <v>120.99</v>
       </c>
       <c r="L69" t="n">
-        <v>238.41</v>
+        <v>148.42</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-23.58</v>
+        <v>-14.78</v>
       </c>
       <c r="K70" t="n">
-        <v>-241.61</v>
+        <v>-151.43</v>
       </c>
       <c r="L70" t="n">
-        <v>242.76</v>
+        <v>152.15</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>-79.44</v>
+        <v>-49.76</v>
       </c>
       <c r="K71" t="n">
-        <v>-600.78</v>
+        <v>-376.32</v>
       </c>
       <c r="L71" t="n">
-        <v>606.01</v>
+        <v>379.59</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>-431.28</v>
+        <v>-261.71</v>
       </c>
       <c r="K72" t="n">
-        <v>257.8</v>
+        <v>156.44</v>
       </c>
       <c r="L72" t="n">
-        <v>502.45</v>
+        <v>304.91</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-83.27</v>
+        <v>-47.86</v>
       </c>
       <c r="K73" t="n">
-        <v>-860.64</v>
+        <v>-494.6</v>
       </c>
       <c r="L73" t="n">
-        <v>864.66</v>
+        <v>496.91</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>-42.96</v>
+        <v>-34.91</v>
       </c>
       <c r="K74" t="n">
-        <v>165.02</v>
+        <v>134.09</v>
       </c>
       <c r="L74" t="n">
-        <v>170.52</v>
+        <v>138.56</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>101.18</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="K75" t="n">
-        <v>-87.5</v>
+        <v>-80.73</v>
       </c>
       <c r="L75" t="n">
-        <v>133.77</v>
+        <v>123.42</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>57.83</v>
+        <v>49.9</v>
       </c>
       <c r="K76" t="n">
-        <v>-79.06</v>
+        <v>-68.23</v>
       </c>
       <c r="L76" t="n">
-        <v>97.95</v>
+        <v>84.53</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-146</v>
+        <v>-130.22</v>
       </c>
       <c r="K77" t="n">
-        <v>173.74</v>
+        <v>154.96</v>
       </c>
       <c r="L77" t="n">
-        <v>226.94</v>
+        <v>202.41</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>106.06</v>
+        <v>83.31</v>
       </c>
       <c r="K78" t="n">
-        <v>65.40000000000001</v>
+        <v>51.37</v>
       </c>
       <c r="L78" t="n">
-        <v>124.6</v>
+        <v>97.87</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-148.61</v>
+        <v>-107.72</v>
       </c>
       <c r="K79" t="n">
-        <v>-146.66</v>
+        <v>-106.3</v>
       </c>
       <c r="L79" t="n">
-        <v>208.79</v>
+        <v>151.33</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>-252.55</v>
+        <v>-165.03</v>
       </c>
       <c r="K80" t="n">
-        <v>-59.85</v>
+        <v>-39.11</v>
       </c>
       <c r="L80" t="n">
-        <v>259.54</v>
+        <v>169.6</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>207.98</v>
+        <v>145.28</v>
       </c>
       <c r="K81" t="n">
-        <v>130.78</v>
+        <v>91.34999999999999</v>
       </c>
       <c r="L81" t="n">
-        <v>245.68</v>
+        <v>171.61</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>27</v>
       </c>
       <c r="J82" t="n">
-        <v>380.89</v>
+        <v>277.2</v>
       </c>
       <c r="K82" t="n">
-        <v>-33.63</v>
+        <v>-24.48</v>
       </c>
       <c r="L82" t="n">
-        <v>382.37</v>
+        <v>278.28</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>28</v>
       </c>
       <c r="J83" t="n">
-        <v>204.01</v>
+        <v>136.7</v>
       </c>
       <c r="K83" t="n">
-        <v>140.64</v>
+        <v>94.23999999999999</v>
       </c>
       <c r="L83" t="n">
-        <v>247.79</v>
+        <v>166.03</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>24</v>
       </c>
       <c r="J84" t="n">
-        <v>-233.78</v>
+        <v>-137.34</v>
       </c>
       <c r="K84" t="n">
-        <v>-241.77</v>
+        <v>-142.03</v>
       </c>
       <c r="L84" t="n">
-        <v>336.31</v>
+        <v>197.57</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>90.41</v>
+        <v>51.45</v>
       </c>
       <c r="K85" t="n">
-        <v>-443.04</v>
+        <v>-252.11</v>
       </c>
       <c r="L85" t="n">
-        <v>452.17</v>
+        <v>257.31</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>779.05</v>
+        <v>388.53</v>
       </c>
       <c r="K86" t="n">
-        <v>117.33</v>
+        <v>58.52</v>
       </c>
       <c r="L86" t="n">
-        <v>787.84</v>
+        <v>392.91</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>28</v>
       </c>
       <c r="J87" t="n">
-        <v>352.54</v>
+        <v>223.99</v>
       </c>
       <c r="K87" t="n">
-        <v>241.78</v>
+        <v>153.62</v>
       </c>
       <c r="L87" t="n">
-        <v>427.48</v>
+        <v>271.61</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>337.47</v>
+        <v>171.8</v>
       </c>
       <c r="K88" t="n">
-        <v>676.49</v>
+        <v>344.39</v>
       </c>
       <c r="L88" t="n">
-        <v>755.99</v>
+        <v>384.86</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-08-21.xlsx
+++ b/output/2024-08-21.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>43.18</v>
+        <v>40.14</v>
       </c>
       <c r="K14" t="n">
-        <v>-93.90000000000001</v>
+        <v>-87.28</v>
       </c>
       <c r="L14" t="n">
-        <v>103.36</v>
+        <v>96.06</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>106.78</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>161.9</v>
+        <v>149.44</v>
       </c>
       <c r="L15" t="n">
-        <v>193.94</v>
+        <v>179.02</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>-73.59999999999999</v>
+        <v>-66.37</v>
       </c>
       <c r="K16" t="n">
-        <v>32.8</v>
+        <v>29.57</v>
       </c>
       <c r="L16" t="n">
-        <v>80.58</v>
+        <v>72.66</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-31.38</v>
+        <v>-29.77</v>
       </c>
       <c r="K17" t="n">
-        <v>31.98</v>
+        <v>30.33</v>
       </c>
       <c r="L17" t="n">
-        <v>44.81</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-67.88</v>
+        <v>-64.56999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>51.85</v>
+        <v>49.33</v>
       </c>
       <c r="L18" t="n">
-        <v>85.42</v>
+        <v>81.26000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-110</v>
+        <v>-104.86</v>
       </c>
       <c r="K19" t="n">
-        <v>-126.64</v>
+        <v>-120.72</v>
       </c>
       <c r="L19" t="n">
-        <v>167.75</v>
+        <v>159.9</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-160.94</v>
+        <v>-161.06</v>
       </c>
       <c r="K20" t="n">
-        <v>21.22</v>
+        <v>21.24</v>
       </c>
       <c r="L20" t="n">
-        <v>162.33</v>
+        <v>162.46</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>28</v>
       </c>
       <c r="J21" t="n">
-        <v>-35.04</v>
+        <v>-34.04</v>
       </c>
       <c r="K21" t="n">
-        <v>-85.33</v>
+        <v>-82.91</v>
       </c>
       <c r="L21" t="n">
-        <v>92.23999999999999</v>
+        <v>89.63</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>-41.97</v>
+        <v>-41.51</v>
       </c>
       <c r="K22" t="n">
-        <v>239.59</v>
+        <v>236.98</v>
       </c>
       <c r="L22" t="n">
-        <v>243.23</v>
+        <v>240.59</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>104.6</v>
+        <v>103.91</v>
       </c>
       <c r="K23" t="n">
-        <v>150.98</v>
+        <v>149.97</v>
       </c>
       <c r="L23" t="n">
-        <v>183.68</v>
+        <v>182.45</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>-103.76</v>
+        <v>-104.38</v>
       </c>
       <c r="K24" t="n">
-        <v>154.91</v>
+        <v>155.84</v>
       </c>
       <c r="L24" t="n">
-        <v>186.45</v>
+        <v>187.57</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>75.34</v>
+        <v>77.39</v>
       </c>
       <c r="K25" t="n">
-        <v>112.93</v>
+        <v>115.99</v>
       </c>
       <c r="L25" t="n">
-        <v>135.76</v>
+        <v>139.44</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>207.46</v>
+        <v>211.57</v>
       </c>
       <c r="K26" t="n">
-        <v>93.51000000000001</v>
+        <v>95.37</v>
       </c>
       <c r="L26" t="n">
-        <v>227.57</v>
+        <v>232.07</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-298.95</v>
+        <v>-308.63</v>
       </c>
       <c r="K27" t="n">
-        <v>-221.37</v>
+        <v>-228.54</v>
       </c>
       <c r="L27" t="n">
-        <v>371.99</v>
+        <v>384.03</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-213.08</v>
+        <v>-216.58</v>
       </c>
       <c r="K28" t="n">
-        <v>280.92</v>
+        <v>285.53</v>
       </c>
       <c r="L28" t="n">
-        <v>352.59</v>
+        <v>358.38</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-12.71</v>
+        <v>-11.66</v>
       </c>
       <c r="K29" t="n">
-        <v>-57.41</v>
+        <v>-52.65</v>
       </c>
       <c r="L29" t="n">
-        <v>58.8</v>
+        <v>53.92</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>9.380000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="K30" t="n">
-        <v>-89.53</v>
+        <v>-84.20999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>90.02</v>
+        <v>84.67</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>27.43</v>
+        <v>25.48</v>
       </c>
       <c r="K31" t="n">
-        <v>129.24</v>
+        <v>120.05</v>
       </c>
       <c r="L31" t="n">
-        <v>132.11</v>
+        <v>122.72</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>58.76</v>
+        <v>55.81</v>
       </c>
       <c r="K32" t="n">
-        <v>67.84</v>
+        <v>64.44</v>
       </c>
       <c r="L32" t="n">
-        <v>89.75</v>
+        <v>85.25</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>32.34</v>
+        <v>31.02</v>
       </c>
       <c r="K33" t="n">
-        <v>105.84</v>
+        <v>101.52</v>
       </c>
       <c r="L33" t="n">
-        <v>110.67</v>
+        <v>106.15</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>31.78</v>
+        <v>30.25</v>
       </c>
       <c r="K34" t="n">
-        <v>-63.33</v>
+        <v>-60.27</v>
       </c>
       <c r="L34" t="n">
-        <v>70.84999999999999</v>
+        <v>67.43000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>136.76</v>
+        <v>135.77</v>
       </c>
       <c r="K35" t="n">
-        <v>19.03</v>
+        <v>18.9</v>
       </c>
       <c r="L35" t="n">
-        <v>138.07</v>
+        <v>137.07</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-111.4</v>
+        <v>-110.07</v>
       </c>
       <c r="K36" t="n">
-        <v>231.22</v>
+        <v>228.46</v>
       </c>
       <c r="L36" t="n">
-        <v>256.65</v>
+        <v>253.6</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>43.12</v>
+        <v>42.39</v>
       </c>
       <c r="K37" t="n">
-        <v>282.9</v>
+        <v>278.13</v>
       </c>
       <c r="L37" t="n">
-        <v>286.17</v>
+        <v>281.34</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>-48.95</v>
+        <v>-48.53</v>
       </c>
       <c r="K38" t="n">
-        <v>120.96</v>
+        <v>119.92</v>
       </c>
       <c r="L38" t="n">
-        <v>130.49</v>
+        <v>129.37</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>113.85</v>
+        <v>114.4</v>
       </c>
       <c r="K39" t="n">
-        <v>199.9</v>
+        <v>200.86</v>
       </c>
       <c r="L39" t="n">
-        <v>230.05</v>
+        <v>231.15</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>29.6</v>
+        <v>30.26</v>
       </c>
       <c r="K40" t="n">
-        <v>144.53</v>
+        <v>147.73</v>
       </c>
       <c r="L40" t="n">
-        <v>147.53</v>
+        <v>150.8</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>-13.41</v>
+        <v>-13.68</v>
       </c>
       <c r="K41" t="n">
-        <v>241.69</v>
+        <v>246.4</v>
       </c>
       <c r="L41" t="n">
-        <v>242.06</v>
+        <v>246.78</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>-351.87</v>
+        <v>-360.19</v>
       </c>
       <c r="K42" t="n">
-        <v>135.12</v>
+        <v>138.32</v>
       </c>
       <c r="L42" t="n">
-        <v>376.93</v>
+        <v>385.83</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-45.75</v>
+        <v>-46.8</v>
       </c>
       <c r="K43" t="n">
-        <v>361.52</v>
+        <v>369.79</v>
       </c>
       <c r="L43" t="n">
-        <v>364.41</v>
+        <v>372.74</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>35.3</v>
+        <v>31.71</v>
       </c>
       <c r="K44" t="n">
-        <v>-129.11</v>
+        <v>-116</v>
       </c>
       <c r="L44" t="n">
-        <v>133.85</v>
+        <v>120.26</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>18.48</v>
+        <v>17.02</v>
       </c>
       <c r="K45" t="n">
-        <v>159.48</v>
+        <v>146.91</v>
       </c>
       <c r="L45" t="n">
-        <v>160.55</v>
+        <v>147.9</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>27</v>
       </c>
       <c r="J46" t="n">
-        <v>33.09</v>
+        <v>30.03</v>
       </c>
       <c r="K46" t="n">
-        <v>-118.71</v>
+        <v>-107.72</v>
       </c>
       <c r="L46" t="n">
-        <v>123.23</v>
+        <v>111.82</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-37.75</v>
+        <v>-35.92</v>
       </c>
       <c r="K47" t="n">
-        <v>-75.38</v>
+        <v>-71.70999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>84.3</v>
+        <v>80.20999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>30.52</v>
+        <v>29.17</v>
       </c>
       <c r="K48" t="n">
-        <v>137.56</v>
+        <v>131.47</v>
       </c>
       <c r="L48" t="n">
-        <v>140.9</v>
+        <v>134.67</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>138.57</v>
+        <v>133</v>
       </c>
       <c r="K49" t="n">
-        <v>-74.06</v>
+        <v>-71.09</v>
       </c>
       <c r="L49" t="n">
-        <v>157.12</v>
+        <v>150.81</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>25.62</v>
+        <v>25.22</v>
       </c>
       <c r="K50" t="n">
-        <v>263.17</v>
+        <v>259.08</v>
       </c>
       <c r="L50" t="n">
-        <v>264.42</v>
+        <v>260.31</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-4.17</v>
+        <v>-4.1</v>
       </c>
       <c r="K51" t="n">
-        <v>134.32</v>
+        <v>132.1</v>
       </c>
       <c r="L51" t="n">
-        <v>134.38</v>
+        <v>132.16</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-129.77</v>
+        <v>-128.62</v>
       </c>
       <c r="K52" t="n">
-        <v>-31.99</v>
+        <v>-31.7</v>
       </c>
       <c r="L52" t="n">
-        <v>133.65</v>
+        <v>132.47</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>273.91</v>
+        <v>277.02</v>
       </c>
       <c r="K53" t="n">
-        <v>-129.76</v>
+        <v>-131.23</v>
       </c>
       <c r="L53" t="n">
-        <v>303.09</v>
+        <v>306.53</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-71.29000000000001</v>
+        <v>-73.09999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>234.79</v>
+        <v>240.74</v>
       </c>
       <c r="L54" t="n">
-        <v>245.38</v>
+        <v>251.59</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>36.69</v>
+        <v>36.67</v>
       </c>
       <c r="K55" t="n">
-        <v>267.38</v>
+        <v>267.2</v>
       </c>
       <c r="L55" t="n">
-        <v>269.88</v>
+        <v>269.71</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>188.41</v>
+        <v>189.67</v>
       </c>
       <c r="K56" t="n">
-        <v>16.82</v>
+        <v>16.93</v>
       </c>
       <c r="L56" t="n">
-        <v>189.16</v>
+        <v>190.42</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>245.46</v>
+        <v>248.49</v>
       </c>
       <c r="K57" t="n">
-        <v>48.39</v>
+        <v>48.99</v>
       </c>
       <c r="L57" t="n">
-        <v>250.19</v>
+        <v>253.27</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>410.44</v>
+        <v>415.21</v>
       </c>
       <c r="K58" t="n">
-        <v>-196.64</v>
+        <v>-198.93</v>
       </c>
       <c r="L58" t="n">
-        <v>455.11</v>
+        <v>460.4</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>96.52</v>
+        <v>89.34</v>
       </c>
       <c r="K59" t="n">
-        <v>62.2</v>
+        <v>57.57</v>
       </c>
       <c r="L59" t="n">
-        <v>114.83</v>
+        <v>106.28</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>74.79000000000001</v>
+        <v>68.67</v>
       </c>
       <c r="K60" t="n">
-        <v>29.05</v>
+        <v>26.67</v>
       </c>
       <c r="L60" t="n">
-        <v>80.23999999999999</v>
+        <v>73.67</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>125.91</v>
+        <v>114.23</v>
       </c>
       <c r="K61" t="n">
-        <v>-70.81999999999999</v>
+        <v>-64.25</v>
       </c>
       <c r="L61" t="n">
-        <v>144.46</v>
+        <v>131.06</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>-173.21</v>
+        <v>-166.78</v>
       </c>
       <c r="K62" t="n">
-        <v>-9.26</v>
+        <v>-8.91</v>
       </c>
       <c r="L62" t="n">
-        <v>173.45</v>
+        <v>167.02</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>62.96</v>
+        <v>60.66</v>
       </c>
       <c r="K63" t="n">
-        <v>-40.94</v>
+        <v>-39.44</v>
       </c>
       <c r="L63" t="n">
-        <v>75.09999999999999</v>
+        <v>72.36</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-21.22</v>
+        <v>-20.31</v>
       </c>
       <c r="K64" t="n">
-        <v>-95.44</v>
+        <v>-91.31999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>97.77</v>
+        <v>93.55</v>
       </c>
     </row>
     <row r="65">
@@ -2785,10 +2785,10 @@
         <v>-83.38</v>
       </c>
       <c r="K65" t="n">
-        <v>-111.86</v>
+        <v>-111.87</v>
       </c>
       <c r="L65" t="n">
-        <v>139.52</v>
+        <v>139.53</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>161.48</v>
+        <v>160.79</v>
       </c>
       <c r="K66" t="n">
-        <v>-114.87</v>
+        <v>-114.38</v>
       </c>
       <c r="L66" t="n">
-        <v>198.16</v>
+        <v>197.32</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>-124.63</v>
+        <v>-121.04</v>
       </c>
       <c r="K67" t="n">
-        <v>48.2</v>
+        <v>46.82</v>
       </c>
       <c r="L67" t="n">
-        <v>133.62</v>
+        <v>129.78</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>43.91</v>
+        <v>44.24</v>
       </c>
       <c r="K68" t="n">
-        <v>-264.51</v>
+        <v>-266.46</v>
       </c>
       <c r="L68" t="n">
-        <v>268.13</v>
+        <v>270.11</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>85.95999999999999</v>
+        <v>86.28</v>
       </c>
       <c r="K69" t="n">
-        <v>120.99</v>
+        <v>121.45</v>
       </c>
       <c r="L69" t="n">
-        <v>148.42</v>
+        <v>148.98</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-14.78</v>
+        <v>-15</v>
       </c>
       <c r="K70" t="n">
-        <v>-151.43</v>
+        <v>-153.65</v>
       </c>
       <c r="L70" t="n">
-        <v>152.15</v>
+        <v>154.38</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>-49.76</v>
+        <v>-49.73</v>
       </c>
       <c r="K71" t="n">
-        <v>-376.32</v>
+        <v>-376.08</v>
       </c>
       <c r="L71" t="n">
-        <v>379.59</v>
+        <v>379.36</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>-261.71</v>
+        <v>-262.8</v>
       </c>
       <c r="K72" t="n">
-        <v>156.44</v>
+        <v>157.09</v>
       </c>
       <c r="L72" t="n">
-        <v>304.91</v>
+        <v>306.17</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-47.86</v>
+        <v>-49.19</v>
       </c>
       <c r="K73" t="n">
-        <v>-494.6</v>
+        <v>-508.34</v>
       </c>
       <c r="L73" t="n">
-        <v>496.91</v>
+        <v>510.72</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>-34.91</v>
+        <v>-32.15</v>
       </c>
       <c r="K74" t="n">
-        <v>134.09</v>
+        <v>123.49</v>
       </c>
       <c r="L74" t="n">
-        <v>138.56</v>
+        <v>127.61</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>93.34999999999999</v>
+        <v>85.53</v>
       </c>
       <c r="K75" t="n">
-        <v>-80.73</v>
+        <v>-73.95999999999999</v>
       </c>
       <c r="L75" t="n">
-        <v>123.42</v>
+        <v>113.07</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>49.9</v>
+        <v>45.51</v>
       </c>
       <c r="K76" t="n">
-        <v>-68.23</v>
+        <v>-62.23</v>
       </c>
       <c r="L76" t="n">
-        <v>84.53</v>
+        <v>77.09</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-130.22</v>
+        <v>-122.44</v>
       </c>
       <c r="K77" t="n">
-        <v>154.96</v>
+        <v>145.71</v>
       </c>
       <c r="L77" t="n">
-        <v>202.41</v>
+        <v>190.33</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>83.31</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>51.37</v>
+        <v>49.02</v>
       </c>
       <c r="L78" t="n">
-        <v>97.87</v>
+        <v>93.39</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-107.72</v>
+        <v>-104.32</v>
       </c>
       <c r="K79" t="n">
-        <v>-106.3</v>
+        <v>-102.95</v>
       </c>
       <c r="L79" t="n">
-        <v>151.33</v>
+        <v>146.57</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>-165.03</v>
+        <v>-163.83</v>
       </c>
       <c r="K80" t="n">
-        <v>-39.11</v>
+        <v>-38.82</v>
       </c>
       <c r="L80" t="n">
-        <v>169.6</v>
+        <v>168.37</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>145.28</v>
+        <v>142.62</v>
       </c>
       <c r="K81" t="n">
-        <v>91.34999999999999</v>
+        <v>89.68000000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>171.61</v>
+        <v>168.47</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>27</v>
       </c>
       <c r="J82" t="n">
-        <v>277.2</v>
+        <v>269.67</v>
       </c>
       <c r="K82" t="n">
-        <v>-24.48</v>
+        <v>-23.81</v>
       </c>
       <c r="L82" t="n">
-        <v>278.28</v>
+        <v>270.72</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>28</v>
       </c>
       <c r="J83" t="n">
-        <v>136.7</v>
+        <v>135.13</v>
       </c>
       <c r="K83" t="n">
-        <v>94.23999999999999</v>
+        <v>93.16</v>
       </c>
       <c r="L83" t="n">
-        <v>166.03</v>
+        <v>164.13</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>24</v>
       </c>
       <c r="J84" t="n">
-        <v>-137.34</v>
+        <v>-139.17</v>
       </c>
       <c r="K84" t="n">
-        <v>-142.03</v>
+        <v>-143.93</v>
       </c>
       <c r="L84" t="n">
-        <v>197.57</v>
+        <v>200.21</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>51.45</v>
+        <v>52.12</v>
       </c>
       <c r="K85" t="n">
-        <v>-252.11</v>
+        <v>-255.39</v>
       </c>
       <c r="L85" t="n">
-        <v>257.31</v>
+        <v>260.65</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>388.53</v>
+        <v>403.22</v>
       </c>
       <c r="K86" t="n">
-        <v>58.52</v>
+        <v>60.73</v>
       </c>
       <c r="L86" t="n">
-        <v>392.91</v>
+        <v>407.77</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>28</v>
       </c>
       <c r="J87" t="n">
-        <v>223.99</v>
+        <v>223.68</v>
       </c>
       <c r="K87" t="n">
-        <v>153.62</v>
+        <v>153.41</v>
       </c>
       <c r="L87" t="n">
-        <v>271.61</v>
+        <v>271.23</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>171.8</v>
+        <v>177.94</v>
       </c>
       <c r="K88" t="n">
-        <v>344.39</v>
+        <v>356.71</v>
       </c>
       <c r="L88" t="n">
-        <v>384.86</v>
+        <v>398.63</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-08-21.xlsx
+++ b/output/2024-08-21.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>40.14</v>
+        <v>24.58</v>
       </c>
       <c r="K14" t="n">
-        <v>-87.28</v>
+        <v>-53.44</v>
       </c>
       <c r="L14" t="n">
-        <v>96.06</v>
+        <v>58.82</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>98.56999999999999</v>
+        <v>58.47</v>
       </c>
       <c r="K15" t="n">
-        <v>149.44</v>
+        <v>88.65000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>179.02</v>
+        <v>106.2</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>-66.37</v>
+        <v>-39.15</v>
       </c>
       <c r="K16" t="n">
-        <v>29.57</v>
+        <v>17.45</v>
       </c>
       <c r="L16" t="n">
-        <v>72.66</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-29.77</v>
+        <v>-5.35</v>
       </c>
       <c r="K17" t="n">
-        <v>30.33</v>
+        <v>5.46</v>
       </c>
       <c r="L17" t="n">
-        <v>42.5</v>
+        <v>7.64</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-64.56999999999999</v>
+        <v>-33.12</v>
       </c>
       <c r="K18" t="n">
-        <v>49.33</v>
+        <v>25.3</v>
       </c>
       <c r="L18" t="n">
-        <v>81.26000000000001</v>
+        <v>41.68</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-104.86</v>
+        <v>-61.5</v>
       </c>
       <c r="K19" t="n">
-        <v>-120.72</v>
+        <v>-70.8</v>
       </c>
       <c r="L19" t="n">
-        <v>159.9</v>
+        <v>93.78</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-161.06</v>
+        <v>-92.84999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>21.24</v>
+        <v>12.24</v>
       </c>
       <c r="L20" t="n">
-        <v>162.46</v>
+        <v>93.66</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>28</v>
       </c>
       <c r="J21" t="n">
-        <v>-34.04</v>
+        <v>-19.63</v>
       </c>
       <c r="K21" t="n">
-        <v>-82.91</v>
+        <v>-47.8</v>
       </c>
       <c r="L21" t="n">
-        <v>89.63</v>
+        <v>51.67</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>-41.51</v>
+        <v>-23.22</v>
       </c>
       <c r="K22" t="n">
-        <v>236.98</v>
+        <v>132.55</v>
       </c>
       <c r="L22" t="n">
-        <v>240.59</v>
+        <v>134.57</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>103.91</v>
+        <v>66.52</v>
       </c>
       <c r="K23" t="n">
-        <v>149.97</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>182.45</v>
+        <v>116.8</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>-104.38</v>
+        <v>-65.45999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>155.84</v>
+        <v>97.72</v>
       </c>
       <c r="L24" t="n">
-        <v>187.57</v>
+        <v>117.62</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>77.39</v>
+        <v>49.45</v>
       </c>
       <c r="K25" t="n">
-        <v>115.99</v>
+        <v>74.12</v>
       </c>
       <c r="L25" t="n">
-        <v>139.44</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>211.57</v>
+        <v>131.14</v>
       </c>
       <c r="K26" t="n">
-        <v>95.37</v>
+        <v>59.11</v>
       </c>
       <c r="L26" t="n">
-        <v>232.07</v>
+        <v>143.84</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-308.63</v>
+        <v>-190.94</v>
       </c>
       <c r="K27" t="n">
-        <v>-228.54</v>
+        <v>-141.39</v>
       </c>
       <c r="L27" t="n">
-        <v>384.03</v>
+        <v>237.59</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-216.58</v>
+        <v>-130.14</v>
       </c>
       <c r="K28" t="n">
-        <v>285.53</v>
+        <v>171.58</v>
       </c>
       <c r="L28" t="n">
-        <v>358.38</v>
+        <v>215.35</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-11.66</v>
+        <v>-2.49</v>
       </c>
       <c r="K29" t="n">
-        <v>-52.65</v>
+        <v>-11.25</v>
       </c>
       <c r="L29" t="n">
-        <v>53.92</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>8.83</v>
+        <v>4.65</v>
       </c>
       <c r="K30" t="n">
-        <v>-84.20999999999999</v>
+        <v>-44.33</v>
       </c>
       <c r="L30" t="n">
-        <v>84.67</v>
+        <v>44.58</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>25.48</v>
+        <v>14.92</v>
       </c>
       <c r="K31" t="n">
-        <v>120.05</v>
+        <v>70.31</v>
       </c>
       <c r="L31" t="n">
-        <v>122.72</v>
+        <v>71.87</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>55.81</v>
+        <v>32.6</v>
       </c>
       <c r="K32" t="n">
-        <v>64.44</v>
+        <v>37.64</v>
       </c>
       <c r="L32" t="n">
-        <v>85.25</v>
+        <v>49.79</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>31.02</v>
+        <v>17.87</v>
       </c>
       <c r="K33" t="n">
-        <v>101.52</v>
+        <v>58.48</v>
       </c>
       <c r="L33" t="n">
-        <v>106.15</v>
+        <v>61.15</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>30.25</v>
+        <v>16.76</v>
       </c>
       <c r="K34" t="n">
-        <v>-60.27</v>
+        <v>-33.4</v>
       </c>
       <c r="L34" t="n">
-        <v>67.43000000000001</v>
+        <v>37.36</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>135.77</v>
+        <v>70.83</v>
       </c>
       <c r="K35" t="n">
-        <v>18.9</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>137.07</v>
+        <v>71.51000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-110.07</v>
+        <v>-59.2</v>
       </c>
       <c r="K36" t="n">
-        <v>228.46</v>
+        <v>122.88</v>
       </c>
       <c r="L36" t="n">
-        <v>253.6</v>
+        <v>136.4</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>42.39</v>
+        <v>21.8</v>
       </c>
       <c r="K37" t="n">
-        <v>278.13</v>
+        <v>143.02</v>
       </c>
       <c r="L37" t="n">
-        <v>281.34</v>
+        <v>144.68</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>-48.53</v>
+        <v>-28.78</v>
       </c>
       <c r="K38" t="n">
-        <v>119.92</v>
+        <v>71.13</v>
       </c>
       <c r="L38" t="n">
-        <v>129.37</v>
+        <v>76.73</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>114.4</v>
+        <v>70.69</v>
       </c>
       <c r="K39" t="n">
-        <v>200.86</v>
+        <v>124.11</v>
       </c>
       <c r="L39" t="n">
-        <v>231.15</v>
+        <v>142.83</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>30.26</v>
+        <v>18.16</v>
       </c>
       <c r="K40" t="n">
-        <v>147.73</v>
+        <v>88.65000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>150.8</v>
+        <v>90.48999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>-13.68</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>246.4</v>
+        <v>149.13</v>
       </c>
       <c r="L41" t="n">
-        <v>246.78</v>
+        <v>149.36</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>-360.19</v>
+        <v>-211.57</v>
       </c>
       <c r="K42" t="n">
-        <v>138.32</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>385.83</v>
+        <v>226.63</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-46.8</v>
+        <v>-27.21</v>
       </c>
       <c r="K43" t="n">
-        <v>369.79</v>
+        <v>214.99</v>
       </c>
       <c r="L43" t="n">
-        <v>372.74</v>
+        <v>216.7</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>31.71</v>
+        <v>17.46</v>
       </c>
       <c r="K44" t="n">
-        <v>-116</v>
+        <v>-63.88</v>
       </c>
       <c r="L44" t="n">
-        <v>120.26</v>
+        <v>66.23</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>17.02</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>146.91</v>
+        <v>83.88</v>
       </c>
       <c r="L45" t="n">
-        <v>147.9</v>
+        <v>84.44</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>27</v>
       </c>
       <c r="J46" t="n">
-        <v>30.03</v>
+        <v>16.8</v>
       </c>
       <c r="K46" t="n">
-        <v>-107.72</v>
+        <v>-60.27</v>
       </c>
       <c r="L46" t="n">
-        <v>111.82</v>
+        <v>62.57</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-35.92</v>
+        <v>-20.5</v>
       </c>
       <c r="K47" t="n">
-        <v>-71.70999999999999</v>
+        <v>-40.92</v>
       </c>
       <c r="L47" t="n">
-        <v>80.20999999999999</v>
+        <v>45.77</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>29.17</v>
+        <v>16.52</v>
       </c>
       <c r="K48" t="n">
-        <v>131.47</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>134.67</v>
+        <v>76.27</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>133</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>-71.09</v>
+        <v>-38.58</v>
       </c>
       <c r="L49" t="n">
-        <v>150.81</v>
+        <v>81.84999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>25.22</v>
+        <v>13.37</v>
       </c>
       <c r="K50" t="n">
-        <v>259.08</v>
+        <v>137.35</v>
       </c>
       <c r="L50" t="n">
-        <v>260.31</v>
+        <v>138</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-4.1</v>
+        <v>-2.25</v>
       </c>
       <c r="K51" t="n">
-        <v>132.1</v>
+        <v>72.59</v>
       </c>
       <c r="L51" t="n">
-        <v>132.16</v>
+        <v>72.62</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-128.62</v>
+        <v>-67.09999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>-31.7</v>
+        <v>-16.54</v>
       </c>
       <c r="L52" t="n">
-        <v>132.47</v>
+        <v>69.11</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>277.02</v>
+        <v>175.49</v>
       </c>
       <c r="K53" t="n">
-        <v>-131.23</v>
+        <v>-83.13</v>
       </c>
       <c r="L53" t="n">
-        <v>306.53</v>
+        <v>194.18</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-73.09999999999999</v>
+        <v>-46.23</v>
       </c>
       <c r="K54" t="n">
-        <v>240.74</v>
+        <v>152.25</v>
       </c>
       <c r="L54" t="n">
-        <v>251.59</v>
+        <v>159.11</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>36.67</v>
+        <v>21.3</v>
       </c>
       <c r="K55" t="n">
-        <v>267.2</v>
+        <v>155.22</v>
       </c>
       <c r="L55" t="n">
-        <v>269.71</v>
+        <v>156.67</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>189.67</v>
+        <v>118</v>
       </c>
       <c r="K56" t="n">
-        <v>16.93</v>
+        <v>10.54</v>
       </c>
       <c r="L56" t="n">
-        <v>190.42</v>
+        <v>118.47</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>248.49</v>
+        <v>137.32</v>
       </c>
       <c r="K57" t="n">
-        <v>48.99</v>
+        <v>27.07</v>
       </c>
       <c r="L57" t="n">
-        <v>253.27</v>
+        <v>139.96</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>415.21</v>
+        <v>248.61</v>
       </c>
       <c r="K58" t="n">
-        <v>-198.93</v>
+        <v>-119.11</v>
       </c>
       <c r="L58" t="n">
-        <v>460.4</v>
+        <v>275.68</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>89.34</v>
+        <v>50.06</v>
       </c>
       <c r="K59" t="n">
-        <v>57.57</v>
+        <v>32.26</v>
       </c>
       <c r="L59" t="n">
-        <v>106.28</v>
+        <v>59.55</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>68.67</v>
+        <v>39.21</v>
       </c>
       <c r="K60" t="n">
-        <v>26.67</v>
+        <v>15.23</v>
       </c>
       <c r="L60" t="n">
-        <v>73.67</v>
+        <v>42.06</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>114.23</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>-64.25</v>
+        <v>-36.68</v>
       </c>
       <c r="L61" t="n">
-        <v>131.06</v>
+        <v>74.81999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>-166.78</v>
+        <v>-96.27</v>
       </c>
       <c r="K62" t="n">
-        <v>-8.91</v>
+        <v>-5.15</v>
       </c>
       <c r="L62" t="n">
-        <v>167.02</v>
+        <v>96.41</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>60.66</v>
+        <v>35.22</v>
       </c>
       <c r="K63" t="n">
-        <v>-39.44</v>
+        <v>-22.9</v>
       </c>
       <c r="L63" t="n">
-        <v>72.36</v>
+        <v>42.02</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-20.31</v>
+        <v>-10.55</v>
       </c>
       <c r="K64" t="n">
-        <v>-91.31999999999999</v>
+        <v>-47.45</v>
       </c>
       <c r="L64" t="n">
-        <v>93.55</v>
+        <v>48.61</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-83.38</v>
+        <v>-46.22</v>
       </c>
       <c r="K65" t="n">
-        <v>-111.87</v>
+        <v>-62.01</v>
       </c>
       <c r="L65" t="n">
-        <v>139.53</v>
+        <v>77.34999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>160.79</v>
+        <v>96.7</v>
       </c>
       <c r="K66" t="n">
-        <v>-114.38</v>
+        <v>-68.78</v>
       </c>
       <c r="L66" t="n">
-        <v>197.32</v>
+        <v>118.66</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>-121.04</v>
+        <v>-68.17</v>
       </c>
       <c r="K67" t="n">
-        <v>46.82</v>
+        <v>26.37</v>
       </c>
       <c r="L67" t="n">
-        <v>129.78</v>
+        <v>73.09</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>44.24</v>
+        <v>25.98</v>
       </c>
       <c r="K68" t="n">
-        <v>-266.46</v>
+        <v>-156.49</v>
       </c>
       <c r="L68" t="n">
-        <v>270.11</v>
+        <v>158.63</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>86.28</v>
+        <v>52.56</v>
       </c>
       <c r="K69" t="n">
-        <v>121.45</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="L69" t="n">
-        <v>148.98</v>
+        <v>90.76000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-15</v>
+        <v>-9.85</v>
       </c>
       <c r="K70" t="n">
-        <v>-153.65</v>
+        <v>-100.91</v>
       </c>
       <c r="L70" t="n">
-        <v>154.38</v>
+        <v>101.39</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>-49.73</v>
+        <v>-28.18</v>
       </c>
       <c r="K71" t="n">
-        <v>-376.08</v>
+        <v>-213.14</v>
       </c>
       <c r="L71" t="n">
-        <v>379.36</v>
+        <v>214.99</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>-262.8</v>
+        <v>-154.89</v>
       </c>
       <c r="K72" t="n">
-        <v>157.09</v>
+        <v>92.59</v>
       </c>
       <c r="L72" t="n">
-        <v>306.17</v>
+        <v>180.46</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-49.19</v>
+        <v>-26.32</v>
       </c>
       <c r="K73" t="n">
-        <v>-508.34</v>
+        <v>-272.04</v>
       </c>
       <c r="L73" t="n">
-        <v>510.72</v>
+        <v>273.31</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>-32.15</v>
+        <v>-17.96</v>
       </c>
       <c r="K74" t="n">
-        <v>123.49</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="L74" t="n">
-        <v>127.61</v>
+        <v>71.29000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>85.53</v>
+        <v>51.42</v>
       </c>
       <c r="K75" t="n">
-        <v>-73.95999999999999</v>
+        <v>-44.47</v>
       </c>
       <c r="L75" t="n">
-        <v>113.07</v>
+        <v>67.98</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>45.51</v>
+        <v>26.33</v>
       </c>
       <c r="K76" t="n">
-        <v>-62.23</v>
+        <v>-36</v>
       </c>
       <c r="L76" t="n">
-        <v>77.09</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-122.44</v>
+        <v>-65.05</v>
       </c>
       <c r="K77" t="n">
-        <v>145.71</v>
+        <v>77.42</v>
       </c>
       <c r="L77" t="n">
-        <v>190.33</v>
+        <v>101.12</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>79.48999999999999</v>
+        <v>45.98</v>
       </c>
       <c r="K78" t="n">
-        <v>49.02</v>
+        <v>28.35</v>
       </c>
       <c r="L78" t="n">
-        <v>93.39</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-104.32</v>
+        <v>-53.51</v>
       </c>
       <c r="K79" t="n">
-        <v>-102.95</v>
+        <v>-52.8</v>
       </c>
       <c r="L79" t="n">
-        <v>146.57</v>
+        <v>75.17</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>-163.83</v>
+        <v>-90.02</v>
       </c>
       <c r="K80" t="n">
-        <v>-38.82</v>
+        <v>-21.33</v>
       </c>
       <c r="L80" t="n">
-        <v>168.37</v>
+        <v>92.52</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>142.62</v>
+        <v>77.69</v>
       </c>
       <c r="K81" t="n">
-        <v>89.68000000000001</v>
+        <v>48.85</v>
       </c>
       <c r="L81" t="n">
-        <v>168.47</v>
+        <v>91.77</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>27</v>
       </c>
       <c r="J82" t="n">
-        <v>269.67</v>
+        <v>136.08</v>
       </c>
       <c r="K82" t="n">
-        <v>-23.81</v>
+        <v>-12.02</v>
       </c>
       <c r="L82" t="n">
-        <v>270.72</v>
+        <v>136.61</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>28</v>
       </c>
       <c r="J83" t="n">
-        <v>135.13</v>
+        <v>71.11</v>
       </c>
       <c r="K83" t="n">
-        <v>93.16</v>
+        <v>49.02</v>
       </c>
       <c r="L83" t="n">
-        <v>164.13</v>
+        <v>86.37</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>24</v>
       </c>
       <c r="J84" t="n">
-        <v>-139.17</v>
+        <v>-81.28</v>
       </c>
       <c r="K84" t="n">
-        <v>-143.93</v>
+        <v>-84.06</v>
       </c>
       <c r="L84" t="n">
-        <v>200.21</v>
+        <v>116.93</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>52.12</v>
+        <v>30.56</v>
       </c>
       <c r="K85" t="n">
-        <v>-255.39</v>
+        <v>-149.78</v>
       </c>
       <c r="L85" t="n">
-        <v>260.65</v>
+        <v>152.87</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>403.22</v>
+        <v>228.24</v>
       </c>
       <c r="K86" t="n">
-        <v>60.73</v>
+        <v>34.38</v>
       </c>
       <c r="L86" t="n">
-        <v>407.77</v>
+        <v>230.81</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>28</v>
       </c>
       <c r="J87" t="n">
-        <v>223.68</v>
+        <v>132.3</v>
       </c>
       <c r="K87" t="n">
-        <v>153.41</v>
+        <v>90.73</v>
       </c>
       <c r="L87" t="n">
-        <v>271.23</v>
+        <v>160.42</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>177.94</v>
+        <v>106.93</v>
       </c>
       <c r="K88" t="n">
-        <v>356.71</v>
+        <v>214.34</v>
       </c>
       <c r="L88" t="n">
-        <v>398.63</v>
+        <v>239.53</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-08-21.xlsx
+++ b/output/2024-08-21.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>24.58</v>
+        <v>24.38</v>
       </c>
       <c r="K14" t="n">
-        <v>-53.44</v>
+        <v>-53.02</v>
       </c>
       <c r="L14" t="n">
-        <v>58.82</v>
+        <v>58.35</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>58.47</v>
+        <v>54.97</v>
       </c>
       <c r="K15" t="n">
-        <v>88.65000000000001</v>
+        <v>83.34</v>
       </c>
       <c r="L15" t="n">
-        <v>106.2</v>
+        <v>99.84</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>-39.15</v>
+        <v>-40.08</v>
       </c>
       <c r="K16" t="n">
-        <v>17.45</v>
+        <v>17.86</v>
       </c>
       <c r="L16" t="n">
-        <v>42.86</v>
+        <v>43.88</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-5.35</v>
+        <v>-5.27</v>
       </c>
       <c r="K17" t="n">
-        <v>5.46</v>
+        <v>5.37</v>
       </c>
       <c r="L17" t="n">
-        <v>7.64</v>
+        <v>7.52</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-33.12</v>
+        <v>-35.88</v>
       </c>
       <c r="K18" t="n">
-        <v>25.3</v>
+        <v>27.41</v>
       </c>
       <c r="L18" t="n">
-        <v>41.68</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-61.5</v>
+        <v>-59.38</v>
       </c>
       <c r="K19" t="n">
-        <v>-70.8</v>
+        <v>-68.36</v>
       </c>
       <c r="L19" t="n">
-        <v>93.78</v>
+        <v>90.55</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-92.84999999999999</v>
+        <v>-93.56999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>12.24</v>
+        <v>12.34</v>
       </c>
       <c r="L20" t="n">
-        <v>93.66</v>
+        <v>94.38</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>28</v>
       </c>
       <c r="J21" t="n">
-        <v>-19.63</v>
+        <v>-21.33</v>
       </c>
       <c r="K21" t="n">
-        <v>-47.8</v>
+        <v>-51.95</v>
       </c>
       <c r="L21" t="n">
-        <v>51.67</v>
+        <v>56.16</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>-23.22</v>
+        <v>-22.36</v>
       </c>
       <c r="K22" t="n">
-        <v>132.55</v>
+        <v>127.63</v>
       </c>
       <c r="L22" t="n">
-        <v>134.57</v>
+        <v>129.58</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>66.52</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>96.01000000000001</v>
+        <v>96.09</v>
       </c>
       <c r="L23" t="n">
-        <v>116.8</v>
+        <v>116.9</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>-65.45999999999999</v>
+        <v>-66.13</v>
       </c>
       <c r="K24" t="n">
-        <v>97.72</v>
+        <v>98.73</v>
       </c>
       <c r="L24" t="n">
-        <v>117.62</v>
+        <v>118.84</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>49.45</v>
+        <v>50.53</v>
       </c>
       <c r="K25" t="n">
-        <v>74.12</v>
+        <v>75.73999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>89.09999999999999</v>
+        <v>91.05</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>131.14</v>
+        <v>134.88</v>
       </c>
       <c r="K26" t="n">
-        <v>59.11</v>
+        <v>60.8</v>
       </c>
       <c r="L26" t="n">
-        <v>143.84</v>
+        <v>147.95</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-190.94</v>
+        <v>-186.03</v>
       </c>
       <c r="K27" t="n">
-        <v>-141.39</v>
+        <v>-137.75</v>
       </c>
       <c r="L27" t="n">
-        <v>237.59</v>
+        <v>231.48</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-130.14</v>
+        <v>-127.25</v>
       </c>
       <c r="K28" t="n">
-        <v>171.58</v>
+        <v>167.76</v>
       </c>
       <c r="L28" t="n">
-        <v>215.35</v>
+        <v>210.56</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-2.49</v>
+        <v>-2.44</v>
       </c>
       <c r="K29" t="n">
-        <v>-11.25</v>
+        <v>-11.03</v>
       </c>
       <c r="L29" t="n">
-        <v>11.52</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>4.65</v>
+        <v>4.91</v>
       </c>
       <c r="K30" t="n">
-        <v>-44.33</v>
+        <v>-46.83</v>
       </c>
       <c r="L30" t="n">
-        <v>44.58</v>
+        <v>47.08</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>14.92</v>
+        <v>14.56</v>
       </c>
       <c r="K31" t="n">
-        <v>70.31</v>
+        <v>68.61</v>
       </c>
       <c r="L31" t="n">
-        <v>71.87</v>
+        <v>70.14</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>32.6</v>
+        <v>34.05</v>
       </c>
       <c r="K32" t="n">
-        <v>37.64</v>
+        <v>39.31</v>
       </c>
       <c r="L32" t="n">
-        <v>49.79</v>
+        <v>52.01</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>17.87</v>
+        <v>18.23</v>
       </c>
       <c r="K33" t="n">
-        <v>58.48</v>
+        <v>59.65</v>
       </c>
       <c r="L33" t="n">
-        <v>61.15</v>
+        <v>62.38</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>16.76</v>
+        <v>17.43</v>
       </c>
       <c r="K34" t="n">
-        <v>-33.4</v>
+        <v>-34.73</v>
       </c>
       <c r="L34" t="n">
-        <v>37.36</v>
+        <v>38.86</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>70.83</v>
+        <v>74.05</v>
       </c>
       <c r="K35" t="n">
-        <v>9.859999999999999</v>
+        <v>10.31</v>
       </c>
       <c r="L35" t="n">
-        <v>71.51000000000001</v>
+        <v>74.77</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-59.2</v>
+        <v>-57.06</v>
       </c>
       <c r="K36" t="n">
-        <v>122.88</v>
+        <v>118.42</v>
       </c>
       <c r="L36" t="n">
-        <v>136.4</v>
+        <v>131.45</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>21.8</v>
+        <v>20.93</v>
       </c>
       <c r="K37" t="n">
-        <v>143.02</v>
+        <v>137.33</v>
       </c>
       <c r="L37" t="n">
-        <v>144.68</v>
+        <v>138.92</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>-28.78</v>
+        <v>-31.25</v>
       </c>
       <c r="K38" t="n">
-        <v>71.13</v>
+        <v>77.23</v>
       </c>
       <c r="L38" t="n">
-        <v>76.73</v>
+        <v>83.31</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>70.69</v>
+        <v>69.92</v>
       </c>
       <c r="K39" t="n">
-        <v>124.11</v>
+        <v>122.76</v>
       </c>
       <c r="L39" t="n">
-        <v>142.83</v>
+        <v>141.27</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>18.16</v>
+        <v>19.4</v>
       </c>
       <c r="K40" t="n">
-        <v>88.65000000000001</v>
+        <v>94.72</v>
       </c>
       <c r="L40" t="n">
-        <v>90.48999999999999</v>
+        <v>96.68000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.279999999999999</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>149.13</v>
+        <v>152.56</v>
       </c>
       <c r="L41" t="n">
-        <v>149.36</v>
+        <v>152.8</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>-211.57</v>
+        <v>-206.59</v>
       </c>
       <c r="K42" t="n">
-        <v>81.23999999999999</v>
+        <v>79.33</v>
       </c>
       <c r="L42" t="n">
-        <v>226.63</v>
+        <v>221.3</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-27.21</v>
+        <v>-26.7</v>
       </c>
       <c r="K43" t="n">
-        <v>214.99</v>
+        <v>210.99</v>
       </c>
       <c r="L43" t="n">
-        <v>216.7</v>
+        <v>212.68</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>17.46</v>
+        <v>17.14</v>
       </c>
       <c r="K44" t="n">
-        <v>-63.88</v>
+        <v>-62.7</v>
       </c>
       <c r="L44" t="n">
-        <v>66.23</v>
+        <v>65</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>9.720000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>83.88</v>
+        <v>80.76000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>84.44</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>27</v>
       </c>
       <c r="J46" t="n">
-        <v>16.8</v>
+        <v>16.59</v>
       </c>
       <c r="K46" t="n">
-        <v>-60.27</v>
+        <v>-59.52</v>
       </c>
       <c r="L46" t="n">
-        <v>62.57</v>
+        <v>61.79</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-20.5</v>
+        <v>-21.73</v>
       </c>
       <c r="K47" t="n">
-        <v>-40.92</v>
+        <v>-43.38</v>
       </c>
       <c r="L47" t="n">
-        <v>45.77</v>
+        <v>48.52</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>16.52</v>
+        <v>16.35</v>
       </c>
       <c r="K48" t="n">
-        <v>74.45999999999999</v>
+        <v>73.69</v>
       </c>
       <c r="L48" t="n">
-        <v>76.27</v>
+        <v>75.48</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>72.18000000000001</v>
+        <v>70.88</v>
       </c>
       <c r="K49" t="n">
-        <v>-38.58</v>
+        <v>-37.89</v>
       </c>
       <c r="L49" t="n">
-        <v>81.84999999999999</v>
+        <v>80.37</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>13.37</v>
+        <v>12.85</v>
       </c>
       <c r="K50" t="n">
-        <v>137.35</v>
+        <v>131.98</v>
       </c>
       <c r="L50" t="n">
-        <v>138</v>
+        <v>132.6</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-2.25</v>
+        <v>-2.34</v>
       </c>
       <c r="K51" t="n">
-        <v>72.59</v>
+        <v>75.37</v>
       </c>
       <c r="L51" t="n">
-        <v>72.62</v>
+        <v>75.40000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-67.09999999999999</v>
+        <v>-70.78</v>
       </c>
       <c r="K52" t="n">
-        <v>-16.54</v>
+        <v>-17.45</v>
       </c>
       <c r="L52" t="n">
-        <v>69.11</v>
+        <v>72.89</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>175.49</v>
+        <v>168.18</v>
       </c>
       <c r="K53" t="n">
-        <v>-83.13</v>
+        <v>-79.67</v>
       </c>
       <c r="L53" t="n">
-        <v>194.18</v>
+        <v>186.1</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-46.23</v>
+        <v>-45.34</v>
       </c>
       <c r="K54" t="n">
-        <v>152.25</v>
+        <v>149.33</v>
       </c>
       <c r="L54" t="n">
-        <v>159.11</v>
+        <v>156.06</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>21.3</v>
+        <v>20.91</v>
       </c>
       <c r="K55" t="n">
-        <v>155.22</v>
+        <v>152.39</v>
       </c>
       <c r="L55" t="n">
-        <v>156.67</v>
+        <v>153.81</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>118</v>
+        <v>124.16</v>
       </c>
       <c r="K56" t="n">
-        <v>10.54</v>
+        <v>11.09</v>
       </c>
       <c r="L56" t="n">
-        <v>118.47</v>
+        <v>124.66</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>137.32</v>
+        <v>146.95</v>
       </c>
       <c r="K57" t="n">
-        <v>27.07</v>
+        <v>28.97</v>
       </c>
       <c r="L57" t="n">
-        <v>139.96</v>
+        <v>149.77</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>248.61</v>
+        <v>237.18</v>
       </c>
       <c r="K58" t="n">
-        <v>-119.11</v>
+        <v>-113.63</v>
       </c>
       <c r="L58" t="n">
-        <v>275.68</v>
+        <v>263</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>50.06</v>
+        <v>50.22</v>
       </c>
       <c r="K59" t="n">
-        <v>32.26</v>
+        <v>32.36</v>
       </c>
       <c r="L59" t="n">
-        <v>59.55</v>
+        <v>59.75</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>39.21</v>
+        <v>40.94</v>
       </c>
       <c r="K60" t="n">
-        <v>15.23</v>
+        <v>15.9</v>
       </c>
       <c r="L60" t="n">
-        <v>42.06</v>
+        <v>43.92</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>65.20999999999999</v>
+        <v>63.08</v>
       </c>
       <c r="K61" t="n">
-        <v>-36.68</v>
+        <v>-35.48</v>
       </c>
       <c r="L61" t="n">
-        <v>74.81999999999999</v>
+        <v>72.37</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>-96.27</v>
+        <v>-93.02</v>
       </c>
       <c r="K62" t="n">
-        <v>-5.15</v>
+        <v>-4.97</v>
       </c>
       <c r="L62" t="n">
-        <v>96.41</v>
+        <v>93.15000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>35.22</v>
+        <v>38.08</v>
       </c>
       <c r="K63" t="n">
-        <v>-22.9</v>
+        <v>-24.76</v>
       </c>
       <c r="L63" t="n">
-        <v>42.02</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-10.55</v>
+        <v>-11.13</v>
       </c>
       <c r="K64" t="n">
-        <v>-47.45</v>
+        <v>-50.06</v>
       </c>
       <c r="L64" t="n">
-        <v>48.61</v>
+        <v>51.28</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-46.22</v>
+        <v>-47.88</v>
       </c>
       <c r="K65" t="n">
-        <v>-62.01</v>
+        <v>-64.23</v>
       </c>
       <c r="L65" t="n">
-        <v>77.34999999999999</v>
+        <v>80.11</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>96.7</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="K66" t="n">
-        <v>-68.78</v>
+        <v>-66.97</v>
       </c>
       <c r="L66" t="n">
-        <v>118.66</v>
+        <v>115.54</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>-68.17</v>
+        <v>-70.02</v>
       </c>
       <c r="K67" t="n">
-        <v>26.37</v>
+        <v>27.08</v>
       </c>
       <c r="L67" t="n">
-        <v>73.09</v>
+        <v>75.08</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>25.98</v>
+        <v>25.56</v>
       </c>
       <c r="K68" t="n">
-        <v>-156.49</v>
+        <v>-153.93</v>
       </c>
       <c r="L68" t="n">
-        <v>158.63</v>
+        <v>156.04</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>52.56</v>
+        <v>55.32</v>
       </c>
       <c r="K69" t="n">
-        <v>73.98999999999999</v>
+        <v>77.86</v>
       </c>
       <c r="L69" t="n">
-        <v>90.76000000000001</v>
+        <v>95.51000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-9.85</v>
+        <v>-10.11</v>
       </c>
       <c r="K70" t="n">
-        <v>-100.91</v>
+        <v>-103.54</v>
       </c>
       <c r="L70" t="n">
-        <v>101.39</v>
+        <v>104.03</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>-28.18</v>
+        <v>-27.48</v>
       </c>
       <c r="K71" t="n">
-        <v>-213.14</v>
+        <v>-207.82</v>
       </c>
       <c r="L71" t="n">
-        <v>214.99</v>
+        <v>209.63</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>-154.89</v>
+        <v>-153.85</v>
       </c>
       <c r="K72" t="n">
-        <v>92.59</v>
+        <v>91.97</v>
       </c>
       <c r="L72" t="n">
-        <v>180.46</v>
+        <v>179.24</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-26.32</v>
+        <v>-27.34</v>
       </c>
       <c r="K73" t="n">
-        <v>-272.04</v>
+        <v>-282.51</v>
       </c>
       <c r="L73" t="n">
-        <v>273.31</v>
+        <v>283.83</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>-17.96</v>
+        <v>-17.67</v>
       </c>
       <c r="K74" t="n">
-        <v>68.98999999999999</v>
+        <v>67.86</v>
       </c>
       <c r="L74" t="n">
-        <v>71.29000000000001</v>
+        <v>70.12</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>51.42</v>
+        <v>50.09</v>
       </c>
       <c r="K75" t="n">
-        <v>-44.47</v>
+        <v>-43.32</v>
       </c>
       <c r="L75" t="n">
-        <v>67.98</v>
+        <v>66.22</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>26.33</v>
+        <v>27.24</v>
       </c>
       <c r="K76" t="n">
-        <v>-36</v>
+        <v>-37.25</v>
       </c>
       <c r="L76" t="n">
-        <v>44.6</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-65.05</v>
+        <v>-62.38</v>
       </c>
       <c r="K77" t="n">
-        <v>77.42</v>
+        <v>74.23</v>
       </c>
       <c r="L77" t="n">
-        <v>101.12</v>
+        <v>96.95999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>45.98</v>
+        <v>47.75</v>
       </c>
       <c r="K78" t="n">
-        <v>28.35</v>
+        <v>29.44</v>
       </c>
       <c r="L78" t="n">
-        <v>54.01</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-53.51</v>
+        <v>-53.38</v>
       </c>
       <c r="K79" t="n">
-        <v>-52.8</v>
+        <v>-52.67</v>
       </c>
       <c r="L79" t="n">
-        <v>75.17</v>
+        <v>74.98999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>-90.02</v>
+        <v>-91.17</v>
       </c>
       <c r="K80" t="n">
-        <v>-21.33</v>
+        <v>-21.6</v>
       </c>
       <c r="L80" t="n">
-        <v>92.52</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>77.69</v>
+        <v>78.38</v>
       </c>
       <c r="K81" t="n">
-        <v>48.85</v>
+        <v>49.28</v>
       </c>
       <c r="L81" t="n">
-        <v>91.77</v>
+        <v>92.59</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>27</v>
       </c>
       <c r="J82" t="n">
-        <v>136.08</v>
+        <v>131.43</v>
       </c>
       <c r="K82" t="n">
-        <v>-12.02</v>
+        <v>-11.61</v>
       </c>
       <c r="L82" t="n">
-        <v>136.61</v>
+        <v>131.94</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>28</v>
       </c>
       <c r="J83" t="n">
-        <v>71.11</v>
+        <v>76.59</v>
       </c>
       <c r="K83" t="n">
-        <v>49.02</v>
+        <v>52.8</v>
       </c>
       <c r="L83" t="n">
-        <v>86.37</v>
+        <v>93.03</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>24</v>
       </c>
       <c r="J84" t="n">
-        <v>-81.28</v>
+        <v>-83.68000000000001</v>
       </c>
       <c r="K84" t="n">
-        <v>-84.06</v>
+        <v>-86.54000000000001</v>
       </c>
       <c r="L84" t="n">
-        <v>116.93</v>
+        <v>120.38</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>30.56</v>
+        <v>30.41</v>
       </c>
       <c r="K85" t="n">
-        <v>-149.78</v>
+        <v>-149</v>
       </c>
       <c r="L85" t="n">
-        <v>152.87</v>
+        <v>152.07</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>228.24</v>
+        <v>225.18</v>
       </c>
       <c r="K86" t="n">
-        <v>34.38</v>
+        <v>33.92</v>
       </c>
       <c r="L86" t="n">
-        <v>230.81</v>
+        <v>227.72</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>28</v>
       </c>
       <c r="J87" t="n">
-        <v>132.3</v>
+        <v>133.63</v>
       </c>
       <c r="K87" t="n">
-        <v>90.73</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="L87" t="n">
-        <v>160.42</v>
+        <v>162.03</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>106.93</v>
+        <v>104.53</v>
       </c>
       <c r="K88" t="n">
-        <v>214.34</v>
+        <v>209.55</v>
       </c>
       <c r="L88" t="n">
-        <v>239.53</v>
+        <v>234.17</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-08-21.xlsx
+++ b/output/2024-08-21.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>24.38</v>
+        <v>24.15</v>
       </c>
       <c r="K14" t="n">
-        <v>-53.02</v>
+        <v>-52.52</v>
       </c>
       <c r="L14" t="n">
-        <v>58.35</v>
+        <v>57.81</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>54.97</v>
+        <v>50.97</v>
       </c>
       <c r="K15" t="n">
-        <v>83.34</v>
+        <v>77.28</v>
       </c>
       <c r="L15" t="n">
-        <v>99.84</v>
+        <v>92.56999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>-40.08</v>
+        <v>-41.14</v>
       </c>
       <c r="K16" t="n">
-        <v>17.86</v>
+        <v>18.33</v>
       </c>
       <c r="L16" t="n">
-        <v>43.88</v>
+        <v>45.04</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-5.27</v>
+        <v>-5.61</v>
       </c>
       <c r="K17" t="n">
-        <v>5.37</v>
+        <v>5.71</v>
       </c>
       <c r="L17" t="n">
-        <v>7.52</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-35.88</v>
+        <v>-39.29</v>
       </c>
       <c r="K18" t="n">
-        <v>27.41</v>
+        <v>30.01</v>
       </c>
       <c r="L18" t="n">
-        <v>45.15</v>
+        <v>49.44</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-59.38</v>
+        <v>-56.96</v>
       </c>
       <c r="K19" t="n">
-        <v>-68.36</v>
+        <v>-65.58</v>
       </c>
       <c r="L19" t="n">
-        <v>90.55</v>
+        <v>86.86</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-93.56999999999999</v>
+        <v>-94.40000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>12.34</v>
+        <v>12.45</v>
       </c>
       <c r="L20" t="n">
-        <v>94.38</v>
+        <v>95.22</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>28</v>
       </c>
       <c r="J21" t="n">
-        <v>-21.33</v>
+        <v>-23.28</v>
       </c>
       <c r="K21" t="n">
-        <v>-51.95</v>
+        <v>-56.7</v>
       </c>
       <c r="L21" t="n">
-        <v>56.16</v>
+        <v>61.29</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>-22.36</v>
+        <v>-21.37</v>
       </c>
       <c r="K22" t="n">
-        <v>127.63</v>
+        <v>122.02</v>
       </c>
       <c r="L22" t="n">
-        <v>129.58</v>
+        <v>123.87</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>66.56999999999999</v>
+        <v>66.64</v>
       </c>
       <c r="K23" t="n">
-        <v>96.09</v>
+        <v>96.19</v>
       </c>
       <c r="L23" t="n">
-        <v>116.9</v>
+        <v>117.02</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>-66.13</v>
+        <v>-66.90000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>98.73</v>
+        <v>99.89</v>
       </c>
       <c r="L24" t="n">
-        <v>118.84</v>
+        <v>120.22</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>50.53</v>
+        <v>55.53</v>
       </c>
       <c r="K25" t="n">
-        <v>75.73999999999999</v>
+        <v>83.23</v>
       </c>
       <c r="L25" t="n">
-        <v>91.05</v>
+        <v>100.06</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>134.88</v>
+        <v>139.16</v>
       </c>
       <c r="K26" t="n">
-        <v>60.8</v>
+        <v>62.73</v>
       </c>
       <c r="L26" t="n">
-        <v>147.95</v>
+        <v>152.64</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-186.03</v>
+        <v>-180.41</v>
       </c>
       <c r="K27" t="n">
-        <v>-137.75</v>
+        <v>-133.6</v>
       </c>
       <c r="L27" t="n">
-        <v>231.48</v>
+        <v>224.49</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-127.25</v>
+        <v>-123.93</v>
       </c>
       <c r="K28" t="n">
-        <v>167.76</v>
+        <v>163.39</v>
       </c>
       <c r="L28" t="n">
-        <v>210.56</v>
+        <v>205.08</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-2.44</v>
+        <v>-2.63</v>
       </c>
       <c r="K29" t="n">
-        <v>-11.03</v>
+        <v>-11.87</v>
       </c>
       <c r="L29" t="n">
-        <v>11.3</v>
+        <v>12.16</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>4.91</v>
+        <v>5.23</v>
       </c>
       <c r="K30" t="n">
-        <v>-46.83</v>
+        <v>-49.87</v>
       </c>
       <c r="L30" t="n">
-        <v>47.08</v>
+        <v>50.14</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>14.56</v>
+        <v>14.15</v>
       </c>
       <c r="K31" t="n">
-        <v>68.61</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>70.14</v>
+        <v>68.17</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>34.05</v>
+        <v>35.7</v>
       </c>
       <c r="K32" t="n">
-        <v>39.31</v>
+        <v>41.22</v>
       </c>
       <c r="L32" t="n">
-        <v>52.01</v>
+        <v>54.53</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>18.23</v>
+        <v>18.64</v>
       </c>
       <c r="K33" t="n">
-        <v>59.65</v>
+        <v>60.99</v>
       </c>
       <c r="L33" t="n">
-        <v>62.38</v>
+        <v>63.77</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>17.43</v>
+        <v>19.19</v>
       </c>
       <c r="K34" t="n">
-        <v>-34.73</v>
+        <v>-38.24</v>
       </c>
       <c r="L34" t="n">
-        <v>38.86</v>
+        <v>42.79</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>74.05</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>10.31</v>
+        <v>10.82</v>
       </c>
       <c r="L35" t="n">
-        <v>74.77</v>
+        <v>78.48999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-57.06</v>
+        <v>-54.6</v>
       </c>
       <c r="K36" t="n">
-        <v>118.42</v>
+        <v>113.33</v>
       </c>
       <c r="L36" t="n">
-        <v>131.45</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>20.93</v>
+        <v>19.95</v>
       </c>
       <c r="K37" t="n">
-        <v>137.33</v>
+        <v>130.9</v>
       </c>
       <c r="L37" t="n">
-        <v>138.92</v>
+        <v>132.41</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>-31.25</v>
+        <v>-34.07</v>
       </c>
       <c r="K38" t="n">
-        <v>77.23</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>83.31</v>
+        <v>90.84</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>69.92</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>122.76</v>
+        <v>121.21</v>
       </c>
       <c r="L39" t="n">
-        <v>141.27</v>
+        <v>139.5</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>19.4</v>
+        <v>20.82</v>
       </c>
       <c r="K40" t="n">
-        <v>94.72</v>
+        <v>101.65</v>
       </c>
       <c r="L40" t="n">
-        <v>96.68000000000001</v>
+        <v>103.76</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.470000000000001</v>
+        <v>-8.69</v>
       </c>
       <c r="K41" t="n">
-        <v>152.56</v>
+        <v>156.49</v>
       </c>
       <c r="L41" t="n">
-        <v>152.8</v>
+        <v>156.73</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>-206.59</v>
+        <v>-200.9</v>
       </c>
       <c r="K42" t="n">
-        <v>79.33</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>221.3</v>
+        <v>215.21</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-26.7</v>
+        <v>-26.12</v>
       </c>
       <c r="K43" t="n">
-        <v>210.99</v>
+        <v>206.43</v>
       </c>
       <c r="L43" t="n">
-        <v>212.68</v>
+        <v>208.08</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>17.14</v>
+        <v>16.77</v>
       </c>
       <c r="K44" t="n">
-        <v>-62.7</v>
+        <v>-61.35</v>
       </c>
       <c r="L44" t="n">
-        <v>65</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>9.359999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="K45" t="n">
-        <v>80.76000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="L45" t="n">
-        <v>81.3</v>
+        <v>77.70999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>27</v>
       </c>
       <c r="J46" t="n">
-        <v>16.59</v>
+        <v>16.35</v>
       </c>
       <c r="K46" t="n">
-        <v>-59.52</v>
+        <v>-58.67</v>
       </c>
       <c r="L46" t="n">
-        <v>61.79</v>
+        <v>60.91</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-21.73</v>
+        <v>-23.14</v>
       </c>
       <c r="K47" t="n">
-        <v>-43.38</v>
+        <v>-46.19</v>
       </c>
       <c r="L47" t="n">
-        <v>48.52</v>
+        <v>51.66</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>16.35</v>
+        <v>16.15</v>
       </c>
       <c r="K48" t="n">
-        <v>73.69</v>
+        <v>72.81</v>
       </c>
       <c r="L48" t="n">
-        <v>75.48</v>
+        <v>74.58</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>70.88</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>-37.89</v>
+        <v>-37.09</v>
       </c>
       <c r="L49" t="n">
-        <v>80.37</v>
+        <v>78.69</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>12.85</v>
+        <v>12.25</v>
       </c>
       <c r="K50" t="n">
-        <v>131.98</v>
+        <v>125.84</v>
       </c>
       <c r="L50" t="n">
-        <v>132.6</v>
+        <v>126.43</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-2.34</v>
+        <v>-2.44</v>
       </c>
       <c r="K51" t="n">
-        <v>75.37</v>
+        <v>78.55</v>
       </c>
       <c r="L51" t="n">
-        <v>75.40000000000001</v>
+        <v>78.58</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-70.78</v>
+        <v>-74.98</v>
       </c>
       <c r="K52" t="n">
-        <v>-17.45</v>
+        <v>-18.48</v>
       </c>
       <c r="L52" t="n">
-        <v>72.89</v>
+        <v>77.22</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>168.18</v>
+        <v>159.83</v>
       </c>
       <c r="K53" t="n">
-        <v>-79.67</v>
+        <v>-75.72</v>
       </c>
       <c r="L53" t="n">
-        <v>186.1</v>
+        <v>176.86</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-45.34</v>
+        <v>-44.33</v>
       </c>
       <c r="K54" t="n">
-        <v>149.33</v>
+        <v>145.99</v>
       </c>
       <c r="L54" t="n">
-        <v>156.06</v>
+        <v>152.57</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>20.91</v>
+        <v>20.47</v>
       </c>
       <c r="K55" t="n">
-        <v>152.39</v>
+        <v>149.15</v>
       </c>
       <c r="L55" t="n">
-        <v>153.81</v>
+        <v>150.55</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>124.16</v>
+        <v>131.2</v>
       </c>
       <c r="K56" t="n">
-        <v>11.09</v>
+        <v>11.71</v>
       </c>
       <c r="L56" t="n">
-        <v>124.66</v>
+        <v>131.73</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>146.95</v>
+        <v>154.27</v>
       </c>
       <c r="K57" t="n">
-        <v>28.97</v>
+        <v>30.41</v>
       </c>
       <c r="L57" t="n">
-        <v>149.77</v>
+        <v>157.24</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>237.18</v>
+        <v>224.12</v>
       </c>
       <c r="K58" t="n">
-        <v>-113.63</v>
+        <v>-107.38</v>
       </c>
       <c r="L58" t="n">
-        <v>263</v>
+        <v>248.51</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>50.22</v>
+        <v>50.41</v>
       </c>
       <c r="K59" t="n">
-        <v>32.36</v>
+        <v>32.48</v>
       </c>
       <c r="L59" t="n">
-        <v>59.75</v>
+        <v>59.97</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>40.94</v>
+        <v>42.93</v>
       </c>
       <c r="K60" t="n">
-        <v>15.9</v>
+        <v>16.67</v>
       </c>
       <c r="L60" t="n">
-        <v>43.92</v>
+        <v>46.05</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>63.08</v>
+        <v>60.63</v>
       </c>
       <c r="K61" t="n">
-        <v>-35.48</v>
+        <v>-34.1</v>
       </c>
       <c r="L61" t="n">
-        <v>72.37</v>
+        <v>69.56</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>-93.02</v>
+        <v>-89.3</v>
       </c>
       <c r="K62" t="n">
-        <v>-4.97</v>
+        <v>-4.77</v>
       </c>
       <c r="L62" t="n">
-        <v>93.15000000000001</v>
+        <v>89.43000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>38.08</v>
+        <v>41.33</v>
       </c>
       <c r="K63" t="n">
-        <v>-24.76</v>
+        <v>-26.88</v>
       </c>
       <c r="L63" t="n">
-        <v>45.42</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-11.13</v>
+        <v>-11.85</v>
       </c>
       <c r="K64" t="n">
-        <v>-50.06</v>
+        <v>-53.31</v>
       </c>
       <c r="L64" t="n">
-        <v>51.28</v>
+        <v>54.62</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-47.88</v>
+        <v>-49.76</v>
       </c>
       <c r="K65" t="n">
-        <v>-64.23</v>
+        <v>-66.76000000000001</v>
       </c>
       <c r="L65" t="n">
-        <v>80.11</v>
+        <v>83.27</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>94.15000000000001</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>-66.97</v>
+        <v>-64.90000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>115.54</v>
+        <v>111.97</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>-70.02</v>
+        <v>-72.14</v>
       </c>
       <c r="K67" t="n">
-        <v>27.08</v>
+        <v>27.9</v>
       </c>
       <c r="L67" t="n">
-        <v>75.08</v>
+        <v>77.34999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>25.56</v>
+        <v>25.07</v>
       </c>
       <c r="K68" t="n">
-        <v>-153.93</v>
+        <v>-151.01</v>
       </c>
       <c r="L68" t="n">
-        <v>156.04</v>
+        <v>153.08</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>55.32</v>
+        <v>58.46</v>
       </c>
       <c r="K69" t="n">
-        <v>77.86</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="L69" t="n">
-        <v>95.51000000000001</v>
+        <v>100.94</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-10.11</v>
+        <v>-10.4</v>
       </c>
       <c r="K70" t="n">
-        <v>-103.54</v>
+        <v>-106.55</v>
       </c>
       <c r="L70" t="n">
-        <v>104.03</v>
+        <v>107.06</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>-27.48</v>
+        <v>-26.66</v>
       </c>
       <c r="K71" t="n">
-        <v>-207.82</v>
+        <v>-201.6</v>
       </c>
       <c r="L71" t="n">
-        <v>209.63</v>
+        <v>203.36</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>-153.85</v>
+        <v>-152.66</v>
       </c>
       <c r="K72" t="n">
-        <v>91.97</v>
+        <v>91.25</v>
       </c>
       <c r="L72" t="n">
-        <v>179.24</v>
+        <v>177.85</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-27.34</v>
+        <v>-26.66</v>
       </c>
       <c r="K73" t="n">
-        <v>-282.51</v>
+        <v>-275.51</v>
       </c>
       <c r="L73" t="n">
-        <v>283.83</v>
+        <v>276.8</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>-17.67</v>
+        <v>-17.33</v>
       </c>
       <c r="K74" t="n">
-        <v>67.86</v>
+        <v>66.56</v>
       </c>
       <c r="L74" t="n">
-        <v>70.12</v>
+        <v>68.78</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>50.09</v>
+        <v>48.57</v>
       </c>
       <c r="K75" t="n">
-        <v>-43.32</v>
+        <v>-42</v>
       </c>
       <c r="L75" t="n">
-        <v>66.22</v>
+        <v>64.20999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>27.24</v>
+        <v>28.28</v>
       </c>
       <c r="K76" t="n">
-        <v>-37.25</v>
+        <v>-38.67</v>
       </c>
       <c r="L76" t="n">
-        <v>46.15</v>
+        <v>47.91</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-62.38</v>
+        <v>-59.48</v>
       </c>
       <c r="K77" t="n">
-        <v>74.23</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="L77" t="n">
-        <v>96.95999999999999</v>
+        <v>92.45999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>47.75</v>
+        <v>49.77</v>
       </c>
       <c r="K78" t="n">
-        <v>29.44</v>
+        <v>30.69</v>
       </c>
       <c r="L78" t="n">
-        <v>56.1</v>
+        <v>58.48</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-53.38</v>
+        <v>-53.65</v>
       </c>
       <c r="K79" t="n">
-        <v>-52.67</v>
+        <v>-52.95</v>
       </c>
       <c r="L79" t="n">
-        <v>74.98999999999999</v>
+        <v>75.38</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>-91.17</v>
+        <v>-92.48</v>
       </c>
       <c r="K80" t="n">
-        <v>-21.6</v>
+        <v>-21.91</v>
       </c>
       <c r="L80" t="n">
-        <v>93.7</v>
+        <v>95.04000000000001</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>78.38</v>
+        <v>79.16</v>
       </c>
       <c r="K81" t="n">
-        <v>49.28</v>
+        <v>49.78</v>
       </c>
       <c r="L81" t="n">
-        <v>92.59</v>
+        <v>93.51000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>27</v>
       </c>
       <c r="J82" t="n">
-        <v>131.43</v>
+        <v>126.71</v>
       </c>
       <c r="K82" t="n">
-        <v>-11.61</v>
+        <v>-11.19</v>
       </c>
       <c r="L82" t="n">
-        <v>131.94</v>
+        <v>127.21</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>28</v>
       </c>
       <c r="J83" t="n">
-        <v>76.59</v>
+        <v>82.61</v>
       </c>
       <c r="K83" t="n">
-        <v>52.8</v>
+        <v>56.95</v>
       </c>
       <c r="L83" t="n">
-        <v>93.03</v>
+        <v>100.33</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>24</v>
       </c>
       <c r="J84" t="n">
-        <v>-83.68000000000001</v>
+        <v>-86.41</v>
       </c>
       <c r="K84" t="n">
-        <v>-86.54000000000001</v>
+        <v>-89.37</v>
       </c>
       <c r="L84" t="n">
-        <v>120.38</v>
+        <v>124.31</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>30.41</v>
+        <v>30.22</v>
       </c>
       <c r="K85" t="n">
-        <v>-149</v>
+        <v>-148.11</v>
       </c>
       <c r="L85" t="n">
-        <v>152.07</v>
+        <v>151.16</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>225.18</v>
+        <v>221.26</v>
       </c>
       <c r="K86" t="n">
-        <v>33.92</v>
+        <v>33.32</v>
       </c>
       <c r="L86" t="n">
-        <v>227.72</v>
+        <v>223.75</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>28</v>
       </c>
       <c r="J87" t="n">
-        <v>133.63</v>
+        <v>135.15</v>
       </c>
       <c r="K87" t="n">
-        <v>91.65000000000001</v>
+        <v>92.69</v>
       </c>
       <c r="L87" t="n">
-        <v>162.03</v>
+        <v>163.88</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>104.53</v>
+        <v>101.8</v>
       </c>
       <c r="K88" t="n">
-        <v>209.55</v>
+        <v>204.07</v>
       </c>
       <c r="L88" t="n">
-        <v>234.17</v>
+        <v>228.05</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-08-21.xlsx
+++ b/output/2024-08-21.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.56</v>
+        <v>3.07</v>
       </c>
       <c r="F14" t="n">
-        <v>6.98</v>
+        <v>8.35</v>
       </c>
       <c r="G14" t="n">
-        <v>101</v>
+        <v>100.1</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J14" t="n">
-        <v>24.15</v>
+        <v>-7.7</v>
       </c>
       <c r="K14" t="n">
-        <v>-52.52</v>
+        <v>53.8</v>
       </c>
       <c r="L14" t="n">
-        <v>57.81</v>
+        <v>54.35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:00:53</t>
+          <t>06:00:46</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.72</v>
+        <v>2.41</v>
       </c>
       <c r="F15" t="n">
-        <v>7.06</v>
+        <v>2.71</v>
       </c>
       <c r="G15" t="n">
-        <v>102.8</v>
+        <v>93.7</v>
       </c>
       <c r="H15" t="n">
-        <v>8.1</v>
+        <v>1.7</v>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>50.97</v>
+        <v>-32.57</v>
       </c>
       <c r="K15" t="n">
-        <v>77.28</v>
+        <v>22.77</v>
       </c>
       <c r="L15" t="n">
-        <v>92.56999999999999</v>
+        <v>39.74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:03:07</t>
+          <t>06:01:56</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="F16" t="n">
-        <v>7.73</v>
+        <v>7.61</v>
       </c>
       <c r="G16" t="n">
-        <v>109.4</v>
+        <v>107.5</v>
       </c>
       <c r="H16" t="n">
-        <v>3.4</v>
+        <v>0.3</v>
       </c>
       <c r="I16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>-41.14</v>
+        <v>63.27</v>
       </c>
       <c r="K16" t="n">
-        <v>18.33</v>
+        <v>35.61</v>
       </c>
       <c r="L16" t="n">
-        <v>45.04</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:07:52</t>
+          <t>06:07:25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.02</v>
+        <v>2.55</v>
       </c>
       <c r="F17" t="n">
-        <v>7.6</v>
+        <v>6.67</v>
       </c>
       <c r="G17" t="n">
-        <v>86.2</v>
+        <v>101.4</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J17" t="n">
-        <v>-5.61</v>
+        <v>-62.13</v>
       </c>
       <c r="K17" t="n">
-        <v>5.71</v>
+        <v>20.65</v>
       </c>
       <c r="L17" t="n">
-        <v>8</v>
+        <v>65.47</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:08:49</t>
+          <t>06:08:52</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.48</v>
+        <v>2.12</v>
       </c>
       <c r="F18" t="n">
-        <v>8.25</v>
+        <v>7.6</v>
       </c>
       <c r="G18" t="n">
-        <v>112</v>
+        <v>83.8</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J18" t="n">
-        <v>-39.29</v>
+        <v>69.5</v>
       </c>
       <c r="K18" t="n">
-        <v>30.01</v>
+        <v>15.98</v>
       </c>
       <c r="L18" t="n">
-        <v>49.44</v>
+        <v>71.31</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:11:15</t>
+          <t>06:11:03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.8</v>
+        <v>2.18</v>
       </c>
       <c r="F19" t="n">
-        <v>7.73</v>
+        <v>5.59</v>
       </c>
       <c r="G19" t="n">
-        <v>79.7</v>
+        <v>98.2</v>
       </c>
       <c r="H19" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="I19" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J19" t="n">
-        <v>-56.96</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-65.58</v>
+        <v>22.77</v>
       </c>
       <c r="L19" t="n">
-        <v>86.86</v>
+        <v>76.48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:17:00</t>
+          <t>06:16:33</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.73</v>
+        <v>2.97</v>
       </c>
       <c r="F20" t="n">
-        <v>7.13</v>
+        <v>7.2</v>
       </c>
       <c r="G20" t="n">
-        <v>81.40000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="I20" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>-94.40000000000001</v>
+        <v>-28.73</v>
       </c>
       <c r="K20" t="n">
-        <v>12.45</v>
+        <v>105.05</v>
       </c>
       <c r="L20" t="n">
-        <v>95.22</v>
+        <v>108.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:19:35</t>
+          <t>06:17:18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.73</v>
+        <v>2.49</v>
       </c>
       <c r="F21" t="n">
-        <v>8.17</v>
+        <v>5.87</v>
       </c>
       <c r="G21" t="n">
-        <v>106.3</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>4.1</v>
+        <v>10.4</v>
       </c>
       <c r="I21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>-23.28</v>
+        <v>-73.73999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>-56.7</v>
+        <v>4.73</v>
       </c>
       <c r="L21" t="n">
-        <v>61.29</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:21:32</t>
+          <t>06:19:03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.86</v>
+        <v>2.65</v>
       </c>
       <c r="F22" t="n">
-        <v>7.89</v>
+        <v>5.97</v>
       </c>
       <c r="G22" t="n">
-        <v>90.59999999999999</v>
+        <v>104.8</v>
       </c>
       <c r="H22" t="n">
-        <v>8.6</v>
+        <v>4.1</v>
       </c>
       <c r="I22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-21.37</v>
+        <v>35.66</v>
       </c>
       <c r="K22" t="n">
-        <v>122.02</v>
+        <v>-66.28</v>
       </c>
       <c r="L22" t="n">
-        <v>123.87</v>
+        <v>75.26000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:26:17</t>
+          <t>06:24:04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="F23" t="n">
-        <v>7.35</v>
+        <v>3.99</v>
       </c>
       <c r="G23" t="n">
-        <v>95.8</v>
+        <v>93.2</v>
       </c>
       <c r="H23" t="n">
-        <v>1.9</v>
+        <v>5.3</v>
       </c>
       <c r="I23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>66.64</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>96.19</v>
+        <v>117.73</v>
       </c>
       <c r="L23" t="n">
-        <v>117.02</v>
+        <v>118.11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:28:40</t>
+          <t>06:26:07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.71</v>
+        <v>2.47</v>
       </c>
       <c r="F24" t="n">
-        <v>7.43</v>
+        <v>6.12</v>
       </c>
       <c r="G24" t="n">
-        <v>92.59999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J24" t="n">
-        <v>-66.90000000000001</v>
+        <v>111.46</v>
       </c>
       <c r="K24" t="n">
-        <v>99.89</v>
+        <v>-7.21</v>
       </c>
       <c r="L24" t="n">
-        <v>120.22</v>
+        <v>111.69</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:29:34</t>
+          <t>06:28:25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.6</v>
+        <v>3.14</v>
       </c>
       <c r="F25" t="n">
-        <v>7.91</v>
+        <v>5.21</v>
       </c>
       <c r="G25" t="n">
-        <v>89.2</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>6.7</v>
+        <v>3.3</v>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>55.53</v>
+        <v>-132.65</v>
       </c>
       <c r="K25" t="n">
-        <v>83.23</v>
+        <v>-147.22</v>
       </c>
       <c r="L25" t="n">
-        <v>100.06</v>
+        <v>198.16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:36:02</t>
+          <t>06:33:45</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.74</v>
+        <v>3.13</v>
       </c>
       <c r="F26" t="n">
-        <v>7.82</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>110.6</v>
+        <v>88.2</v>
       </c>
       <c r="H26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>139.16</v>
+        <v>75.27</v>
       </c>
       <c r="K26" t="n">
-        <v>62.73</v>
+        <v>139.31</v>
       </c>
       <c r="L26" t="n">
-        <v>152.64</v>
+        <v>158.34</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:38:20</t>
+          <t>06:34:52</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="F27" t="n">
-        <v>7.57</v>
+        <v>5.82</v>
       </c>
       <c r="G27" t="n">
-        <v>109.8</v>
+        <v>109.1</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="I27" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>-180.41</v>
+        <v>-140.86</v>
       </c>
       <c r="K27" t="n">
-        <v>-133.6</v>
+        <v>-92.84999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>224.49</v>
+        <v>168.71</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:40:28</t>
+          <t>06:36:22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="F28" t="n">
-        <v>7.72</v>
+        <v>7.97</v>
       </c>
       <c r="G28" t="n">
-        <v>96.5</v>
+        <v>95.7</v>
       </c>
       <c r="H28" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="I28" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>-123.93</v>
+        <v>-17.68</v>
       </c>
       <c r="K28" t="n">
-        <v>163.39</v>
+        <v>222.49</v>
       </c>
       <c r="L28" t="n">
-        <v>205.08</v>
+        <v>223.19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:49:39</t>
+          <t>06:45:14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="F29" t="n">
-        <v>7.73</v>
+        <v>4.9</v>
       </c>
       <c r="G29" t="n">
-        <v>99.3</v>
+        <v>96.8</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J29" t="n">
-        <v>-2.63</v>
+        <v>35.05</v>
       </c>
       <c r="K29" t="n">
-        <v>-11.87</v>
+        <v>43.15</v>
       </c>
       <c r="L29" t="n">
-        <v>12.16</v>
+        <v>55.59</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:51:38</t>
+          <t>06:46:46</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.38</v>
+        <v>3.05</v>
       </c>
       <c r="F30" t="n">
-        <v>8</v>
+        <v>6.12</v>
       </c>
       <c r="G30" t="n">
-        <v>108.2</v>
+        <v>110.6</v>
       </c>
       <c r="H30" t="n">
-        <v>8.300000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="I30" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J30" t="n">
-        <v>5.23</v>
+        <v>39.46</v>
       </c>
       <c r="K30" t="n">
-        <v>-49.87</v>
+        <v>-20.07</v>
       </c>
       <c r="L30" t="n">
-        <v>50.14</v>
+        <v>44.27</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:53:41</t>
+          <t>06:48:33</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.79</v>
+        <v>2.64</v>
       </c>
       <c r="F31" t="n">
-        <v>7.65</v>
+        <v>6.6</v>
       </c>
       <c r="G31" t="n">
-        <v>106</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="I31" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J31" t="n">
-        <v>14.15</v>
+        <v>-35.81</v>
       </c>
       <c r="K31" t="n">
-        <v>66.68000000000001</v>
+        <v>-40.18</v>
       </c>
       <c r="L31" t="n">
-        <v>68.17</v>
+        <v>53.83</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:58:39</t>
+          <t>06:53:12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="F32" t="n">
-        <v>8.06</v>
+        <v>6.29</v>
       </c>
       <c r="G32" t="n">
-        <v>92.59999999999999</v>
+        <v>103.9</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="I32" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J32" t="n">
-        <v>35.7</v>
+        <v>59.51</v>
       </c>
       <c r="K32" t="n">
-        <v>41.22</v>
+        <v>-53.56</v>
       </c>
       <c r="L32" t="n">
-        <v>54.53</v>
+        <v>80.06</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:00:18</t>
+          <t>06:54:38</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.89</v>
+        <v>2.5</v>
       </c>
       <c r="F33" t="n">
-        <v>7.79</v>
+        <v>6.57</v>
       </c>
       <c r="G33" t="n">
-        <v>96.3</v>
+        <v>94.2</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>18.64</v>
+        <v>-46.07</v>
       </c>
       <c r="K33" t="n">
-        <v>60.99</v>
+        <v>85.02</v>
       </c>
       <c r="L33" t="n">
-        <v>63.77</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:01:25</t>
+          <t>06:56:04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="F34" t="n">
-        <v>7.33</v>
+        <v>6.29</v>
       </c>
       <c r="G34" t="n">
-        <v>86.09999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>6.9</v>
+        <v>4</v>
       </c>
       <c r="I34" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>19.19</v>
+        <v>-6.26</v>
       </c>
       <c r="K34" t="n">
-        <v>-38.24</v>
+        <v>74.72</v>
       </c>
       <c r="L34" t="n">
-        <v>42.79</v>
+        <v>74.98</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:05:17</t>
+          <t>07:00:58</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.19</v>
+        <v>2.43</v>
       </c>
       <c r="F35" t="n">
-        <v>8.220000000000001</v>
+        <v>6.47</v>
       </c>
       <c r="G35" t="n">
-        <v>96.8</v>
+        <v>111.4</v>
       </c>
       <c r="H35" t="n">
-        <v>11.1</v>
+        <v>9.5</v>
       </c>
       <c r="I35" t="n">
         <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>77.73999999999999</v>
+        <v>37.45</v>
       </c>
       <c r="K35" t="n">
-        <v>10.82</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>78.48999999999999</v>
+        <v>85.76000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:07:23</t>
+          <t>07:03:18</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="F36" t="n">
-        <v>8.18</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>84.7</v>
+        <v>114.8</v>
       </c>
       <c r="H36" t="n">
-        <v>7.9</v>
+        <v>2.8</v>
       </c>
       <c r="I36" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J36" t="n">
-        <v>-54.6</v>
+        <v>-24.34</v>
       </c>
       <c r="K36" t="n">
-        <v>113.33</v>
+        <v>-81.16</v>
       </c>
       <c r="L36" t="n">
-        <v>125.8</v>
+        <v>84.73</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:08:39</t>
+          <t>07:05:05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.29</v>
+        <v>3.13</v>
       </c>
       <c r="F37" t="n">
-        <v>8.41</v>
+        <v>7.46</v>
       </c>
       <c r="G37" t="n">
-        <v>100.1</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="H37" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="I37" t="n">
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>19.95</v>
+        <v>105.58</v>
       </c>
       <c r="K37" t="n">
-        <v>130.9</v>
+        <v>-32.87</v>
       </c>
       <c r="L37" t="n">
-        <v>132.41</v>
+        <v>110.58</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:13:26</t>
+          <t>07:09:31</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.07</v>
+        <v>3.33</v>
       </c>
       <c r="F38" t="n">
-        <v>7.48</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>106.5</v>
+        <v>107.1</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I38" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>-34.07</v>
+        <v>71.86</v>
       </c>
       <c r="K38" t="n">
-        <v>84.20999999999999</v>
+        <v>125.62</v>
       </c>
       <c r="L38" t="n">
-        <v>90.84</v>
+        <v>144.72</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:15:10</t>
+          <t>07:11:01</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="F39" t="n">
-        <v>7.92</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>112.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1</v>
+        <v>3.7</v>
       </c>
       <c r="I39" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J39" t="n">
-        <v>69.04000000000001</v>
+        <v>21.71</v>
       </c>
       <c r="K39" t="n">
-        <v>121.21</v>
+        <v>132.39</v>
       </c>
       <c r="L39" t="n">
-        <v>139.5</v>
+        <v>134.16</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:16:33</t>
+          <t>07:11:55</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.99</v>
+        <v>2.65</v>
       </c>
       <c r="F40" t="n">
-        <v>7.69</v>
+        <v>7.2</v>
       </c>
       <c r="G40" t="n">
-        <v>116.5</v>
+        <v>103.8</v>
       </c>
       <c r="H40" t="n">
-        <v>6.1</v>
+        <v>0.9</v>
       </c>
       <c r="I40" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J40" t="n">
-        <v>20.82</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>101.65</v>
+        <v>115.75</v>
       </c>
       <c r="L40" t="n">
-        <v>103.76</v>
+        <v>142.98</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:21:29</t>
+          <t>07:17:01</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="F41" t="n">
-        <v>8.17</v>
+        <v>6.98</v>
       </c>
       <c r="G41" t="n">
-        <v>90.5</v>
+        <v>103.8</v>
       </c>
       <c r="H41" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="I41" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.69</v>
+        <v>134.53</v>
       </c>
       <c r="K41" t="n">
-        <v>156.49</v>
+        <v>133.76</v>
       </c>
       <c r="L41" t="n">
-        <v>156.73</v>
+        <v>189.71</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:23:12</t>
+          <t>07:18:51</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.04</v>
+        <v>3.43</v>
       </c>
       <c r="F42" t="n">
-        <v>7.14</v>
+        <v>8.41</v>
       </c>
       <c r="G42" t="n">
-        <v>98.2</v>
+        <v>105.3</v>
       </c>
       <c r="H42" t="n">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>-200.9</v>
+        <v>38.36</v>
       </c>
       <c r="K42" t="n">
-        <v>77.15000000000001</v>
+        <v>-206.5</v>
       </c>
       <c r="L42" t="n">
-        <v>215.21</v>
+        <v>210.03</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:25:01</t>
+          <t>07:20:12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="F43" t="n">
-        <v>7.76</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>84</v>
+        <v>81.3</v>
       </c>
       <c r="H43" t="n">
-        <v>5.6</v>
+        <v>2.1</v>
       </c>
       <c r="I43" t="n">
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-26.12</v>
+        <v>-50.32</v>
       </c>
       <c r="K43" t="n">
-        <v>206.43</v>
+        <v>-196.58</v>
       </c>
       <c r="L43" t="n">
-        <v>208.08</v>
+        <v>202.92</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:36:45</t>
+          <t>07:32:14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="F44" t="n">
-        <v>7.87</v>
+        <v>8.56</v>
       </c>
       <c r="G44" t="n">
-        <v>88.7</v>
+        <v>101.7</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>10.5</v>
       </c>
       <c r="I44" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>16.77</v>
+        <v>47.51</v>
       </c>
       <c r="K44" t="n">
-        <v>-61.35</v>
+        <v>-25.04</v>
       </c>
       <c r="L44" t="n">
-        <v>63.6</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:38:10</t>
+          <t>07:32:56</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.94</v>
+        <v>3.21</v>
       </c>
       <c r="F45" t="n">
-        <v>8.130000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G45" t="n">
-        <v>86.8</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="I45" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J45" t="n">
-        <v>8.94</v>
+        <v>-18.56</v>
       </c>
       <c r="K45" t="n">
-        <v>77.2</v>
+        <v>44.37</v>
       </c>
       <c r="L45" t="n">
-        <v>77.70999999999999</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:39:40</t>
+          <t>07:35:19</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="F46" t="n">
-        <v>8.31</v>
+        <v>7.24</v>
       </c>
       <c r="G46" t="n">
-        <v>94.3</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="H46" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>16.35</v>
+        <v>-30.8</v>
       </c>
       <c r="K46" t="n">
-        <v>-58.67</v>
+        <v>-37.48</v>
       </c>
       <c r="L46" t="n">
-        <v>60.91</v>
+        <v>48.52</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:42:35</t>
+          <t>07:39:44</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="F47" t="n">
-        <v>7.8</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>100.1</v>
+        <v>108.6</v>
       </c>
       <c r="H47" t="n">
-        <v>0.8</v>
+        <v>6.2</v>
       </c>
       <c r="I47" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-23.14</v>
+        <v>75.45</v>
       </c>
       <c r="K47" t="n">
-        <v>-46.19</v>
+        <v>-54.38</v>
       </c>
       <c r="L47" t="n">
-        <v>51.66</v>
+        <v>93.01000000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:45:20</t>
+          <t>07:41:49</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="F48" t="n">
-        <v>7.83</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>93</v>
+        <v>101.9</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>16.15</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>72.81</v>
+        <v>-63.35</v>
       </c>
       <c r="L48" t="n">
-        <v>74.58</v>
+        <v>107.45</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:47:09</t>
+          <t>07:43:27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.22</v>
+        <v>2.73</v>
       </c>
       <c r="F49" t="n">
-        <v>8.06</v>
+        <v>7.49</v>
       </c>
       <c r="G49" t="n">
-        <v>87.40000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>8</v>
+        <v>1.5</v>
       </c>
       <c r="I49" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>69.40000000000001</v>
+        <v>-7.57</v>
       </c>
       <c r="K49" t="n">
-        <v>-37.09</v>
+        <v>55.63</v>
       </c>
       <c r="L49" t="n">
-        <v>78.69</v>
+        <v>56.14</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:52:04</t>
+          <t>07:48:14</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.11</v>
+        <v>3.04</v>
       </c>
       <c r="F50" t="n">
-        <v>7.49</v>
+        <v>7.96</v>
       </c>
       <c r="G50" t="n">
-        <v>85.5</v>
+        <v>104</v>
       </c>
       <c r="H50" t="n">
-        <v>9.1</v>
+        <v>4.7</v>
       </c>
       <c r="I50" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>12.25</v>
+        <v>74.47</v>
       </c>
       <c r="K50" t="n">
-        <v>125.84</v>
+        <v>44.73</v>
       </c>
       <c r="L50" t="n">
-        <v>126.43</v>
+        <v>86.87</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:53:43</t>
+          <t>07:49:49</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.94</v>
+        <v>3.13</v>
       </c>
       <c r="F51" t="n">
-        <v>7.96</v>
+        <v>7.34</v>
       </c>
       <c r="G51" t="n">
-        <v>99.5</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="H51" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>-2.44</v>
+        <v>-67.12</v>
       </c>
       <c r="K51" t="n">
-        <v>78.55</v>
+        <v>51.86</v>
       </c>
       <c r="L51" t="n">
-        <v>78.58</v>
+        <v>84.81999999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:55:52</t>
+          <t>07:50:56</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.19</v>
+        <v>2.79</v>
       </c>
       <c r="F52" t="n">
-        <v>8.1</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G52" t="n">
-        <v>99.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J52" t="n">
-        <v>-74.98</v>
+        <v>48.68</v>
       </c>
       <c r="K52" t="n">
-        <v>-18.48</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>77.22</v>
+        <v>89.45</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:00:29</t>
+          <t>07:55:11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.65</v>
+        <v>3.46</v>
       </c>
       <c r="F53" t="n">
-        <v>7.55</v>
+        <v>8.34</v>
       </c>
       <c r="G53" t="n">
-        <v>100.1</v>
+        <v>103</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="I53" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>159.83</v>
+        <v>155.11</v>
       </c>
       <c r="K53" t="n">
-        <v>-75.72</v>
+        <v>75.81</v>
       </c>
       <c r="L53" t="n">
-        <v>176.86</v>
+        <v>172.64</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:02:08</t>
+          <t>07:56:18</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.66</v>
+        <v>3.01</v>
       </c>
       <c r="F54" t="n">
-        <v>8.6</v>
+        <v>8.24</v>
       </c>
       <c r="G54" t="n">
-        <v>101.9</v>
+        <v>87.8</v>
       </c>
       <c r="H54" t="n">
-        <v>2.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J54" t="n">
-        <v>-44.33</v>
+        <v>-67.22</v>
       </c>
       <c r="K54" t="n">
-        <v>145.99</v>
+        <v>-85.3</v>
       </c>
       <c r="L54" t="n">
-        <v>152.57</v>
+        <v>108.6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:04:37</t>
+          <t>07:58:16</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.22</v>
+        <v>2.96</v>
       </c>
       <c r="F55" t="n">
-        <v>7.88</v>
+        <v>8.68</v>
       </c>
       <c r="G55" t="n">
-        <v>103</v>
+        <v>101.6</v>
       </c>
       <c r="H55" t="n">
-        <v>6.2</v>
+        <v>2.8</v>
       </c>
       <c r="I55" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>20.47</v>
+        <v>141.87</v>
       </c>
       <c r="K55" t="n">
-        <v>149.15</v>
+        <v>-91.73999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>150.55</v>
+        <v>168.95</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:10:07</t>
+          <t>08:04:48</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.72</v>
+        <v>2.87</v>
       </c>
       <c r="F56" t="n">
-        <v>7.79</v>
+        <v>7.61</v>
       </c>
       <c r="G56" t="n">
-        <v>93.3</v>
+        <v>97.7</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="I56" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>131.2</v>
+        <v>227.41</v>
       </c>
       <c r="K56" t="n">
-        <v>11.71</v>
+        <v>77.31</v>
       </c>
       <c r="L56" t="n">
-        <v>131.73</v>
+        <v>240.19</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:11:38</t>
+          <t>08:06:07</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.71</v>
+        <v>3.06</v>
       </c>
       <c r="F57" t="n">
-        <v>7.94</v>
+        <v>7.12</v>
       </c>
       <c r="G57" t="n">
-        <v>93.09999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J57" t="n">
-        <v>154.27</v>
+        <v>19.29</v>
       </c>
       <c r="K57" t="n">
-        <v>30.41</v>
+        <v>-135.38</v>
       </c>
       <c r="L57" t="n">
-        <v>157.24</v>
+        <v>136.75</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:13:31</t>
+          <t>08:08:17</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="F58" t="n">
-        <v>8.08</v>
+        <v>5.63</v>
       </c>
       <c r="G58" t="n">
-        <v>99</v>
+        <v>101.8</v>
       </c>
       <c r="H58" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="I58" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J58" t="n">
-        <v>224.12</v>
+        <v>168.88</v>
       </c>
       <c r="K58" t="n">
-        <v>-107.38</v>
+        <v>-43.8</v>
       </c>
       <c r="L58" t="n">
-        <v>248.51</v>
+        <v>174.46</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:22:52</t>
+          <t>08:18:49</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.06</v>
+        <v>2.74</v>
       </c>
       <c r="F59" t="n">
-        <v>8.279999999999999</v>
+        <v>8.49</v>
       </c>
       <c r="G59" t="n">
-        <v>90.40000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="I59" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>50.41</v>
+        <v>-10.78</v>
       </c>
       <c r="K59" t="n">
-        <v>32.48</v>
+        <v>-64.94</v>
       </c>
       <c r="L59" t="n">
-        <v>59.97</v>
+        <v>65.81999999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:23:46</t>
+          <t>08:20:22</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.94</v>
+        <v>3.04</v>
       </c>
       <c r="F60" t="n">
-        <v>7.36</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G60" t="n">
-        <v>87.8</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H60" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="I60" t="n">
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>42.93</v>
+        <v>-51.9</v>
       </c>
       <c r="K60" t="n">
-        <v>16.67</v>
+        <v>-35.79</v>
       </c>
       <c r="L60" t="n">
-        <v>46.05</v>
+        <v>63.04</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:24:53</t>
+          <t>08:21:35</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.94</v>
+        <v>3.06</v>
       </c>
       <c r="F61" t="n">
-        <v>8.01</v>
+        <v>5.29</v>
       </c>
       <c r="G61" t="n">
-        <v>97.09999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="I61" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>60.63</v>
+        <v>-43.79</v>
       </c>
       <c r="K61" t="n">
-        <v>-34.1</v>
+        <v>-25.38</v>
       </c>
       <c r="L61" t="n">
-        <v>69.56</v>
+        <v>50.62</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:29:39</t>
+          <t>08:26:20</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="F62" t="n">
-        <v>8.039999999999999</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G62" t="n">
-        <v>81.40000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="H62" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="I62" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>-89.3</v>
+        <v>-7.63</v>
       </c>
       <c r="K62" t="n">
-        <v>-4.77</v>
+        <v>-64.70999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>89.43000000000001</v>
+        <v>65.16</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:31:53</t>
+          <t>08:28:28</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.85</v>
+        <v>3.13</v>
       </c>
       <c r="F63" t="n">
-        <v>7.91</v>
+        <v>7.48</v>
       </c>
       <c r="G63" t="n">
-        <v>110.7</v>
+        <v>91.3</v>
       </c>
       <c r="H63" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>41.33</v>
+        <v>-33.73</v>
       </c>
       <c r="K63" t="n">
-        <v>-26.88</v>
+        <v>-52.78</v>
       </c>
       <c r="L63" t="n">
-        <v>49.3</v>
+        <v>62.63</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:33:12</t>
+          <t>08:30:20</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.42</v>
+        <v>3.19</v>
       </c>
       <c r="F64" t="n">
-        <v>7</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G64" t="n">
-        <v>83.5</v>
+        <v>91.3</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I64" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>-11.85</v>
+        <v>-36.94</v>
       </c>
       <c r="K64" t="n">
-        <v>-53.31</v>
+        <v>-49.5</v>
       </c>
       <c r="L64" t="n">
-        <v>54.62</v>
+        <v>61.76</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:38:05</t>
+          <t>08:34:40</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="F65" t="n">
-        <v>7.54</v>
+        <v>8.75</v>
       </c>
       <c r="G65" t="n">
-        <v>103.1</v>
+        <v>97.7</v>
       </c>
       <c r="H65" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="I65" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>-49.76</v>
+        <v>-72.09</v>
       </c>
       <c r="K65" t="n">
-        <v>-66.76000000000001</v>
+        <v>-78.56</v>
       </c>
       <c r="L65" t="n">
-        <v>83.27</v>
+        <v>106.62</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:40:10</t>
+          <t>08:37:02</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.56</v>
+        <v>3.34</v>
       </c>
       <c r="F66" t="n">
-        <v>8.01</v>
+        <v>8.09</v>
       </c>
       <c r="G66" t="n">
-        <v>103</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H66" t="n">
-        <v>6.1</v>
+        <v>3.9</v>
       </c>
       <c r="I66" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J66" t="n">
-        <v>91.23999999999999</v>
+        <v>-72.89</v>
       </c>
       <c r="K66" t="n">
-        <v>-64.90000000000001</v>
+        <v>34.28</v>
       </c>
       <c r="L66" t="n">
-        <v>111.97</v>
+        <v>80.54000000000001</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:42:18</t>
+          <t>08:38:48</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.83</v>
+        <v>3.12</v>
       </c>
       <c r="F67" t="n">
-        <v>7.62</v>
+        <v>8.1</v>
       </c>
       <c r="G67" t="n">
-        <v>101</v>
+        <v>104.5</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I67" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>-72.14</v>
+        <v>-96.90000000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>27.9</v>
+        <v>-60.59</v>
       </c>
       <c r="L67" t="n">
-        <v>77.34999999999999</v>
+        <v>114.28</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:46:32</t>
+          <t>08:43:45</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.14</v>
+        <v>2.82</v>
       </c>
       <c r="F68" t="n">
-        <v>8.380000000000001</v>
+        <v>6.95</v>
       </c>
       <c r="G68" t="n">
-        <v>94.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="H68" t="n">
-        <v>0.5</v>
+        <v>8.1</v>
       </c>
       <c r="I68" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>25.07</v>
+        <v>79.73</v>
       </c>
       <c r="K68" t="n">
-        <v>-151.01</v>
+        <v>81.98</v>
       </c>
       <c r="L68" t="n">
-        <v>153.08</v>
+        <v>114.36</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:47:43</t>
+          <t>08:44:50</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.89</v>
+        <v>2.44</v>
       </c>
       <c r="F69" t="n">
-        <v>7.17</v>
+        <v>6.3</v>
       </c>
       <c r="G69" t="n">
-        <v>109.4</v>
+        <v>93.3</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>58.46</v>
+        <v>-79.79000000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>82.29000000000001</v>
+        <v>84.67</v>
       </c>
       <c r="L69" t="n">
-        <v>100.94</v>
+        <v>116.34</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:49:11</t>
+          <t>08:46:40</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.45</v>
+        <v>3.47</v>
       </c>
       <c r="F70" t="n">
-        <v>8.56</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G70" t="n">
-        <v>107.4</v>
+        <v>96.7</v>
       </c>
       <c r="H70" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>-10.4</v>
+        <v>-3.8</v>
       </c>
       <c r="K70" t="n">
-        <v>-106.55</v>
+        <v>-170.98</v>
       </c>
       <c r="L70" t="n">
-        <v>107.06</v>
+        <v>171.02</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:54:59</t>
+          <t>08:50:10</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="F71" t="n">
-        <v>7.8</v>
+        <v>5.37</v>
       </c>
       <c r="G71" t="n">
-        <v>89.90000000000001</v>
+        <v>111.5</v>
       </c>
       <c r="H71" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="I71" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J71" t="n">
-        <v>-26.66</v>
+        <v>131.43</v>
       </c>
       <c r="K71" t="n">
-        <v>-201.6</v>
+        <v>97.76000000000001</v>
       </c>
       <c r="L71" t="n">
-        <v>203.36</v>
+        <v>163.8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:56:27</t>
+          <t>08:51:47</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.02</v>
+        <v>3.23</v>
       </c>
       <c r="F72" t="n">
-        <v>8</v>
+        <v>7.23</v>
       </c>
       <c r="G72" t="n">
-        <v>98.5</v>
+        <v>97.3</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="I72" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-152.66</v>
+        <v>206.2</v>
       </c>
       <c r="K72" t="n">
-        <v>91.25</v>
+        <v>-55.15</v>
       </c>
       <c r="L72" t="n">
-        <v>177.85</v>
+        <v>213.44</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:58:05</t>
+          <t>08:53:04</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.4</v>
+        <v>2.63</v>
       </c>
       <c r="F73" t="n">
-        <v>7.58</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="G73" t="n">
-        <v>97.3</v>
+        <v>108.6</v>
       </c>
       <c r="H73" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="I73" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-26.66</v>
+        <v>-6.55</v>
       </c>
       <c r="K73" t="n">
-        <v>-275.51</v>
+        <v>201.92</v>
       </c>
       <c r="L73" t="n">
-        <v>276.8</v>
+        <v>202.03</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:08:50</t>
+          <t>09:04:28</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.08</v>
+        <v>2.63</v>
       </c>
       <c r="F74" t="n">
-        <v>8.4</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G74" t="n">
-        <v>99.3</v>
+        <v>101.9</v>
       </c>
       <c r="H74" t="n">
-        <v>3.1</v>
+        <v>6.6</v>
       </c>
       <c r="I74" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J74" t="n">
-        <v>-17.33</v>
+        <v>-40.61</v>
       </c>
       <c r="K74" t="n">
-        <v>66.56</v>
+        <v>55.05</v>
       </c>
       <c r="L74" t="n">
-        <v>68.78</v>
+        <v>68.41</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:11:05</t>
+          <t>09:06:39</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="F75" t="n">
-        <v>8.07</v>
+        <v>8.5</v>
       </c>
       <c r="G75" t="n">
-        <v>101.9</v>
+        <v>100</v>
       </c>
       <c r="H75" t="n">
-        <v>6.6</v>
+        <v>2.5</v>
       </c>
       <c r="I75" t="n">
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>48.57</v>
+        <v>32.25</v>
       </c>
       <c r="K75" t="n">
-        <v>-42</v>
+        <v>-42.91</v>
       </c>
       <c r="L75" t="n">
-        <v>64.20999999999999</v>
+        <v>53.68</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:12:10</t>
+          <t>09:08:28</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="F76" t="n">
-        <v>7.97</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G76" t="n">
-        <v>98.3</v>
+        <v>99.8</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I76" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>28.28</v>
+        <v>-73.87</v>
       </c>
       <c r="K76" t="n">
-        <v>-38.67</v>
+        <v>-50.45</v>
       </c>
       <c r="L76" t="n">
-        <v>47.91</v>
+        <v>89.45999999999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:17:37</t>
+          <t>09:12:01</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.32</v>
+        <v>3.58</v>
       </c>
       <c r="F77" t="n">
-        <v>7.09</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G77" t="n">
-        <v>99.8</v>
+        <v>96.2</v>
       </c>
       <c r="H77" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="I77" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>-59.48</v>
+        <v>58.61</v>
       </c>
       <c r="K77" t="n">
-        <v>70.79000000000001</v>
+        <v>32.67</v>
       </c>
       <c r="L77" t="n">
-        <v>92.45999999999999</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:18:37</t>
+          <t>09:14:22</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.87</v>
+        <v>3.47</v>
       </c>
       <c r="F78" t="n">
-        <v>7.78</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G78" t="n">
-        <v>94.7</v>
+        <v>103.7</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="I78" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>49.77</v>
+        <v>-25.38</v>
       </c>
       <c r="K78" t="n">
-        <v>30.69</v>
+        <v>-64.01000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>58.48</v>
+        <v>68.86</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:20:14</t>
+          <t>09:16:56</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.48</v>
+        <v>2.95</v>
       </c>
       <c r="F79" t="n">
-        <v>7.74</v>
+        <v>8.84</v>
       </c>
       <c r="G79" t="n">
-        <v>103.7</v>
+        <v>100.5</v>
       </c>
       <c r="H79" t="n">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
       <c r="I79" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-53.65</v>
+        <v>-67.59999999999999</v>
       </c>
       <c r="K79" t="n">
-        <v>-52.95</v>
+        <v>-16.09</v>
       </c>
       <c r="L79" t="n">
-        <v>75.38</v>
+        <v>69.48999999999999</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:24:48</t>
+          <t>09:20:46</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="F80" t="n">
-        <v>8</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G80" t="n">
-        <v>100.1</v>
+        <v>112.8</v>
       </c>
       <c r="H80" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>-92.48</v>
+        <v>77.47</v>
       </c>
       <c r="K80" t="n">
-        <v>-21.91</v>
+        <v>81.63</v>
       </c>
       <c r="L80" t="n">
-        <v>95.04000000000001</v>
+        <v>112.54</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:26:12</t>
+          <t>09:22:57</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.98</v>
+        <v>3.38</v>
       </c>
       <c r="F81" t="n">
-        <v>7.92</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G81" t="n">
-        <v>112.8</v>
+        <v>89.8</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="I81" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J81" t="n">
-        <v>79.16</v>
+        <v>-28.37</v>
       </c>
       <c r="K81" t="n">
-        <v>49.78</v>
+        <v>117.27</v>
       </c>
       <c r="L81" t="n">
-        <v>93.51000000000001</v>
+        <v>120.65</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:27:30</t>
+          <t>09:25:12</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.59</v>
+        <v>3.13</v>
       </c>
       <c r="F82" t="n">
-        <v>7.12</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G82" t="n">
-        <v>89.8</v>
+        <v>111.8</v>
       </c>
       <c r="H82" t="n">
-        <v>1.1</v>
+        <v>13.7</v>
       </c>
       <c r="I82" t="n">
         <v>27</v>
       </c>
       <c r="J82" t="n">
-        <v>126.71</v>
+        <v>81</v>
       </c>
       <c r="K82" t="n">
-        <v>-11.19</v>
+        <v>25.2</v>
       </c>
       <c r="L82" t="n">
-        <v>127.21</v>
+        <v>84.81999999999999</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:31:41</t>
+          <t>09:29:08</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="F83" t="n">
-        <v>8.74</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G83" t="n">
-        <v>111.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>82.61</v>
+        <v>-67.36</v>
       </c>
       <c r="K83" t="n">
-        <v>56.95</v>
+        <v>-106.87</v>
       </c>
       <c r="L83" t="n">
-        <v>100.33</v>
+        <v>126.33</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:32:38</t>
+          <t>09:30:57</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="F84" t="n">
-        <v>7.25</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G84" t="n">
-        <v>92.90000000000001</v>
+        <v>105.9</v>
       </c>
       <c r="H84" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="I84" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>-86.41</v>
+        <v>78.58</v>
       </c>
       <c r="K84" t="n">
-        <v>-89.37</v>
+        <v>23.8</v>
       </c>
       <c r="L84" t="n">
-        <v>124.31</v>
+        <v>82.11</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:34:07</t>
+          <t>09:31:57</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="F85" t="n">
-        <v>7.88</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G85" t="n">
-        <v>105.9</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="H85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J85" t="n">
-        <v>30.22</v>
+        <v>152.42</v>
       </c>
       <c r="K85" t="n">
-        <v>-148.11</v>
+        <v>22.67</v>
       </c>
       <c r="L85" t="n">
-        <v>151.16</v>
+        <v>154.1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:39:08</t>
+          <t>09:37:36</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="F86" t="n">
-        <v>7.19</v>
+        <v>7.37</v>
       </c>
       <c r="G86" t="n">
-        <v>85.8</v>
+        <v>104.1</v>
       </c>
       <c r="H86" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J86" t="n">
-        <v>221.26</v>
+        <v>-113.63</v>
       </c>
       <c r="K86" t="n">
-        <v>33.32</v>
+        <v>112.56</v>
       </c>
       <c r="L86" t="n">
-        <v>223.75</v>
+        <v>159.94</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:40:17</t>
+          <t>09:39:06</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="F87" t="n">
-        <v>8.210000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G87" t="n">
-        <v>104.1</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I87" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>135.15</v>
+        <v>129.52</v>
       </c>
       <c r="K87" t="n">
-        <v>92.69</v>
+        <v>204.22</v>
       </c>
       <c r="L87" t="n">
-        <v>163.88</v>
+        <v>241.83</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:41:39</t>
+          <t>09:40:21</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.91</v>
+        <v>3.03</v>
       </c>
       <c r="F88" t="n">
-        <v>7.12</v>
+        <v>8.23</v>
       </c>
       <c r="G88" t="n">
-        <v>97.90000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H88" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="I88" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J88" t="n">
-        <v>101.8</v>
+        <v>-142.8</v>
       </c>
       <c r="K88" t="n">
-        <v>204.07</v>
+        <v>67.69</v>
       </c>
       <c r="L88" t="n">
-        <v>228.05</v>
+        <v>158.03</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-08-21.xlsx
+++ b/output/2024-08-21.xlsx
@@ -640,13 +640,13 @@
         <v>30</v>
       </c>
       <c r="J14" t="n">
-        <v>-7.7</v>
+        <v>-6.65</v>
       </c>
       <c r="K14" t="n">
-        <v>53.8</v>
+        <v>46.47</v>
       </c>
       <c r="L14" t="n">
-        <v>54.35</v>
+        <v>46.94</v>
       </c>
     </row>
     <row r="15">
@@ -724,13 +724,13 @@
         <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>63.27</v>
+        <v>59.23</v>
       </c>
       <c r="K16" t="n">
-        <v>35.61</v>
+        <v>33.34</v>
       </c>
       <c r="L16" t="n">
-        <v>72.59999999999999</v>
+        <v>67.97</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>30</v>
       </c>
       <c r="J17" t="n">
-        <v>-62.13</v>
+        <v>-53.65</v>
       </c>
       <c r="K17" t="n">
-        <v>20.65</v>
+        <v>17.83</v>
       </c>
       <c r="L17" t="n">
-        <v>65.47</v>
+        <v>56.54</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>29</v>
       </c>
       <c r="J18" t="n">
-        <v>69.5</v>
+        <v>61.78</v>
       </c>
       <c r="K18" t="n">
-        <v>15.98</v>
+        <v>14.2</v>
       </c>
       <c r="L18" t="n">
-        <v>71.31</v>
+        <v>63.39</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>28</v>
       </c>
       <c r="J19" t="n">
-        <v>73.01000000000001</v>
+        <v>66.66</v>
       </c>
       <c r="K19" t="n">
-        <v>22.77</v>
+        <v>20.79</v>
       </c>
       <c r="L19" t="n">
-        <v>76.48</v>
+        <v>69.83</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>-28.73</v>
+        <v>-25.54</v>
       </c>
       <c r="K20" t="n">
-        <v>105.05</v>
+        <v>93.37</v>
       </c>
       <c r="L20" t="n">
-        <v>108.9</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>-73.73999999999999</v>
+        <v>-69.04000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>4.73</v>
+        <v>4.42</v>
       </c>
       <c r="L21" t="n">
-        <v>73.90000000000001</v>
+        <v>69.18000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>35.66</v>
+        <v>34.94</v>
       </c>
       <c r="K22" t="n">
-        <v>-66.28</v>
+        <v>-64.93000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>75.26000000000001</v>
+        <v>73.73</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>-9.380000000000001</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>117.73</v>
+        <v>110.22</v>
       </c>
       <c r="L23" t="n">
-        <v>118.11</v>
+        <v>110.57</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>30</v>
       </c>
       <c r="J24" t="n">
-        <v>111.46</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>-7.21</v>
+        <v>-6.23</v>
       </c>
       <c r="L24" t="n">
-        <v>111.69</v>
+        <v>96.45999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1144,13 +1144,13 @@
         <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>75.27</v>
+        <v>70.47</v>
       </c>
       <c r="K26" t="n">
-        <v>139.31</v>
+        <v>130.42</v>
       </c>
       <c r="L26" t="n">
-        <v>158.34</v>
+        <v>148.24</v>
       </c>
     </row>
     <row r="27">
@@ -1270,13 +1270,13 @@
         <v>29</v>
       </c>
       <c r="J29" t="n">
-        <v>35.05</v>
+        <v>31.15</v>
       </c>
       <c r="K29" t="n">
-        <v>43.15</v>
+        <v>38.36</v>
       </c>
       <c r="L29" t="n">
-        <v>55.59</v>
+        <v>49.42</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>30</v>
       </c>
       <c r="J30" t="n">
-        <v>39.46</v>
+        <v>34.08</v>
       </c>
       <c r="K30" t="n">
-        <v>-20.07</v>
+        <v>-17.33</v>
       </c>
       <c r="L30" t="n">
-        <v>44.27</v>
+        <v>38.24</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>29</v>
       </c>
       <c r="J31" t="n">
-        <v>-35.81</v>
+        <v>-31.83</v>
       </c>
       <c r="K31" t="n">
-        <v>-40.18</v>
+        <v>-35.72</v>
       </c>
       <c r="L31" t="n">
-        <v>53.83</v>
+        <v>47.85</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>30</v>
       </c>
       <c r="J32" t="n">
-        <v>59.51</v>
+        <v>51.4</v>
       </c>
       <c r="K32" t="n">
-        <v>-53.56</v>
+        <v>-46.25</v>
       </c>
       <c r="L32" t="n">
-        <v>80.06</v>
+        <v>69.14</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>-46.07</v>
+        <v>-42.06</v>
       </c>
       <c r="K33" t="n">
-        <v>85.02</v>
+        <v>77.63</v>
       </c>
       <c r="L33" t="n">
-        <v>96.7</v>
+        <v>88.29000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>-6.26</v>
+        <v>-5.72</v>
       </c>
       <c r="K34" t="n">
-        <v>74.72</v>
+        <v>68.22</v>
       </c>
       <c r="L34" t="n">
-        <v>74.98</v>
+        <v>68.45999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>37.45</v>
+        <v>35.89</v>
       </c>
       <c r="K35" t="n">
-        <v>77.15000000000001</v>
+        <v>73.94</v>
       </c>
       <c r="L35" t="n">
-        <v>85.76000000000001</v>
+        <v>82.19</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>29</v>
       </c>
       <c r="J36" t="n">
-        <v>-24.34</v>
+        <v>-21.64</v>
       </c>
       <c r="K36" t="n">
-        <v>-81.16</v>
+        <v>-72.14</v>
       </c>
       <c r="L36" t="n">
-        <v>84.73</v>
+        <v>75.31</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>105.58</v>
+        <v>101.18</v>
       </c>
       <c r="K37" t="n">
-        <v>-32.87</v>
+        <v>-31.5</v>
       </c>
       <c r="L37" t="n">
-        <v>110.58</v>
+        <v>105.97</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>71.86</v>
+        <v>65.61</v>
       </c>
       <c r="K38" t="n">
-        <v>125.62</v>
+        <v>114.71</v>
       </c>
       <c r="L38" t="n">
-        <v>144.72</v>
+        <v>132.15</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>29</v>
       </c>
       <c r="J39" t="n">
-        <v>21.71</v>
+        <v>19.31</v>
       </c>
       <c r="K39" t="n">
-        <v>132.39</v>
+        <v>117.71</v>
       </c>
       <c r="L39" t="n">
-        <v>134.16</v>
+        <v>119.28</v>
       </c>
     </row>
     <row r="40">
@@ -1774,13 +1774,13 @@
         <v>27</v>
       </c>
       <c r="J41" t="n">
-        <v>134.53</v>
+        <v>125.94</v>
       </c>
       <c r="K41" t="n">
-        <v>133.76</v>
+        <v>125.22</v>
       </c>
       <c r="L41" t="n">
-        <v>189.71</v>
+        <v>177.6</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>38.36</v>
+        <v>38.42</v>
       </c>
       <c r="K42" t="n">
-        <v>-206.5</v>
+        <v>-206.82</v>
       </c>
       <c r="L42" t="n">
-        <v>210.03</v>
+        <v>210.36</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-50.32</v>
+        <v>-49.29</v>
       </c>
       <c r="K43" t="n">
-        <v>-196.58</v>
+        <v>-192.57</v>
       </c>
       <c r="L43" t="n">
-        <v>202.92</v>
+        <v>198.78</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>26</v>
       </c>
       <c r="J44" t="n">
-        <v>47.51</v>
+        <v>45.53</v>
       </c>
       <c r="K44" t="n">
-        <v>-25.04</v>
+        <v>-23.99</v>
       </c>
       <c r="L44" t="n">
-        <v>53.7</v>
+        <v>51.47</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>29</v>
       </c>
       <c r="J45" t="n">
-        <v>-18.56</v>
+        <v>-16.5</v>
       </c>
       <c r="K45" t="n">
-        <v>44.37</v>
+        <v>39.44</v>
       </c>
       <c r="L45" t="n">
-        <v>48.1</v>
+        <v>42.76</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>26</v>
       </c>
       <c r="J46" t="n">
-        <v>-30.8</v>
+        <v>-29.52</v>
       </c>
       <c r="K46" t="n">
-        <v>-37.48</v>
+        <v>-35.92</v>
       </c>
       <c r="L46" t="n">
-        <v>48.52</v>
+        <v>46.49</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>75.45</v>
+        <v>72.31</v>
       </c>
       <c r="K47" t="n">
-        <v>-54.38</v>
+        <v>-52.11</v>
       </c>
       <c r="L47" t="n">
-        <v>93.01000000000001</v>
+        <v>89.13</v>
       </c>
     </row>
     <row r="48">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>74.47</v>
+        <v>72.95</v>
       </c>
       <c r="K50" t="n">
-        <v>44.73</v>
+        <v>43.82</v>
       </c>
       <c r="L50" t="n">
-        <v>86.87</v>
+        <v>85.09999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>-67.12</v>
+        <v>-64.31999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>51.86</v>
+        <v>49.7</v>
       </c>
       <c r="L51" t="n">
-        <v>84.81999999999999</v>
+        <v>81.29000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>28</v>
       </c>
       <c r="J52" t="n">
-        <v>48.68</v>
+        <v>44.45</v>
       </c>
       <c r="K52" t="n">
-        <v>75.04000000000001</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>89.45</v>
+        <v>81.67</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>155.11</v>
+        <v>151.98</v>
       </c>
       <c r="K53" t="n">
-        <v>75.81</v>
+        <v>74.28</v>
       </c>
       <c r="L53" t="n">
-        <v>172.64</v>
+        <v>169.16</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>29</v>
       </c>
       <c r="J54" t="n">
-        <v>-67.22</v>
+        <v>-59.75</v>
       </c>
       <c r="K54" t="n">
-        <v>-85.3</v>
+        <v>-75.81999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>108.6</v>
+        <v>96.53</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>141.87</v>
+        <v>138.97</v>
       </c>
       <c r="K55" t="n">
-        <v>-91.73999999999999</v>
+        <v>-89.87</v>
       </c>
       <c r="L55" t="n">
-        <v>168.95</v>
+        <v>165.5</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>227.41</v>
+        <v>217.94</v>
       </c>
       <c r="K56" t="n">
-        <v>77.31</v>
+        <v>74.09</v>
       </c>
       <c r="L56" t="n">
-        <v>240.19</v>
+        <v>230.19</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>30</v>
       </c>
       <c r="J57" t="n">
-        <v>19.29</v>
+        <v>16.66</v>
       </c>
       <c r="K57" t="n">
-        <v>-135.38</v>
+        <v>-116.92</v>
       </c>
       <c r="L57" t="n">
-        <v>136.75</v>
+        <v>118.1</v>
       </c>
     </row>
     <row r="58">
@@ -2530,13 +2530,13 @@
         <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>-10.78</v>
+        <v>-10.09</v>
       </c>
       <c r="K59" t="n">
-        <v>-64.94</v>
+        <v>-60.79</v>
       </c>
       <c r="L59" t="n">
-        <v>65.81999999999999</v>
+        <v>61.62</v>
       </c>
     </row>
     <row r="60">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>-43.79</v>
+        <v>-42.9</v>
       </c>
       <c r="K61" t="n">
-        <v>-25.38</v>
+        <v>-24.86</v>
       </c>
       <c r="L61" t="n">
-        <v>50.62</v>
+        <v>49.58</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>-7.63</v>
+        <v>-6.78</v>
       </c>
       <c r="K62" t="n">
-        <v>-64.70999999999999</v>
+        <v>-57.52</v>
       </c>
       <c r="L62" t="n">
-        <v>65.16</v>
+        <v>57.92</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>-33.73</v>
+        <v>-33.04</v>
       </c>
       <c r="K63" t="n">
-        <v>-52.78</v>
+        <v>-51.7</v>
       </c>
       <c r="L63" t="n">
-        <v>62.63</v>
+        <v>61.36</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>27</v>
       </c>
       <c r="J64" t="n">
-        <v>-36.94</v>
+        <v>-34.58</v>
       </c>
       <c r="K64" t="n">
-        <v>-49.5</v>
+        <v>-46.34</v>
       </c>
       <c r="L64" t="n">
-        <v>61.76</v>
+        <v>57.82</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>-72.09</v>
+        <v>-70.62</v>
       </c>
       <c r="K65" t="n">
-        <v>-78.56</v>
+        <v>-76.95</v>
       </c>
       <c r="L65" t="n">
-        <v>106.62</v>
+        <v>104.45</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>29</v>
       </c>
       <c r="J66" t="n">
-        <v>-72.89</v>
+        <v>-64.78</v>
       </c>
       <c r="K66" t="n">
-        <v>34.28</v>
+        <v>30.46</v>
       </c>
       <c r="L66" t="n">
-        <v>80.54000000000001</v>
+        <v>71.58</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>-96.90000000000001</v>
+        <v>-94.92</v>
       </c>
       <c r="K67" t="n">
-        <v>-60.59</v>
+        <v>-59.36</v>
       </c>
       <c r="L67" t="n">
-        <v>114.28</v>
+        <v>111.95</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>79.73</v>
+        <v>76.41</v>
       </c>
       <c r="K68" t="n">
-        <v>81.98</v>
+        <v>78.56</v>
       </c>
       <c r="L68" t="n">
-        <v>114.36</v>
+        <v>109.59</v>
       </c>
     </row>
     <row r="69">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>-3.8</v>
+        <v>-3.64</v>
       </c>
       <c r="K70" t="n">
-        <v>-170.98</v>
+        <v>-163.9</v>
       </c>
       <c r="L70" t="n">
-        <v>171.02</v>
+        <v>163.94</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>30</v>
       </c>
       <c r="J71" t="n">
-        <v>131.43</v>
+        <v>113.51</v>
       </c>
       <c r="K71" t="n">
-        <v>97.76000000000001</v>
+        <v>84.43000000000001</v>
       </c>
       <c r="L71" t="n">
-        <v>163.8</v>
+        <v>141.46</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>206.2</v>
+        <v>201.99</v>
       </c>
       <c r="K72" t="n">
-        <v>-55.15</v>
+        <v>-54.02</v>
       </c>
       <c r="L72" t="n">
-        <v>213.44</v>
+        <v>209.09</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>-6.55</v>
+        <v>-6.42</v>
       </c>
       <c r="K73" t="n">
-        <v>201.92</v>
+        <v>197.8</v>
       </c>
       <c r="L73" t="n">
-        <v>202.03</v>
+        <v>197.91</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>27</v>
       </c>
       <c r="J74" t="n">
-        <v>-40.61</v>
+        <v>-38.02</v>
       </c>
       <c r="K74" t="n">
-        <v>55.05</v>
+        <v>51.54</v>
       </c>
       <c r="L74" t="n">
-        <v>68.41</v>
+        <v>64.04000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>32.25</v>
+        <v>30.9</v>
       </c>
       <c r="K75" t="n">
-        <v>-42.91</v>
+        <v>-41.12</v>
       </c>
       <c r="L75" t="n">
-        <v>53.68</v>
+        <v>51.44</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>-73.87</v>
+        <v>-65.65000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>-50.45</v>
+        <v>-44.84</v>
       </c>
       <c r="L76" t="n">
-        <v>89.45999999999999</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>58.61</v>
+        <v>56.07</v>
       </c>
       <c r="K77" t="n">
-        <v>32.67</v>
+        <v>31.25</v>
       </c>
       <c r="L77" t="n">
-        <v>67.09999999999999</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>-25.38</v>
+        <v>-23.15</v>
       </c>
       <c r="K78" t="n">
-        <v>-64.01000000000001</v>
+        <v>-58.38</v>
       </c>
       <c r="L78" t="n">
-        <v>68.86</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>28</v>
       </c>
       <c r="J79" t="n">
-        <v>-67.59999999999999</v>
+        <v>-61.72</v>
       </c>
       <c r="K79" t="n">
-        <v>-16.09</v>
+        <v>-14.69</v>
       </c>
       <c r="L79" t="n">
-        <v>69.48999999999999</v>
+        <v>63.45</v>
       </c>
     </row>
     <row r="80">
@@ -3454,13 +3454,13 @@
         <v>30</v>
       </c>
       <c r="J81" t="n">
-        <v>-28.37</v>
+        <v>-24.5</v>
       </c>
       <c r="K81" t="n">
-        <v>117.27</v>
+        <v>101.25</v>
       </c>
       <c r="L81" t="n">
-        <v>120.65</v>
+        <v>104.17</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>27</v>
       </c>
       <c r="J82" t="n">
-        <v>81</v>
+        <v>75.83</v>
       </c>
       <c r="K82" t="n">
-        <v>25.2</v>
+        <v>23.59</v>
       </c>
       <c r="L82" t="n">
-        <v>84.81999999999999</v>
+        <v>79.41</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>-67.36</v>
+        <v>-64.55</v>
       </c>
       <c r="K83" t="n">
-        <v>-106.87</v>
+        <v>-102.42</v>
       </c>
       <c r="L83" t="n">
-        <v>126.33</v>
+        <v>121.07</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>78.58</v>
+        <v>71.75</v>
       </c>
       <c r="K84" t="n">
-        <v>23.8</v>
+        <v>21.73</v>
       </c>
       <c r="L84" t="n">
-        <v>82.11</v>
+        <v>74.97</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>30</v>
       </c>
       <c r="J85" t="n">
-        <v>152.42</v>
+        <v>131.64</v>
       </c>
       <c r="K85" t="n">
-        <v>22.67</v>
+        <v>19.58</v>
       </c>
       <c r="L85" t="n">
-        <v>154.1</v>
+        <v>133.09</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>30</v>
       </c>
       <c r="J86" t="n">
-        <v>-113.63</v>
+        <v>-98.13</v>
       </c>
       <c r="K86" t="n">
-        <v>112.56</v>
+        <v>97.20999999999999</v>
       </c>
       <c r="L86" t="n">
-        <v>159.94</v>
+        <v>138.13</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>27</v>
       </c>
       <c r="J87" t="n">
-        <v>129.52</v>
+        <v>121.37</v>
       </c>
       <c r="K87" t="n">
-        <v>204.22</v>
+        <v>191.37</v>
       </c>
       <c r="L87" t="n">
-        <v>241.83</v>
+        <v>226.61</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>30</v>
       </c>
       <c r="J88" t="n">
-        <v>-142.8</v>
+        <v>-123.33</v>
       </c>
       <c r="K88" t="n">
-        <v>67.69</v>
+        <v>58.46</v>
       </c>
       <c r="L88" t="n">
-        <v>158.03</v>
+        <v>136.48</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-08-21.xlsx
+++ b/output/2024-08-21.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.07</v>
+        <v>2.37</v>
       </c>
       <c r="F14" t="n">
-        <v>8.35</v>
+        <v>3.41</v>
       </c>
       <c r="G14" t="n">
-        <v>100.1</v>
+        <v>111.4</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>37.4</v>
       </c>
       <c r="I14" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.65</v>
+        <v>24.63</v>
       </c>
       <c r="K14" t="n">
-        <v>46.47</v>
+        <v>-34.35</v>
       </c>
       <c r="L14" t="n">
-        <v>46.94</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:00:46</t>
+          <t>06:01:04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.41</v>
+        <v>2.54</v>
       </c>
       <c r="F15" t="n">
-        <v>2.71</v>
+        <v>6.66</v>
       </c>
       <c r="G15" t="n">
-        <v>93.7</v>
+        <v>101.6</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7</v>
+        <v>43.5</v>
       </c>
       <c r="I15" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>-32.57</v>
+        <v>9.5</v>
       </c>
       <c r="K15" t="n">
-        <v>22.77</v>
+        <v>-5.11</v>
       </c>
       <c r="L15" t="n">
-        <v>39.74</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:01:56</t>
+          <t>06:03:27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="F16" t="n">
-        <v>7.61</v>
+        <v>6.03</v>
       </c>
       <c r="G16" t="n">
-        <v>107.5</v>
+        <v>88.5</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3</v>
+        <v>50.4</v>
       </c>
       <c r="I16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>59.23</v>
+        <v>13.21</v>
       </c>
       <c r="K16" t="n">
-        <v>33.34</v>
+        <v>36.45</v>
       </c>
       <c r="L16" t="n">
-        <v>67.97</v>
+        <v>38.77</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:07:25</t>
+          <t>06:07:33</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="F17" t="n">
-        <v>6.67</v>
+        <v>3.48</v>
       </c>
       <c r="G17" t="n">
-        <v>101.4</v>
+        <v>100.4</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>81.8</v>
       </c>
       <c r="I17" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-53.65</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>17.83</v>
+        <v>-14.98</v>
       </c>
       <c r="L17" t="n">
-        <v>56.54</v>
+        <v>79.73999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:08:52</t>
+          <t>06:08:34</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.12</v>
+        <v>2.51</v>
       </c>
       <c r="F18" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="G18" t="n">
-        <v>83.8</v>
+        <v>84</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>56.6</v>
       </c>
       <c r="I18" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J18" t="n">
-        <v>61.78</v>
+        <v>54.82</v>
       </c>
       <c r="K18" t="n">
-        <v>14.2</v>
+        <v>16.88</v>
       </c>
       <c r="L18" t="n">
-        <v>63.39</v>
+        <v>57.36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:11:03</t>
+          <t>06:09:51</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.18</v>
+        <v>2.64</v>
       </c>
       <c r="F19" t="n">
-        <v>5.59</v>
+        <v>4.93</v>
       </c>
       <c r="G19" t="n">
-        <v>98.2</v>
+        <v>100.8</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2</v>
+        <v>41.4</v>
       </c>
       <c r="I19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>66.66</v>
+        <v>15.28</v>
       </c>
       <c r="K19" t="n">
-        <v>20.79</v>
+        <v>-73.56</v>
       </c>
       <c r="L19" t="n">
-        <v>69.83</v>
+        <v>75.13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:16:33</t>
+          <t>06:14:57</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.97</v>
+        <v>2.23</v>
       </c>
       <c r="F20" t="n">
-        <v>7.2</v>
+        <v>5.72</v>
       </c>
       <c r="G20" t="n">
-        <v>94.2</v>
+        <v>84.3</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9</v>
+        <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>-25.54</v>
+        <v>8.16</v>
       </c>
       <c r="K20" t="n">
-        <v>93.37</v>
+        <v>-86.09999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>96.8</v>
+        <v>86.48999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:17:18</t>
+          <t>06:17:02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.49</v>
+        <v>2.98</v>
       </c>
       <c r="F21" t="n">
-        <v>5.87</v>
+        <v>7.11</v>
       </c>
       <c r="G21" t="n">
-        <v>93.09999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>10.4</v>
+        <v>37.2</v>
       </c>
       <c r="I21" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>-69.04000000000001</v>
+        <v>74.05</v>
       </c>
       <c r="K21" t="n">
-        <v>4.42</v>
+        <v>-66.01000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>69.18000000000001</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:19:03</t>
+          <t>06:19:51</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="F22" t="n">
-        <v>5.97</v>
+        <v>3.8</v>
       </c>
       <c r="G22" t="n">
-        <v>104.8</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>4.1</v>
+        <v>30.9</v>
       </c>
       <c r="I22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>34.94</v>
+        <v>-94.98</v>
       </c>
       <c r="K22" t="n">
-        <v>-64.93000000000001</v>
+        <v>-52.75</v>
       </c>
       <c r="L22" t="n">
-        <v>73.73</v>
+        <v>108.65</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:24:04</t>
+          <t>06:25:11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.57</v>
+        <v>3.13</v>
       </c>
       <c r="F23" t="n">
-        <v>3.99</v>
+        <v>8.49</v>
       </c>
       <c r="G23" t="n">
-        <v>93.2</v>
+        <v>96.3</v>
       </c>
       <c r="H23" t="n">
-        <v>5.3</v>
+        <v>51.7</v>
       </c>
       <c r="I23" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>-8.779999999999999</v>
+        <v>-45.38</v>
       </c>
       <c r="K23" t="n">
-        <v>110.22</v>
+        <v>124.18</v>
       </c>
       <c r="L23" t="n">
-        <v>110.57</v>
+        <v>132.21</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:26:07</t>
+          <t>06:26:31</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,28 +1045,28 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.47</v>
+        <v>2.71</v>
       </c>
       <c r="F24" t="n">
-        <v>6.12</v>
+        <v>6.05</v>
       </c>
       <c r="G24" t="n">
-        <v>98.59999999999999</v>
+        <v>105.8</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>50.3</v>
       </c>
       <c r="I24" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>96.26000000000001</v>
+        <v>153.91</v>
       </c>
       <c r="K24" t="n">
-        <v>-6.23</v>
+        <v>101.53</v>
       </c>
       <c r="L24" t="n">
-        <v>96.45999999999999</v>
+        <v>184.38</v>
       </c>
     </row>
     <row r="25">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.14</v>
+        <v>2.76</v>
       </c>
       <c r="F25" t="n">
-        <v>5.21</v>
+        <v>7.38</v>
       </c>
       <c r="G25" t="n">
-        <v>96.90000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>3.3</v>
+        <v>38.5</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>-132.65</v>
+        <v>-99.94</v>
       </c>
       <c r="K25" t="n">
-        <v>-147.22</v>
+        <v>-111.21</v>
       </c>
       <c r="L25" t="n">
-        <v>198.16</v>
+        <v>149.52</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:33:45</t>
+          <t>06:33:05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.13</v>
+        <v>2.52</v>
       </c>
       <c r="F26" t="n">
-        <v>8.970000000000001</v>
+        <v>4.41</v>
       </c>
       <c r="G26" t="n">
-        <v>88.2</v>
+        <v>103.8</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>15.2</v>
       </c>
       <c r="I26" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>70.47</v>
+        <v>11.36</v>
       </c>
       <c r="K26" t="n">
-        <v>130.42</v>
+        <v>-37.59</v>
       </c>
       <c r="L26" t="n">
-        <v>148.24</v>
+        <v>39.27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:34:52</t>
+          <t>06:35:10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.72</v>
+        <v>3.91</v>
       </c>
       <c r="F27" t="n">
-        <v>5.82</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>109.1</v>
+        <v>96.3</v>
       </c>
       <c r="H27" t="n">
-        <v>7.3</v>
+        <v>44</v>
       </c>
       <c r="I27" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-140.86</v>
+        <v>53.96</v>
       </c>
       <c r="K27" t="n">
-        <v>-92.84999999999999</v>
+        <v>-266.2</v>
       </c>
       <c r="L27" t="n">
-        <v>168.71</v>
+        <v>271.61</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:36:22</t>
+          <t>06:36:39</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="F28" t="n">
-        <v>7.97</v>
+        <v>6.67</v>
       </c>
       <c r="G28" t="n">
-        <v>95.7</v>
+        <v>88.8</v>
       </c>
       <c r="H28" t="n">
-        <v>1.5</v>
+        <v>15.9</v>
       </c>
       <c r="I28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-17.68</v>
+        <v>95.76000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>222.49</v>
+        <v>203.59</v>
       </c>
       <c r="L28" t="n">
-        <v>223.19</v>
+        <v>224.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:45:14</t>
+          <t>06:49:20</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="F29" t="n">
-        <v>4.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>96.8</v>
+        <v>97</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>35.2</v>
       </c>
       <c r="I29" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>31.15</v>
+        <v>44.57</v>
       </c>
       <c r="K29" t="n">
-        <v>38.36</v>
+        <v>-87.61</v>
       </c>
       <c r="L29" t="n">
-        <v>49.42</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:46:46</t>
+          <t>06:51:03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="F30" t="n">
-        <v>6.12</v>
+        <v>8.6</v>
       </c>
       <c r="G30" t="n">
-        <v>110.6</v>
+        <v>82.8</v>
       </c>
       <c r="H30" t="n">
-        <v>3.1</v>
+        <v>34.7</v>
       </c>
       <c r="I30" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>34.08</v>
+        <v>-41.13</v>
       </c>
       <c r="K30" t="n">
-        <v>-17.33</v>
+        <v>35.85</v>
       </c>
       <c r="L30" t="n">
-        <v>38.24</v>
+        <v>54.57</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:48:33</t>
+          <t>06:51:40</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="F31" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="G31" t="n">
-        <v>99.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>3.7</v>
+        <v>40.4</v>
       </c>
       <c r="I31" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-31.83</v>
+        <v>32.79</v>
       </c>
       <c r="K31" t="n">
-        <v>-35.72</v>
+        <v>-33.18</v>
       </c>
       <c r="L31" t="n">
-        <v>47.85</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:53:12</t>
+          <t>06:56:59</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.77</v>
+        <v>2.54</v>
       </c>
       <c r="F32" t="n">
-        <v>6.29</v>
+        <v>7.87</v>
       </c>
       <c r="G32" t="n">
-        <v>103.9</v>
+        <v>95</v>
       </c>
       <c r="H32" t="n">
-        <v>2.7</v>
+        <v>20.4</v>
       </c>
       <c r="I32" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>51.4</v>
+        <v>-43.63</v>
       </c>
       <c r="K32" t="n">
-        <v>-46.25</v>
+        <v>57.76</v>
       </c>
       <c r="L32" t="n">
-        <v>69.14</v>
+        <v>72.39</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:54:38</t>
+          <t>06:58:15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="F33" t="n">
-        <v>6.57</v>
+        <v>6.36</v>
       </c>
       <c r="G33" t="n">
-        <v>94.2</v>
+        <v>87.8</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>27.5</v>
       </c>
       <c r="I33" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>-42.06</v>
+        <v>50.45</v>
       </c>
       <c r="K33" t="n">
-        <v>77.63</v>
+        <v>42.46</v>
       </c>
       <c r="L33" t="n">
-        <v>88.29000000000001</v>
+        <v>65.94</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:56:04</t>
+          <t>07:00:30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="F34" t="n">
-        <v>6.29</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>97.40000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="H34" t="n">
-        <v>4</v>
+        <v>58.9</v>
       </c>
       <c r="I34" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-5.72</v>
+        <v>-65.06999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>68.22</v>
+        <v>-32.42</v>
       </c>
       <c r="L34" t="n">
-        <v>68.45999999999999</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:00:58</t>
+          <t>07:06:20</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.43</v>
+        <v>2.68</v>
       </c>
       <c r="F35" t="n">
-        <v>6.47</v>
+        <v>8.81</v>
       </c>
       <c r="G35" t="n">
-        <v>111.4</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>9.5</v>
+        <v>24.1</v>
       </c>
       <c r="I35" t="n">
         <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>35.89</v>
+        <v>96.22</v>
       </c>
       <c r="K35" t="n">
-        <v>73.94</v>
+        <v>-17.3</v>
       </c>
       <c r="L35" t="n">
-        <v>82.19</v>
+        <v>97.77</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:03:18</t>
+          <t>07:08:23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.92</v>
+        <v>2.68</v>
       </c>
       <c r="F36" t="n">
-        <v>8.970000000000001</v>
+        <v>8.91</v>
       </c>
       <c r="G36" t="n">
-        <v>114.8</v>
+        <v>111.5</v>
       </c>
       <c r="H36" t="n">
-        <v>2.8</v>
+        <v>36.8</v>
       </c>
       <c r="I36" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>-21.64</v>
+        <v>82.5</v>
       </c>
       <c r="K36" t="n">
-        <v>-72.14</v>
+        <v>-48.19</v>
       </c>
       <c r="L36" t="n">
-        <v>75.31</v>
+        <v>95.54000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:05:05</t>
+          <t>07:09:47</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.13</v>
+        <v>2.73</v>
       </c>
       <c r="F37" t="n">
-        <v>7.46</v>
+        <v>7.29</v>
       </c>
       <c r="G37" t="n">
-        <v>95.09999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>3.1</v>
+        <v>13.5</v>
       </c>
       <c r="I37" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>101.18</v>
+        <v>60.57</v>
       </c>
       <c r="K37" t="n">
-        <v>-31.5</v>
+        <v>51.92</v>
       </c>
       <c r="L37" t="n">
-        <v>105.97</v>
+        <v>79.77</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:09:31</t>
+          <t>07:14:14</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.33</v>
+        <v>2.54</v>
       </c>
       <c r="F38" t="n">
-        <v>8.970000000000001</v>
+        <v>7.42</v>
       </c>
       <c r="G38" t="n">
-        <v>107.1</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>4.2</v>
+        <v>69.5</v>
       </c>
       <c r="I38" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>65.61</v>
+        <v>-80.11</v>
       </c>
       <c r="K38" t="n">
-        <v>114.71</v>
+        <v>58.92</v>
       </c>
       <c r="L38" t="n">
-        <v>132.15</v>
+        <v>99.45</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:11:01</t>
+          <t>07:16:15</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.45</v>
+        <v>3.22</v>
       </c>
       <c r="F39" t="n">
-        <v>8.970000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="G39" t="n">
-        <v>96.90000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="H39" t="n">
-        <v>3.7</v>
+        <v>35.1</v>
       </c>
       <c r="I39" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>19.31</v>
+        <v>-81.91</v>
       </c>
       <c r="K39" t="n">
-        <v>117.71</v>
+        <v>-134.03</v>
       </c>
       <c r="L39" t="n">
-        <v>119.28</v>
+        <v>157.07</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:11:55</t>
+          <t>07:18:16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.65</v>
+        <v>3.16</v>
       </c>
       <c r="F40" t="n">
-        <v>7.2</v>
+        <v>5.37</v>
       </c>
       <c r="G40" t="n">
-        <v>103.8</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9</v>
+        <v>58.3</v>
       </c>
       <c r="I40" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>83.93000000000001</v>
+        <v>134.64</v>
       </c>
       <c r="K40" t="n">
-        <v>115.75</v>
+        <v>71.36</v>
       </c>
       <c r="L40" t="n">
-        <v>142.98</v>
+        <v>152.38</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:17:01</t>
+          <t>07:24:32</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="F41" t="n">
-        <v>6.98</v>
+        <v>6.75</v>
       </c>
       <c r="G41" t="n">
         <v>103.8</v>
       </c>
       <c r="H41" t="n">
-        <v>4.3</v>
+        <v>27.5</v>
       </c>
       <c r="I41" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J41" t="n">
-        <v>125.94</v>
+        <v>144.55</v>
       </c>
       <c r="K41" t="n">
-        <v>125.22</v>
+        <v>155.13</v>
       </c>
       <c r="L41" t="n">
-        <v>177.6</v>
+        <v>212.03</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:18:51</t>
+          <t>07:26:44</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.43</v>
+        <v>3.31</v>
       </c>
       <c r="F42" t="n">
-        <v>8.41</v>
+        <v>8.35</v>
       </c>
       <c r="G42" t="n">
-        <v>105.3</v>
+        <v>109.6</v>
       </c>
       <c r="H42" t="n">
-        <v>8.199999999999999</v>
+        <v>35.8</v>
       </c>
       <c r="I42" t="n">
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>38.42</v>
+        <v>49.89</v>
       </c>
       <c r="K42" t="n">
-        <v>-206.82</v>
+        <v>229.36</v>
       </c>
       <c r="L42" t="n">
-        <v>210.36</v>
+        <v>234.73</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:20:12</t>
+          <t>07:28:20</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="F43" t="n">
-        <v>8.279999999999999</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
       <c r="H43" t="n">
-        <v>2.1</v>
+        <v>39</v>
       </c>
       <c r="I43" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>-49.29</v>
+        <v>193.47</v>
       </c>
       <c r="K43" t="n">
-        <v>-192.57</v>
+        <v>77.52</v>
       </c>
       <c r="L43" t="n">
-        <v>198.78</v>
+        <v>208.42</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:32:14</t>
+          <t>07:38:36</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="F44" t="n">
-        <v>8.56</v>
+        <v>6.15</v>
       </c>
       <c r="G44" t="n">
-        <v>101.7</v>
+        <v>94.3</v>
       </c>
       <c r="H44" t="n">
-        <v>10.5</v>
+        <v>57.3</v>
       </c>
       <c r="I44" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>45.53</v>
+        <v>-51.08</v>
       </c>
       <c r="K44" t="n">
-        <v>-23.99</v>
+        <v>24.49</v>
       </c>
       <c r="L44" t="n">
-        <v>51.47</v>
+        <v>56.64</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:32:56</t>
+          <t>07:40:01</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.21</v>
+        <v>2.62</v>
       </c>
       <c r="F45" t="n">
-        <v>8.970000000000001</v>
+        <v>6.36</v>
       </c>
       <c r="G45" t="n">
-        <v>96.09999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="H45" t="n">
-        <v>1.9</v>
+        <v>40.6</v>
       </c>
       <c r="I45" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>-16.5</v>
+        <v>12.91</v>
       </c>
       <c r="K45" t="n">
-        <v>39.44</v>
+        <v>35.2</v>
       </c>
       <c r="L45" t="n">
-        <v>42.76</v>
+        <v>37.49</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:35:19</t>
+          <t>07:41:20</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.9</v>
+        <v>3.11</v>
       </c>
       <c r="F46" t="n">
-        <v>7.24</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>98.09999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>44.6</v>
       </c>
       <c r="I46" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>-29.52</v>
+        <v>9.32</v>
       </c>
       <c r="K46" t="n">
-        <v>-35.92</v>
+        <v>33.05</v>
       </c>
       <c r="L46" t="n">
-        <v>46.49</v>
+        <v>34.34</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:39:44</t>
+          <t>07:45:28</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.93</v>
+        <v>3.04</v>
       </c>
       <c r="F47" t="n">
-        <v>8.220000000000001</v>
+        <v>5.77</v>
       </c>
       <c r="G47" t="n">
-        <v>108.6</v>
+        <v>102</v>
       </c>
       <c r="H47" t="n">
-        <v>6.2</v>
+        <v>46.2</v>
       </c>
       <c r="I47" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>72.31</v>
+        <v>45.14</v>
       </c>
       <c r="K47" t="n">
-        <v>-52.11</v>
+        <v>-77.01000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>89.13</v>
+        <v>89.26000000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:41:49</t>
+          <t>07:46:24</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.08</v>
+        <v>2.93</v>
       </c>
       <c r="F48" t="n">
         <v>8.970000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>101.9</v>
+        <v>102</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>51.6</v>
       </c>
       <c r="I48" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>86.79000000000001</v>
+        <v>28.03</v>
       </c>
       <c r="K48" t="n">
-        <v>-63.35</v>
+        <v>61.28</v>
       </c>
       <c r="L48" t="n">
-        <v>107.45</v>
+        <v>67.39</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:43:27</t>
+          <t>07:47:38</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.73</v>
+        <v>3.09</v>
       </c>
       <c r="F49" t="n">
-        <v>7.49</v>
+        <v>6.52</v>
       </c>
       <c r="G49" t="n">
-        <v>97.40000000000001</v>
+        <v>103.7</v>
       </c>
       <c r="H49" t="n">
-        <v>1.5</v>
+        <v>29.7</v>
       </c>
       <c r="I49" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>-7.57</v>
+        <v>-78.06999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>55.63</v>
+        <v>40.77</v>
       </c>
       <c r="L49" t="n">
-        <v>56.14</v>
+        <v>88.08</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:48:14</t>
+          <t>07:53:31</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.04</v>
+        <v>2.77</v>
       </c>
       <c r="F50" t="n">
-        <v>7.96</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G50" t="n">
-        <v>104</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>4.7</v>
+        <v>40.4</v>
       </c>
       <c r="I50" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>72.95</v>
+        <v>-77.48999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>43.82</v>
+        <v>44.92</v>
       </c>
       <c r="L50" t="n">
-        <v>85.09999999999999</v>
+        <v>89.56999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:49:49</t>
+          <t>07:55:10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="F51" t="n">
-        <v>7.34</v>
+        <v>8.18</v>
       </c>
       <c r="G51" t="n">
-        <v>99.90000000000001</v>
+        <v>107</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>16.8</v>
       </c>
       <c r="I51" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-64.31999999999999</v>
+        <v>84.78</v>
       </c>
       <c r="K51" t="n">
-        <v>49.7</v>
+        <v>-11.78</v>
       </c>
       <c r="L51" t="n">
-        <v>81.29000000000001</v>
+        <v>85.59</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:50:56</t>
+          <t>07:57:00</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="F52" t="n">
-        <v>8.970000000000001</v>
+        <v>5.59</v>
       </c>
       <c r="G52" t="n">
-        <v>86.40000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J52" t="n">
-        <v>44.45</v>
+        <v>88.33</v>
       </c>
       <c r="K52" t="n">
-        <v>68.51000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>81.67</v>
+        <v>116.46</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:55:11</t>
+          <t>08:03:03</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.46</v>
+        <v>3.27</v>
       </c>
       <c r="F53" t="n">
-        <v>8.34</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="G53" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H53" t="n">
-        <v>5.5</v>
+        <v>51.9</v>
       </c>
       <c r="I53" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>151.98</v>
+        <v>154.96</v>
       </c>
       <c r="K53" t="n">
-        <v>74.28</v>
+        <v>127.75</v>
       </c>
       <c r="L53" t="n">
-        <v>169.16</v>
+        <v>200.83</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:56:18</t>
+          <t>08:05:01</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.01</v>
+        <v>2.91</v>
       </c>
       <c r="F54" t="n">
-        <v>8.24</v>
+        <v>8.25</v>
       </c>
       <c r="G54" t="n">
-        <v>87.8</v>
+        <v>85.3</v>
       </c>
       <c r="H54" t="n">
-        <v>8.300000000000001</v>
+        <v>34.5</v>
       </c>
       <c r="I54" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>-59.75</v>
+        <v>136.24</v>
       </c>
       <c r="K54" t="n">
-        <v>-75.81999999999999</v>
+        <v>-17</v>
       </c>
       <c r="L54" t="n">
-        <v>96.53</v>
+        <v>137.29</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:58:16</t>
+          <t>08:07:07</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.96</v>
+        <v>3.21</v>
       </c>
       <c r="F55" t="n">
-        <v>8.68</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>101.6</v>
+        <v>90.7</v>
       </c>
       <c r="H55" t="n">
-        <v>2.8</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J55" t="n">
-        <v>138.97</v>
+        <v>173.91</v>
       </c>
       <c r="K55" t="n">
-        <v>-89.87</v>
+        <v>-20.52</v>
       </c>
       <c r="L55" t="n">
-        <v>165.5</v>
+        <v>175.11</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:04:48</t>
+          <t>08:12:22</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.87</v>
+        <v>3.07</v>
       </c>
       <c r="F56" t="n">
-        <v>7.61</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G56" t="n">
-        <v>97.7</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H56" t="n">
-        <v>3.6</v>
+        <v>52.1</v>
       </c>
       <c r="I56" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>217.94</v>
+        <v>71.73</v>
       </c>
       <c r="K56" t="n">
-        <v>74.09</v>
+        <v>-73.69</v>
       </c>
       <c r="L56" t="n">
-        <v>230.19</v>
+        <v>102.84</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:06:07</t>
+          <t>08:14:45</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.06</v>
+        <v>3.2</v>
       </c>
       <c r="F57" t="n">
-        <v>7.12</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>97.5</v>
+        <v>111.2</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>30.4</v>
       </c>
       <c r="I57" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>16.66</v>
+        <v>-211.16</v>
       </c>
       <c r="K57" t="n">
-        <v>-116.92</v>
+        <v>-104.22</v>
       </c>
       <c r="L57" t="n">
-        <v>118.1</v>
+        <v>235.48</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:08:17</t>
+          <t>08:15:55</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="F58" t="n">
-        <v>5.63</v>
+        <v>4.57</v>
       </c>
       <c r="G58" t="n">
-        <v>101.8</v>
+        <v>86</v>
       </c>
       <c r="H58" t="n">
-        <v>5.6</v>
+        <v>45.6</v>
       </c>
       <c r="I58" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>168.88</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="K58" t="n">
-        <v>-43.8</v>
+        <v>145.78</v>
       </c>
       <c r="L58" t="n">
-        <v>174.46</v>
+        <v>171.82</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:18:49</t>
+          <t>08:27:23</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="F59" t="n">
-        <v>8.49</v>
+        <v>6.84</v>
       </c>
       <c r="G59" t="n">
-        <v>93.5</v>
+        <v>93.2</v>
       </c>
       <c r="H59" t="n">
-        <v>2.7</v>
+        <v>22.4</v>
       </c>
       <c r="I59" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-10.09</v>
+        <v>-45.31</v>
       </c>
       <c r="K59" t="n">
-        <v>-60.79</v>
+        <v>21.49</v>
       </c>
       <c r="L59" t="n">
-        <v>61.62</v>
+        <v>50.15</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:20:22</t>
+          <t>08:28:37</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.04</v>
+        <v>3.09</v>
       </c>
       <c r="F60" t="n">
         <v>8.970000000000001</v>
       </c>
       <c r="G60" t="n">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="H60" t="n">
-        <v>3.8</v>
+        <v>32.2</v>
       </c>
       <c r="I60" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-51.9</v>
+        <v>-46.69</v>
       </c>
       <c r="K60" t="n">
-        <v>-35.79</v>
+        <v>34.51</v>
       </c>
       <c r="L60" t="n">
-        <v>63.04</v>
+        <v>58.06</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:21:35</t>
+          <t>08:29:50</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.06</v>
+        <v>2.98</v>
       </c>
       <c r="F61" t="n">
-        <v>5.29</v>
+        <v>7.83</v>
       </c>
       <c r="G61" t="n">
-        <v>79.59999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="H61" t="n">
-        <v>2.7</v>
+        <v>21.6</v>
       </c>
       <c r="I61" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-42.9</v>
+        <v>-42.65</v>
       </c>
       <c r="K61" t="n">
-        <v>-24.86</v>
+        <v>-29.69</v>
       </c>
       <c r="L61" t="n">
-        <v>49.58</v>
+        <v>51.97</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:26:20</t>
+          <t>08:34:50</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.7</v>
+        <v>3.55</v>
       </c>
       <c r="F62" t="n">
-        <v>8.970000000000001</v>
+        <v>6.97</v>
       </c>
       <c r="G62" t="n">
-        <v>79.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="H62" t="n">
-        <v>2.8</v>
+        <v>16.8</v>
       </c>
       <c r="I62" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-6.78</v>
+        <v>-72.06999999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>-57.52</v>
+        <v>34.32</v>
       </c>
       <c r="L62" t="n">
-        <v>57.92</v>
+        <v>79.81999999999999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:28:28</t>
+          <t>08:36:16</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.13</v>
+        <v>2.82</v>
       </c>
       <c r="F63" t="n">
-        <v>7.48</v>
+        <v>8.59</v>
       </c>
       <c r="G63" t="n">
-        <v>91.3</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="I63" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>-33.04</v>
+        <v>35.12</v>
       </c>
       <c r="K63" t="n">
-        <v>-51.7</v>
+        <v>-63.7</v>
       </c>
       <c r="L63" t="n">
-        <v>61.36</v>
+        <v>72.73999999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:30:20</t>
+          <t>08:37:35</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>3.19</v>
+        <v>2.58</v>
       </c>
       <c r="F64" t="n">
-        <v>8.970000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="G64" t="n">
-        <v>91.3</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="H64" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="I64" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-34.58</v>
+        <v>71.52</v>
       </c>
       <c r="K64" t="n">
-        <v>-46.34</v>
+        <v>-31.95</v>
       </c>
       <c r="L64" t="n">
-        <v>57.82</v>
+        <v>78.34</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:34:40</t>
+          <t>08:42:59</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.55</v>
+        <v>2.89</v>
       </c>
       <c r="F65" t="n">
-        <v>8.75</v>
+        <v>7.72</v>
       </c>
       <c r="G65" t="n">
-        <v>97.7</v>
+        <v>108.1</v>
       </c>
       <c r="H65" t="n">
-        <v>3.8</v>
+        <v>20</v>
       </c>
       <c r="I65" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-70.62</v>
+        <v>-3.23</v>
       </c>
       <c r="K65" t="n">
-        <v>-76.95</v>
+        <v>93.31</v>
       </c>
       <c r="L65" t="n">
-        <v>104.45</v>
+        <v>93.37</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:37:02</t>
+          <t>08:43:41</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.34</v>
+        <v>3.07</v>
       </c>
       <c r="F66" t="n">
-        <v>8.09</v>
+        <v>3.98</v>
       </c>
       <c r="G66" t="n">
-        <v>93.09999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="H66" t="n">
-        <v>3.9</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-64.78</v>
+        <v>77.73</v>
       </c>
       <c r="K66" t="n">
-        <v>30.46</v>
+        <v>97.53</v>
       </c>
       <c r="L66" t="n">
-        <v>71.58</v>
+        <v>124.72</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:38:48</t>
+          <t>08:45:21</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.12</v>
+        <v>3.38</v>
       </c>
       <c r="F67" t="n">
-        <v>8.1</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G67" t="n">
-        <v>104.5</v>
+        <v>84</v>
       </c>
       <c r="H67" t="n">
-        <v>7.5</v>
+        <v>33.3</v>
       </c>
       <c r="I67" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-94.92</v>
+        <v>118.47</v>
       </c>
       <c r="K67" t="n">
-        <v>-59.36</v>
+        <v>2.75</v>
       </c>
       <c r="L67" t="n">
-        <v>111.95</v>
+        <v>118.5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:43:45</t>
+          <t>08:50:31</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.82</v>
+        <v>3.31</v>
       </c>
       <c r="F68" t="n">
-        <v>6.95</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G68" t="n">
-        <v>84</v>
+        <v>114.5</v>
       </c>
       <c r="H68" t="n">
-        <v>8.1</v>
+        <v>48.3</v>
       </c>
       <c r="I68" t="n">
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>76.41</v>
+        <v>229.95</v>
       </c>
       <c r="K68" t="n">
-        <v>78.56</v>
+        <v>0.68</v>
       </c>
       <c r="L68" t="n">
-        <v>109.59</v>
+        <v>229.96</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:44:50</t>
+          <t>08:51:54</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.44</v>
+        <v>2.73</v>
       </c>
       <c r="F69" t="n">
-        <v>6.3</v>
+        <v>7.11</v>
       </c>
       <c r="G69" t="n">
-        <v>93.3</v>
+        <v>107.1</v>
       </c>
       <c r="H69" t="n">
-        <v>9.300000000000001</v>
+        <v>31.4</v>
       </c>
       <c r="I69" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-79.79000000000001</v>
+        <v>113.81</v>
       </c>
       <c r="K69" t="n">
-        <v>84.67</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="L69" t="n">
-        <v>116.34</v>
+        <v>141.79</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:46:40</t>
+          <t>08:53:58</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.47</v>
+        <v>3.13</v>
       </c>
       <c r="F70" t="n">
         <v>8.970000000000001</v>
       </c>
       <c r="G70" t="n">
-        <v>96.7</v>
+        <v>92.8</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>42.7</v>
       </c>
       <c r="I70" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>-3.64</v>
+        <v>-69.87</v>
       </c>
       <c r="K70" t="n">
-        <v>-163.9</v>
+        <v>151.93</v>
       </c>
       <c r="L70" t="n">
-        <v>163.94</v>
+        <v>167.23</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:50:10</t>
+          <t>08:59:50</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="F71" t="n">
-        <v>5.37</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="G71" t="n">
-        <v>111.5</v>
+        <v>85.8</v>
       </c>
       <c r="H71" t="n">
-        <v>3.7</v>
+        <v>29.5</v>
       </c>
       <c r="I71" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J71" t="n">
-        <v>113.51</v>
+        <v>241.96</v>
       </c>
       <c r="K71" t="n">
-        <v>84.43000000000001</v>
+        <v>79.78</v>
       </c>
       <c r="L71" t="n">
-        <v>141.46</v>
+        <v>254.77</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:51:47</t>
+          <t>09:01:03</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.23</v>
+        <v>3.45</v>
       </c>
       <c r="F72" t="n">
-        <v>7.23</v>
+        <v>6.19</v>
       </c>
       <c r="G72" t="n">
-        <v>97.3</v>
+        <v>86</v>
       </c>
       <c r="H72" t="n">
-        <v>2.1</v>
+        <v>80.5</v>
       </c>
       <c r="I72" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>201.99</v>
+        <v>230.73</v>
       </c>
       <c r="K72" t="n">
-        <v>-54.02</v>
+        <v>-119.93</v>
       </c>
       <c r="L72" t="n">
-        <v>209.09</v>
+        <v>260.03</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:53:04</t>
+          <t>09:02:53</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.63</v>
+        <v>3.11</v>
       </c>
       <c r="F73" t="n">
-        <v>8.039999999999999</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G73" t="n">
-        <v>108.6</v>
+        <v>101.2</v>
       </c>
       <c r="H73" t="n">
-        <v>3</v>
+        <v>60.2</v>
       </c>
       <c r="I73" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>-6.42</v>
+        <v>-38.32</v>
       </c>
       <c r="K73" t="n">
-        <v>197.8</v>
+        <v>214.36</v>
       </c>
       <c r="L73" t="n">
-        <v>197.91</v>
+        <v>217.75</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:04:28</t>
+          <t>09:14:29</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.63</v>
+        <v>3.07</v>
       </c>
       <c r="F74" t="n">
-        <v>8.970000000000001</v>
+        <v>3.87</v>
       </c>
       <c r="G74" t="n">
-        <v>101.9</v>
+        <v>95.8</v>
       </c>
       <c r="H74" t="n">
-        <v>6.6</v>
+        <v>36.5</v>
       </c>
       <c r="I74" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>-38.02</v>
+        <v>-56.63</v>
       </c>
       <c r="K74" t="n">
-        <v>51.54</v>
+        <v>-8.81</v>
       </c>
       <c r="L74" t="n">
-        <v>64.04000000000001</v>
+        <v>57.31</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:06:39</t>
+          <t>09:16:14</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.83</v>
+        <v>3.28</v>
       </c>
       <c r="F75" t="n">
-        <v>8.5</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G75" t="n">
-        <v>100</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="H75" t="n">
-        <v>2.5</v>
+        <v>40.8</v>
       </c>
       <c r="I75" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>30.9</v>
+        <v>3.28</v>
       </c>
       <c r="K75" t="n">
-        <v>-41.12</v>
+        <v>59.43</v>
       </c>
       <c r="L75" t="n">
-        <v>51.44</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:08:28</t>
+          <t>09:17:56</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.3</v>
+        <v>2.77</v>
       </c>
       <c r="F76" t="n">
-        <v>8.970000000000001</v>
+        <v>7.75</v>
       </c>
       <c r="G76" t="n">
-        <v>99.8</v>
+        <v>107.4</v>
       </c>
       <c r="H76" t="n">
-        <v>2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>-65.65000000000001</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>-44.84</v>
+        <v>44.55</v>
       </c>
       <c r="L76" t="n">
-        <v>79.5</v>
+        <v>45.56</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:12:01</t>
+          <t>09:23:58</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.58</v>
+        <v>3.63</v>
       </c>
       <c r="F77" t="n">
         <v>8.970000000000001</v>
       </c>
       <c r="G77" t="n">
-        <v>96.2</v>
+        <v>106.1</v>
       </c>
       <c r="H77" t="n">
-        <v>0.7</v>
+        <v>54.4</v>
       </c>
       <c r="I77" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J77" t="n">
-        <v>56.07</v>
+        <v>79.13</v>
       </c>
       <c r="K77" t="n">
-        <v>31.25</v>
+        <v>-47.45</v>
       </c>
       <c r="L77" t="n">
-        <v>64.2</v>
+        <v>92.27</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:14:22</t>
+          <t>09:25:07</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.47</v>
+        <v>3.01</v>
       </c>
       <c r="F78" t="n">
         <v>8.970000000000001</v>
       </c>
       <c r="G78" t="n">
-        <v>103.7</v>
+        <v>118.1</v>
       </c>
       <c r="H78" t="n">
-        <v>5.3</v>
+        <v>24.5</v>
       </c>
       <c r="I78" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-23.15</v>
+        <v>-37.24</v>
       </c>
       <c r="K78" t="n">
-        <v>-58.38</v>
+        <v>40.75</v>
       </c>
       <c r="L78" t="n">
-        <v>62.8</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:16:56</t>
+          <t>09:27:07</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.95</v>
+        <v>3.32</v>
       </c>
       <c r="F79" t="n">
-        <v>8.84</v>
+        <v>7.08</v>
       </c>
       <c r="G79" t="n">
-        <v>100.5</v>
+        <v>92.5</v>
       </c>
       <c r="H79" t="n">
-        <v>3.4</v>
+        <v>35.3</v>
       </c>
       <c r="I79" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-61.72</v>
+        <v>-51.81</v>
       </c>
       <c r="K79" t="n">
-        <v>-14.69</v>
+        <v>-53.97</v>
       </c>
       <c r="L79" t="n">
-        <v>63.45</v>
+        <v>74.81999999999999</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:20:46</t>
+          <t>09:30:27</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="F80" t="n">
         <v>8.970000000000001</v>
       </c>
       <c r="G80" t="n">
-        <v>112.8</v>
+        <v>100.9</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="I80" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>77.47</v>
+        <v>101.86</v>
       </c>
       <c r="K80" t="n">
-        <v>81.63</v>
+        <v>17.1</v>
       </c>
       <c r="L80" t="n">
-        <v>112.54</v>
+        <v>103.29</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:22:57</t>
+          <t>09:31:46</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>3.38</v>
+        <v>2.83</v>
       </c>
       <c r="F81" t="n">
-        <v>8.970000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="G81" t="n">
-        <v>89.8</v>
+        <v>104.5</v>
       </c>
       <c r="H81" t="n">
-        <v>1.1</v>
+        <v>25.9</v>
       </c>
       <c r="I81" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J81" t="n">
-        <v>-24.5</v>
+        <v>-71.06</v>
       </c>
       <c r="K81" t="n">
-        <v>101.25</v>
+        <v>-66.91</v>
       </c>
       <c r="L81" t="n">
-        <v>104.17</v>
+        <v>97.59999999999999</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:25:12</t>
+          <t>09:33:47</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.13</v>
+        <v>3.26</v>
       </c>
       <c r="F82" t="n">
         <v>8.970000000000001</v>
       </c>
       <c r="G82" t="n">
-        <v>111.8</v>
+        <v>98.5</v>
       </c>
       <c r="H82" t="n">
-        <v>13.7</v>
+        <v>52.6</v>
       </c>
       <c r="I82" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>75.83</v>
+        <v>-107.76</v>
       </c>
       <c r="K82" t="n">
-        <v>23.59</v>
+        <v>-26.02</v>
       </c>
       <c r="L82" t="n">
-        <v>79.41</v>
+        <v>110.86</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:29:08</t>
+          <t>09:39:36</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="F83" t="n">
-        <v>8.970000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="G83" t="n">
-        <v>85.59999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="I83" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>-64.55</v>
+        <v>-93.62</v>
       </c>
       <c r="K83" t="n">
-        <v>-102.42</v>
+        <v>57.19</v>
       </c>
       <c r="L83" t="n">
-        <v>121.07</v>
+        <v>109.71</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:30:57</t>
+          <t>09:41:25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="F84" t="n">
         <v>8.970000000000001</v>
       </c>
       <c r="G84" t="n">
-        <v>105.9</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="H84" t="n">
-        <v>1</v>
+        <v>56.1</v>
       </c>
       <c r="I84" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>71.75</v>
+        <v>84.34</v>
       </c>
       <c r="K84" t="n">
-        <v>21.73</v>
+        <v>120.53</v>
       </c>
       <c r="L84" t="n">
-        <v>74.97</v>
+        <v>147.11</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:31:57</t>
+          <t>09:42:57</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.86</v>
+        <v>3.45</v>
       </c>
       <c r="F85" t="n">
         <v>8.970000000000001</v>
       </c>
       <c r="G85" t="n">
-        <v>84.40000000000001</v>
+        <v>104.8</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="I85" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>131.64</v>
+        <v>6.31</v>
       </c>
       <c r="K85" t="n">
-        <v>19.58</v>
+        <v>-224.01</v>
       </c>
       <c r="L85" t="n">
-        <v>133.09</v>
+        <v>224.1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:37:36</t>
+          <t>09:48:26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="F86" t="n">
-        <v>7.37</v>
+        <v>7.48</v>
       </c>
       <c r="G86" t="n">
-        <v>104.1</v>
+        <v>94.3</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>48.4</v>
       </c>
       <c r="I86" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>-98.13</v>
+        <v>-131.13</v>
       </c>
       <c r="K86" t="n">
-        <v>97.20999999999999</v>
+        <v>-91.86</v>
       </c>
       <c r="L86" t="n">
-        <v>138.13</v>
+        <v>160.11</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:39:06</t>
+          <t>09:49:41</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="F87" t="n">
         <v>8.970000000000001</v>
       </c>
       <c r="G87" t="n">
-        <v>82.90000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="H87" t="n">
-        <v>2.4</v>
+        <v>32.1</v>
       </c>
       <c r="I87" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>121.37</v>
+        <v>-255.62</v>
       </c>
       <c r="K87" t="n">
-        <v>191.37</v>
+        <v>83.69</v>
       </c>
       <c r="L87" t="n">
-        <v>226.61</v>
+        <v>268.97</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:40:21</t>
+          <t>09:50:36</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.03</v>
+        <v>3.14</v>
       </c>
       <c r="F88" t="n">
-        <v>8.23</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="G88" t="n">
-        <v>97.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H88" t="n">
-        <v>2.9</v>
+        <v>57.3</v>
       </c>
       <c r="I88" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>-123.33</v>
+        <v>211.03</v>
       </c>
       <c r="K88" t="n">
-        <v>58.46</v>
+        <v>-101.91</v>
       </c>
       <c r="L88" t="n">
-        <v>136.48</v>
+        <v>234.35</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-08-21.xlsx
+++ b/output/2024-08-21.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="F14" t="n">
-        <v>3.41</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>111.4</v>
+        <v>96.7</v>
       </c>
       <c r="H14" t="n">
-        <v>37.4</v>
+        <v>56.4</v>
       </c>
       <c r="I14" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>24.63</v>
+        <v>30.18</v>
       </c>
       <c r="K14" t="n">
-        <v>-34.35</v>
+        <v>-31.12</v>
       </c>
       <c r="L14" t="n">
-        <v>42.26</v>
+        <v>43.35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:01:04</t>
+          <t>06:00:30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.54</v>
+        <v>3.05</v>
       </c>
       <c r="F15" t="n">
-        <v>6.66</v>
+        <v>3.35</v>
       </c>
       <c r="G15" t="n">
-        <v>101.6</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>43.5</v>
+        <v>38</v>
       </c>
       <c r="I15" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="J15" t="n">
-        <v>9.5</v>
+        <v>38.13</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.11</v>
+        <v>-14.62</v>
       </c>
       <c r="L15" t="n">
-        <v>10.79</v>
+        <v>40.84</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:03:27</t>
+          <t>06:02:27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="F16" t="n">
-        <v>6.03</v>
+        <v>6.63</v>
       </c>
       <c r="G16" t="n">
-        <v>88.5</v>
+        <v>101.5</v>
       </c>
       <c r="H16" t="n">
-        <v>50.4</v>
+        <v>45.8</v>
       </c>
       <c r="I16" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J16" t="n">
-        <v>13.21</v>
+        <v>31.77</v>
       </c>
       <c r="K16" t="n">
-        <v>36.45</v>
+        <v>-34.26</v>
       </c>
       <c r="L16" t="n">
-        <v>38.77</v>
+        <v>46.72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:07:33</t>
+          <t>06:07:15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.67</v>
+        <v>2.53</v>
       </c>
       <c r="F17" t="n">
-        <v>3.48</v>
+        <v>4.33</v>
       </c>
       <c r="G17" t="n">
-        <v>100.4</v>
+        <v>93.2</v>
       </c>
       <c r="H17" t="n">
-        <v>81.8</v>
+        <v>35.9</v>
       </c>
       <c r="I17" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J17" t="n">
-        <v>78.31999999999999</v>
+        <v>-32.79</v>
       </c>
       <c r="K17" t="n">
-        <v>-14.98</v>
+        <v>18.3</v>
       </c>
       <c r="L17" t="n">
-        <v>79.73999999999999</v>
+        <v>37.55</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:08:34</t>
+          <t>06:08:44</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.51</v>
+        <v>2.86</v>
       </c>
       <c r="F18" t="n">
-        <v>7.7</v>
+        <v>5.63</v>
       </c>
       <c r="G18" t="n">
-        <v>84</v>
+        <v>103.6</v>
       </c>
       <c r="H18" t="n">
-        <v>56.6</v>
+        <v>41.6</v>
       </c>
       <c r="I18" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>54.82</v>
+        <v>50.3</v>
       </c>
       <c r="K18" t="n">
-        <v>16.88</v>
+        <v>19.16</v>
       </c>
       <c r="L18" t="n">
-        <v>57.36</v>
+        <v>53.83</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:09:51</t>
+          <t>06:11:07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="F19" t="n">
-        <v>4.93</v>
+        <v>4.58</v>
       </c>
       <c r="G19" t="n">
-        <v>100.8</v>
+        <v>103.2</v>
       </c>
       <c r="H19" t="n">
-        <v>41.4</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>15.28</v>
+        <v>54.18</v>
       </c>
       <c r="K19" t="n">
-        <v>-73.56</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>75.13</v>
+        <v>55.02</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:14:57</t>
+          <t>06:15:47</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.23</v>
+        <v>2.71</v>
       </c>
       <c r="F20" t="n">
-        <v>5.72</v>
+        <v>5.78</v>
       </c>
       <c r="G20" t="n">
-        <v>84.3</v>
+        <v>108.7</v>
       </c>
       <c r="H20" t="n">
-        <v>48.3</v>
+        <v>45.4</v>
       </c>
       <c r="I20" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J20" t="n">
-        <v>8.16</v>
+        <v>-91.95999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>-86.09999999999999</v>
+        <v>-11.23</v>
       </c>
       <c r="L20" t="n">
-        <v>86.48999999999999</v>
+        <v>92.65000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:17:02</t>
+          <t>06:17:23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.98</v>
+        <v>2.47</v>
       </c>
       <c r="F21" t="n">
-        <v>7.11</v>
+        <v>7.7</v>
       </c>
       <c r="G21" t="n">
-        <v>98.09999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="H21" t="n">
-        <v>37.2</v>
+        <v>61.6</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>74.05</v>
+        <v>48.15</v>
       </c>
       <c r="K21" t="n">
-        <v>-66.01000000000001</v>
+        <v>-60.55</v>
       </c>
       <c r="L21" t="n">
-        <v>99.2</v>
+        <v>77.36</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:19:51</t>
+          <t>06:18:05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="F22" t="n">
-        <v>3.8</v>
+        <v>8.69</v>
       </c>
       <c r="G22" t="n">
-        <v>93.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>30.9</v>
+        <v>11</v>
       </c>
       <c r="I22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-94.98</v>
+        <v>-74.72</v>
       </c>
       <c r="K22" t="n">
-        <v>-52.75</v>
+        <v>-1.28</v>
       </c>
       <c r="L22" t="n">
-        <v>108.65</v>
+        <v>74.73</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:25:11</t>
+          <t>06:22:34</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.13</v>
+        <v>2.67</v>
       </c>
       <c r="F23" t="n">
-        <v>8.49</v>
+        <v>8.18</v>
       </c>
       <c r="G23" t="n">
-        <v>96.3</v>
+        <v>87.2</v>
       </c>
       <c r="H23" t="n">
-        <v>51.7</v>
+        <v>42.7</v>
       </c>
       <c r="I23" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J23" t="n">
-        <v>-45.38</v>
+        <v>-16.01</v>
       </c>
       <c r="K23" t="n">
-        <v>124.18</v>
+        <v>125.51</v>
       </c>
       <c r="L23" t="n">
-        <v>132.21</v>
+        <v>126.52</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:26:31</t>
+          <t>06:25:08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="F24" t="n">
-        <v>6.05</v>
+        <v>7.11</v>
       </c>
       <c r="G24" t="n">
-        <v>105.8</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>50.3</v>
+        <v>40</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>153.91</v>
+        <v>19.78</v>
       </c>
       <c r="K24" t="n">
-        <v>101.53</v>
+        <v>-145.01</v>
       </c>
       <c r="L24" t="n">
-        <v>184.38</v>
+        <v>146.36</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:28:25</t>
+          <t>06:26:46</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>7.38</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>88.40000000000001</v>
+        <v>99</v>
       </c>
       <c r="H25" t="n">
-        <v>38.5</v>
+        <v>13.9</v>
       </c>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J25" t="n">
-        <v>-99.94</v>
+        <v>45.14</v>
       </c>
       <c r="K25" t="n">
-        <v>-111.21</v>
+        <v>-169.93</v>
       </c>
       <c r="L25" t="n">
-        <v>149.52</v>
+        <v>175.83</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:33:05</t>
+          <t>06:32:34</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="F26" t="n">
-        <v>4.41</v>
+        <v>6.53</v>
       </c>
       <c r="G26" t="n">
-        <v>103.8</v>
+        <v>105.2</v>
       </c>
       <c r="H26" t="n">
-        <v>15.2</v>
+        <v>35.6</v>
       </c>
       <c r="I26" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J26" t="n">
-        <v>11.36</v>
+        <v>-167.73</v>
       </c>
       <c r="K26" t="n">
-        <v>-37.59</v>
+        <v>126.7</v>
       </c>
       <c r="L26" t="n">
-        <v>39.27</v>
+        <v>210.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:35:10</t>
+          <t>06:34:14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.91</v>
+        <v>2.84</v>
       </c>
       <c r="F27" t="n">
-        <v>8.800000000000001</v>
+        <v>7.35</v>
       </c>
       <c r="G27" t="n">
-        <v>96.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>44</v>
+        <v>50.7</v>
       </c>
       <c r="I27" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>53.96</v>
+        <v>60.79</v>
       </c>
       <c r="K27" t="n">
-        <v>-266.2</v>
+        <v>153.63</v>
       </c>
       <c r="L27" t="n">
-        <v>271.61</v>
+        <v>165.22</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:36:39</t>
+          <t>06:35:15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.76</v>
+        <v>2.97</v>
       </c>
       <c r="F28" t="n">
-        <v>6.67</v>
+        <v>5.96</v>
       </c>
       <c r="G28" t="n">
-        <v>88.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>15.9</v>
+        <v>76</v>
       </c>
       <c r="I28" t="n">
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>95.76000000000001</v>
+        <v>-247.45</v>
       </c>
       <c r="K28" t="n">
-        <v>203.59</v>
+        <v>112.29</v>
       </c>
       <c r="L28" t="n">
-        <v>224.99</v>
+        <v>271.73</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:49:20</t>
+          <t>06:48:21</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.17</v>
+        <v>2.73</v>
       </c>
       <c r="F29" t="n">
-        <v>8.199999999999999</v>
+        <v>6.49</v>
       </c>
       <c r="G29" t="n">
-        <v>97</v>
+        <v>116.3</v>
       </c>
       <c r="H29" t="n">
-        <v>35.2</v>
+        <v>42.6</v>
       </c>
       <c r="I29" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J29" t="n">
-        <v>44.57</v>
+        <v>42.41</v>
       </c>
       <c r="K29" t="n">
-        <v>-87.61</v>
+        <v>-26.31</v>
       </c>
       <c r="L29" t="n">
-        <v>98.3</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:51:03</t>
+          <t>06:49:45</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.09</v>
+        <v>3.01</v>
       </c>
       <c r="F30" t="n">
-        <v>8.6</v>
+        <v>8.43</v>
       </c>
       <c r="G30" t="n">
-        <v>82.8</v>
+        <v>101.6</v>
       </c>
       <c r="H30" t="n">
-        <v>34.7</v>
+        <v>34.5</v>
       </c>
       <c r="I30" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J30" t="n">
-        <v>-41.13</v>
+        <v>14.24</v>
       </c>
       <c r="K30" t="n">
-        <v>35.85</v>
+        <v>-57.74</v>
       </c>
       <c r="L30" t="n">
-        <v>54.57</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:51:40</t>
+          <t>06:50:53</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.63</v>
+        <v>2.76</v>
       </c>
       <c r="F31" t="n">
-        <v>6.7</v>
+        <v>6.59</v>
       </c>
       <c r="G31" t="n">
-        <v>95.59999999999999</v>
+        <v>114.1</v>
       </c>
       <c r="H31" t="n">
-        <v>40.4</v>
+        <v>55.5</v>
       </c>
       <c r="I31" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J31" t="n">
-        <v>32.79</v>
+        <v>-32.55</v>
       </c>
       <c r="K31" t="n">
-        <v>-33.18</v>
+        <v>-26.56</v>
       </c>
       <c r="L31" t="n">
-        <v>46.65</v>
+        <v>42.01</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:56:59</t>
+          <t>06:55:55</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="F32" t="n">
-        <v>7.87</v>
+        <v>6.77</v>
       </c>
       <c r="G32" t="n">
-        <v>95</v>
+        <v>104.1</v>
       </c>
       <c r="H32" t="n">
-        <v>20.4</v>
+        <v>56.1</v>
       </c>
       <c r="I32" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J32" t="n">
-        <v>-43.63</v>
+        <v>45.43</v>
       </c>
       <c r="K32" t="n">
-        <v>57.76</v>
+        <v>-47.33</v>
       </c>
       <c r="L32" t="n">
-        <v>72.39</v>
+        <v>65.61</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:58:15</t>
+          <t>06:57:11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.2</v>
+        <v>2.77</v>
       </c>
       <c r="F33" t="n">
-        <v>6.36</v>
+        <v>7.91</v>
       </c>
       <c r="G33" t="n">
-        <v>87.8</v>
+        <v>98</v>
       </c>
       <c r="H33" t="n">
-        <v>27.5</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>50.45</v>
+        <v>-39.59</v>
       </c>
       <c r="K33" t="n">
-        <v>42.46</v>
+        <v>49.64</v>
       </c>
       <c r="L33" t="n">
-        <v>65.94</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:00:30</t>
+          <t>06:59:40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.65</v>
+        <v>2.79</v>
       </c>
       <c r="F34" t="n">
-        <v>8.960000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="G34" t="n">
-        <v>95.2</v>
+        <v>100.7</v>
       </c>
       <c r="H34" t="n">
-        <v>58.9</v>
+        <v>39.7</v>
       </c>
       <c r="I34" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J34" t="n">
-        <v>-65.06999999999999</v>
+        <v>-60</v>
       </c>
       <c r="K34" t="n">
-        <v>-32.42</v>
+        <v>-47.88</v>
       </c>
       <c r="L34" t="n">
-        <v>72.7</v>
+        <v>76.76000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:06:20</t>
+          <t>07:04:23</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="F35" t="n">
-        <v>8.81</v>
+        <v>8.24</v>
       </c>
       <c r="G35" t="n">
-        <v>93.90000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="H35" t="n">
-        <v>24.1</v>
+        <v>37.3</v>
       </c>
       <c r="I35" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>96.22</v>
+        <v>-47.61</v>
       </c>
       <c r="K35" t="n">
-        <v>-17.3</v>
+        <v>-71.68000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>97.77</v>
+        <v>86.05</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:08:23</t>
+          <t>07:06:26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.68</v>
+        <v>2.26</v>
       </c>
       <c r="F36" t="n">
-        <v>8.91</v>
+        <v>5.02</v>
       </c>
       <c r="G36" t="n">
-        <v>111.5</v>
+        <v>93.8</v>
       </c>
       <c r="H36" t="n">
-        <v>36.8</v>
+        <v>0.6</v>
       </c>
       <c r="I36" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J36" t="n">
-        <v>82.5</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>-48.19</v>
+        <v>-15.28</v>
       </c>
       <c r="L36" t="n">
-        <v>95.54000000000001</v>
+        <v>77.95</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:09:47</t>
+          <t>07:08:31</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="F37" t="n">
-        <v>7.29</v>
+        <v>7.67</v>
       </c>
       <c r="G37" t="n">
-        <v>99.40000000000001</v>
+        <v>102.1</v>
       </c>
       <c r="H37" t="n">
-        <v>13.5</v>
+        <v>29.8</v>
       </c>
       <c r="I37" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J37" t="n">
-        <v>60.57</v>
+        <v>-87.86</v>
       </c>
       <c r="K37" t="n">
-        <v>51.92</v>
+        <v>27.48</v>
       </c>
       <c r="L37" t="n">
-        <v>79.77</v>
+        <v>92.06</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:14:14</t>
+          <t>07:14:13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.54</v>
+        <v>2.96</v>
       </c>
       <c r="F38" t="n">
-        <v>7.42</v>
+        <v>5.73</v>
       </c>
       <c r="G38" t="n">
-        <v>88.90000000000001</v>
+        <v>101.6</v>
       </c>
       <c r="H38" t="n">
-        <v>69.5</v>
+        <v>28.1</v>
       </c>
       <c r="I38" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J38" t="n">
-        <v>-80.11</v>
+        <v>53.64</v>
       </c>
       <c r="K38" t="n">
-        <v>58.92</v>
+        <v>122.41</v>
       </c>
       <c r="L38" t="n">
-        <v>99.45</v>
+        <v>133.64</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:16:15</t>
+          <t>07:16:29</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.22</v>
+        <v>2.67</v>
       </c>
       <c r="F39" t="n">
-        <v>8.6</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>93.5</v>
+        <v>96.8</v>
       </c>
       <c r="H39" t="n">
-        <v>35.1</v>
+        <v>59.2</v>
       </c>
       <c r="I39" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>-81.91</v>
+        <v>-111.7</v>
       </c>
       <c r="K39" t="n">
-        <v>-134.03</v>
+        <v>23.21</v>
       </c>
       <c r="L39" t="n">
-        <v>157.07</v>
+        <v>114.08</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:18:16</t>
+          <t>07:17:33</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.16</v>
+        <v>3.86</v>
       </c>
       <c r="F40" t="n">
-        <v>5.37</v>
+        <v>8.83</v>
       </c>
       <c r="G40" t="n">
-        <v>89.09999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="H40" t="n">
-        <v>58.3</v>
+        <v>45</v>
       </c>
       <c r="I40" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J40" t="n">
-        <v>134.64</v>
+        <v>-61.78</v>
       </c>
       <c r="K40" t="n">
-        <v>71.36</v>
+        <v>203.31</v>
       </c>
       <c r="L40" t="n">
-        <v>152.38</v>
+        <v>212.49</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:24:32</t>
+          <t>07:21:21</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="F41" t="n">
-        <v>6.75</v>
+        <v>6.47</v>
       </c>
       <c r="G41" t="n">
-        <v>103.8</v>
+        <v>96.3</v>
       </c>
       <c r="H41" t="n">
-        <v>27.5</v>
+        <v>44</v>
       </c>
       <c r="I41" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>144.55</v>
+        <v>-25.42</v>
       </c>
       <c r="K41" t="n">
-        <v>155.13</v>
+        <v>-195.91</v>
       </c>
       <c r="L41" t="n">
-        <v>212.03</v>
+        <v>197.55</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:26:44</t>
+          <t>07:22:22</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.31</v>
+        <v>2.9</v>
       </c>
       <c r="F42" t="n">
-        <v>8.35</v>
+        <v>7.26</v>
       </c>
       <c r="G42" t="n">
-        <v>109.6</v>
+        <v>88.8</v>
       </c>
       <c r="H42" t="n">
-        <v>35.8</v>
+        <v>15.9</v>
       </c>
       <c r="I42" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J42" t="n">
-        <v>49.89</v>
+        <v>56.41</v>
       </c>
       <c r="K42" t="n">
-        <v>229.36</v>
+        <v>227.28</v>
       </c>
       <c r="L42" t="n">
-        <v>234.73</v>
+        <v>234.17</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:28:20</t>
+          <t>07:23:29</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.94</v>
+        <v>3.27</v>
       </c>
       <c r="F43" t="n">
-        <v>8.130000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="G43" t="n">
-        <v>81.2</v>
+        <v>97</v>
       </c>
       <c r="H43" t="n">
-        <v>39</v>
+        <v>35.2</v>
       </c>
       <c r="I43" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J43" t="n">
-        <v>193.47</v>
+        <v>98.55</v>
       </c>
       <c r="K43" t="n">
-        <v>77.52</v>
+        <v>-365.98</v>
       </c>
       <c r="L43" t="n">
-        <v>208.42</v>
+        <v>379.01</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:38:36</t>
+          <t>07:33:51</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.86</v>
+        <v>3.22</v>
       </c>
       <c r="F44" t="n">
-        <v>6.15</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G44" t="n">
-        <v>94.3</v>
+        <v>82.8</v>
       </c>
       <c r="H44" t="n">
-        <v>57.3</v>
+        <v>34.7</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J44" t="n">
-        <v>-51.08</v>
+        <v>-48.04</v>
       </c>
       <c r="K44" t="n">
-        <v>24.49</v>
+        <v>30.02</v>
       </c>
       <c r="L44" t="n">
-        <v>56.64</v>
+        <v>56.65</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:40:01</t>
+          <t>07:36:02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="F45" t="n">
-        <v>6.36</v>
+        <v>7.25</v>
       </c>
       <c r="G45" t="n">
-        <v>92.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>40.6</v>
+        <v>40.4</v>
       </c>
       <c r="I45" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J45" t="n">
-        <v>12.91</v>
+        <v>29.27</v>
       </c>
       <c r="K45" t="n">
-        <v>35.2</v>
+        <v>-39.37</v>
       </c>
       <c r="L45" t="n">
-        <v>37.49</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:41:20</t>
+          <t>07:38:35</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.11</v>
+        <v>2.66</v>
       </c>
       <c r="F46" t="n">
-        <v>8.970000000000001</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>91.5</v>
+        <v>95</v>
       </c>
       <c r="H46" t="n">
-        <v>44.6</v>
+        <v>20.4</v>
       </c>
       <c r="I46" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J46" t="n">
-        <v>9.32</v>
+        <v>-32.84</v>
       </c>
       <c r="K46" t="n">
-        <v>33.05</v>
+        <v>32.92</v>
       </c>
       <c r="L46" t="n">
-        <v>34.34</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:45:28</t>
+          <t>07:42:41</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>3.04</v>
+        <v>2.32</v>
       </c>
       <c r="F47" t="n">
-        <v>5.77</v>
+        <v>6.85</v>
       </c>
       <c r="G47" t="n">
-        <v>102</v>
+        <v>87.8</v>
       </c>
       <c r="H47" t="n">
-        <v>46.2</v>
+        <v>27.5</v>
       </c>
       <c r="I47" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J47" t="n">
-        <v>45.14</v>
+        <v>46.23</v>
       </c>
       <c r="K47" t="n">
-        <v>-77.01000000000001</v>
+        <v>49.07</v>
       </c>
       <c r="L47" t="n">
-        <v>89.26000000000001</v>
+        <v>67.42</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:46:24</t>
+          <t>07:44:02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.93</v>
+        <v>2.78</v>
       </c>
       <c r="F48" t="n">
         <v>8.970000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>102</v>
+        <v>95.2</v>
       </c>
       <c r="H48" t="n">
-        <v>51.6</v>
+        <v>58.9</v>
       </c>
       <c r="I48" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J48" t="n">
-        <v>28.03</v>
+        <v>-69.94</v>
       </c>
       <c r="K48" t="n">
-        <v>61.28</v>
+        <v>-26.63</v>
       </c>
       <c r="L48" t="n">
-        <v>67.39</v>
+        <v>74.84</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:47:38</t>
+          <t>07:44:47</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.09</v>
+        <v>2.79</v>
       </c>
       <c r="F49" t="n">
-        <v>6.52</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G49" t="n">
-        <v>103.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>29.7</v>
+        <v>24.1</v>
       </c>
       <c r="I49" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J49" t="n">
-        <v>-78.06999999999999</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>40.77</v>
+        <v>-13.92</v>
       </c>
       <c r="L49" t="n">
-        <v>88.08</v>
+        <v>68.95999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:53:31</t>
+          <t>07:50:42</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="F50" t="n">
         <v>8.970000000000001</v>
       </c>
       <c r="G50" t="n">
-        <v>94.90000000000001</v>
+        <v>111.5</v>
       </c>
       <c r="H50" t="n">
-        <v>40.4</v>
+        <v>36.8</v>
       </c>
       <c r="I50" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J50" t="n">
-        <v>-77.48999999999999</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>44.92</v>
+        <v>-51.62</v>
       </c>
       <c r="L50" t="n">
-        <v>89.56999999999999</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:55:10</t>
+          <t>07:52:34</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="F51" t="n">
-        <v>8.18</v>
+        <v>7.81</v>
       </c>
       <c r="G51" t="n">
-        <v>107</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="H51" t="n">
-        <v>16.8</v>
+        <v>13.5</v>
       </c>
       <c r="I51" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J51" t="n">
-        <v>84.78</v>
+        <v>51.21</v>
       </c>
       <c r="K51" t="n">
-        <v>-11.78</v>
+        <v>61.93</v>
       </c>
       <c r="L51" t="n">
-        <v>85.59</v>
+        <v>80.36</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:57:00</t>
+          <t>07:54:51</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.76</v>
+        <v>2.65</v>
       </c>
       <c r="F52" t="n">
-        <v>5.59</v>
+        <v>7.89</v>
       </c>
       <c r="G52" t="n">
-        <v>92.8</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>71.09999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="I52" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J52" t="n">
-        <v>88.33</v>
+        <v>-61.5</v>
       </c>
       <c r="K52" t="n">
-        <v>75.90000000000001</v>
+        <v>35.43</v>
       </c>
       <c r="L52" t="n">
-        <v>116.46</v>
+        <v>70.97</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:03:03</t>
+          <t>07:59:09</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="F53" t="n">
-        <v>8.630000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G53" t="n">
-        <v>100</v>
+        <v>93.5</v>
       </c>
       <c r="H53" t="n">
-        <v>51.9</v>
+        <v>35.1</v>
       </c>
       <c r="I53" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>154.96</v>
+        <v>-120.02</v>
       </c>
       <c r="K53" t="n">
-        <v>127.75</v>
+        <v>-129.96</v>
       </c>
       <c r="L53" t="n">
-        <v>200.83</v>
+        <v>176.9</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:05:01</t>
+          <t>08:01:19</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.91</v>
+        <v>3.27</v>
       </c>
       <c r="F54" t="n">
-        <v>8.25</v>
+        <v>5.9</v>
       </c>
       <c r="G54" t="n">
-        <v>85.3</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="H54" t="n">
-        <v>34.5</v>
+        <v>58.3</v>
       </c>
       <c r="I54" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>136.24</v>
+        <v>139.96</v>
       </c>
       <c r="K54" t="n">
-        <v>-17</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>137.29</v>
+        <v>170.24</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:07:07</t>
+          <t>08:02:10</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.21</v>
+        <v>2.97</v>
       </c>
       <c r="F55" t="n">
-        <v>8.970000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="G55" t="n">
-        <v>90.7</v>
+        <v>103.8</v>
       </c>
       <c r="H55" t="n">
-        <v>77.59999999999999</v>
+        <v>27.5</v>
       </c>
       <c r="I55" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>173.91</v>
+        <v>-108.15</v>
       </c>
       <c r="K55" t="n">
-        <v>-20.52</v>
+        <v>142.34</v>
       </c>
       <c r="L55" t="n">
-        <v>175.11</v>
+        <v>178.76</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:12:22</t>
+          <t>08:05:35</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.07</v>
+        <v>2.77</v>
       </c>
       <c r="F56" t="n">
         <v>8.970000000000001</v>
       </c>
       <c r="G56" t="n">
-        <v>93.09999999999999</v>
+        <v>94.8</v>
       </c>
       <c r="H56" t="n">
-        <v>52.1</v>
+        <v>38.7</v>
       </c>
       <c r="I56" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J56" t="n">
-        <v>71.73</v>
+        <v>-61.34</v>
       </c>
       <c r="K56" t="n">
-        <v>-73.69</v>
+        <v>-208.96</v>
       </c>
       <c r="L56" t="n">
-        <v>102.84</v>
+        <v>217.78</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:14:45</t>
+          <t>08:07:04</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>3.2</v>
+        <v>3.88</v>
       </c>
       <c r="F57" t="n">
         <v>8.970000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>111.2</v>
+        <v>112.1</v>
       </c>
       <c r="H57" t="n">
-        <v>30.4</v>
+        <v>42.7</v>
       </c>
       <c r="I57" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J57" t="n">
-        <v>-211.16</v>
+        <v>131.18</v>
       </c>
       <c r="K57" t="n">
-        <v>-104.22</v>
+        <v>210.34</v>
       </c>
       <c r="L57" t="n">
-        <v>235.48</v>
+        <v>247.89</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:15:55</t>
+          <t>08:08:23</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.65</v>
+        <v>3.23</v>
       </c>
       <c r="F58" t="n">
-        <v>4.57</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>86</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>45.6</v>
+        <v>59.9</v>
       </c>
       <c r="I58" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>90.95999999999999</v>
+        <v>-69.02</v>
       </c>
       <c r="K58" t="n">
-        <v>145.78</v>
+        <v>-163.22</v>
       </c>
       <c r="L58" t="n">
-        <v>171.82</v>
+        <v>177.21</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:27:23</t>
+          <t>08:18:21</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.88</v>
+        <v>3.41</v>
       </c>
       <c r="F59" t="n">
-        <v>6.84</v>
+        <v>7.35</v>
       </c>
       <c r="G59" t="n">
-        <v>93.2</v>
+        <v>91.3</v>
       </c>
       <c r="H59" t="n">
-        <v>22.4</v>
+        <v>30.5</v>
       </c>
       <c r="I59" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-45.31</v>
+        <v>-17.92</v>
       </c>
       <c r="K59" t="n">
-        <v>21.49</v>
+        <v>-50.59</v>
       </c>
       <c r="L59" t="n">
-        <v>50.15</v>
+        <v>53.67</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:28:37</t>
+          <t>08:19:32</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.09</v>
+        <v>2.86</v>
       </c>
       <c r="F60" t="n">
         <v>8.970000000000001</v>
       </c>
       <c r="G60" t="n">
-        <v>98.2</v>
+        <v>105.1</v>
       </c>
       <c r="H60" t="n">
-        <v>32.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J60" t="n">
-        <v>-46.69</v>
+        <v>14.96</v>
       </c>
       <c r="K60" t="n">
-        <v>34.51</v>
+        <v>-41.14</v>
       </c>
       <c r="L60" t="n">
-        <v>58.06</v>
+        <v>43.78</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:29:50</t>
+          <t>08:21:00</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.98</v>
+        <v>3.21</v>
       </c>
       <c r="F61" t="n">
-        <v>7.83</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G61" t="n">
-        <v>95.7</v>
+        <v>97.3</v>
       </c>
       <c r="H61" t="n">
-        <v>21.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>-42.65</v>
+        <v>50.2</v>
       </c>
       <c r="K61" t="n">
-        <v>-29.69</v>
+        <v>-28.82</v>
       </c>
       <c r="L61" t="n">
-        <v>51.97</v>
+        <v>57.89</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:34:50</t>
+          <t>08:25:12</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.55</v>
+        <v>2.74</v>
       </c>
       <c r="F62" t="n">
-        <v>6.97</v>
+        <v>6.2</v>
       </c>
       <c r="G62" t="n">
-        <v>92.40000000000001</v>
+        <v>102.1</v>
       </c>
       <c r="H62" t="n">
-        <v>16.8</v>
+        <v>58.6</v>
       </c>
       <c r="I62" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J62" t="n">
-        <v>-72.06999999999999</v>
+        <v>-43.83</v>
       </c>
       <c r="K62" t="n">
-        <v>34.32</v>
+        <v>47</v>
       </c>
       <c r="L62" t="n">
-        <v>79.81999999999999</v>
+        <v>64.26000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:36:16</t>
+          <t>08:27:25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="F63" t="n">
-        <v>8.59</v>
+        <v>5.03</v>
       </c>
       <c r="G63" t="n">
-        <v>87.40000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="H63" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="I63" t="n">
         <v>31</v>
       </c>
-      <c r="I63" t="n">
-        <v>27</v>
-      </c>
       <c r="J63" t="n">
-        <v>35.12</v>
+        <v>-57.23</v>
       </c>
       <c r="K63" t="n">
-        <v>-63.7</v>
+        <v>-8.34</v>
       </c>
       <c r="L63" t="n">
-        <v>72.73999999999999</v>
+        <v>57.84</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:37:35</t>
+          <t>08:29:33</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.58</v>
+        <v>3.11</v>
       </c>
       <c r="F64" t="n">
-        <v>6.2</v>
+        <v>7.31</v>
       </c>
       <c r="G64" t="n">
-        <v>98.09999999999999</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="H64" t="n">
-        <v>23</v>
+        <v>75.3</v>
       </c>
       <c r="I64" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J64" t="n">
-        <v>71.52</v>
+        <v>-9.23</v>
       </c>
       <c r="K64" t="n">
-        <v>-31.95</v>
+        <v>-84.95999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>78.34</v>
+        <v>85.45999999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:42:59</t>
+          <t>08:35:10</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.89</v>
+        <v>2.68</v>
       </c>
       <c r="F65" t="n">
-        <v>7.72</v>
+        <v>4.78</v>
       </c>
       <c r="G65" t="n">
-        <v>108.1</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="H65" t="n">
-        <v>20</v>
+        <v>5.9</v>
       </c>
       <c r="I65" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J65" t="n">
-        <v>-3.23</v>
+        <v>91.41</v>
       </c>
       <c r="K65" t="n">
-        <v>93.31</v>
+        <v>-63.61</v>
       </c>
       <c r="L65" t="n">
-        <v>93.37</v>
+        <v>111.36</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:43:41</t>
+          <t>08:36:23</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.07</v>
+        <v>3.24</v>
       </c>
       <c r="F66" t="n">
-        <v>3.98</v>
+        <v>7.96</v>
       </c>
       <c r="G66" t="n">
-        <v>97.2</v>
+        <v>109.9</v>
       </c>
       <c r="H66" t="n">
-        <v>88.09999999999999</v>
+        <v>15.3</v>
       </c>
       <c r="I66" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>77.73</v>
+        <v>69.05</v>
       </c>
       <c r="K66" t="n">
-        <v>97.53</v>
+        <v>83.18000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>124.72</v>
+        <v>108.1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:45:21</t>
+          <t>08:37:52</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>3.38</v>
+        <v>2.75</v>
       </c>
       <c r="F67" t="n">
-        <v>8.970000000000001</v>
+        <v>4.81</v>
       </c>
       <c r="G67" t="n">
-        <v>84</v>
+        <v>102.2</v>
       </c>
       <c r="H67" t="n">
-        <v>33.3</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>118.47</v>
+        <v>9.99</v>
       </c>
       <c r="K67" t="n">
-        <v>2.75</v>
+        <v>86.04000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>118.5</v>
+        <v>86.62</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:50:31</t>
+          <t>08:40:41</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.31</v>
+        <v>3.09</v>
       </c>
       <c r="F68" t="n">
-        <v>8.699999999999999</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G68" t="n">
-        <v>114.5</v>
+        <v>95.2</v>
       </c>
       <c r="H68" t="n">
-        <v>48.3</v>
+        <v>43.1</v>
       </c>
       <c r="I68" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>229.95</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="K68" t="n">
-        <v>0.68</v>
+        <v>-83.56</v>
       </c>
       <c r="L68" t="n">
-        <v>229.96</v>
+        <v>118.73</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:51:54</t>
+          <t>08:41:55</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.73</v>
+        <v>3.37</v>
       </c>
       <c r="F69" t="n">
-        <v>7.11</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G69" t="n">
-        <v>107.1</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="H69" t="n">
-        <v>31.4</v>
+        <v>51.3</v>
       </c>
       <c r="I69" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>113.81</v>
+        <v>-99.62</v>
       </c>
       <c r="K69" t="n">
-        <v>84.56999999999999</v>
+        <v>-131.49</v>
       </c>
       <c r="L69" t="n">
-        <v>141.79</v>
+        <v>164.97</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:53:58</t>
+          <t>08:43:52</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.13</v>
+        <v>3.39</v>
       </c>
       <c r="F70" t="n">
         <v>8.970000000000001</v>
       </c>
       <c r="G70" t="n">
-        <v>92.8</v>
+        <v>91.5</v>
       </c>
       <c r="H70" t="n">
-        <v>42.7</v>
+        <v>43.2</v>
       </c>
       <c r="I70" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-69.87</v>
+        <v>-65.13</v>
       </c>
       <c r="K70" t="n">
-        <v>151.93</v>
+        <v>161.94</v>
       </c>
       <c r="L70" t="n">
-        <v>167.23</v>
+        <v>174.54</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:59:50</t>
+          <t>08:49:57</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>3.55</v>
+        <v>2.99</v>
       </c>
       <c r="F71" t="n">
-        <v>8.869999999999999</v>
+        <v>7.49</v>
       </c>
       <c r="G71" t="n">
-        <v>85.8</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="H71" t="n">
-        <v>29.5</v>
+        <v>49.8</v>
       </c>
       <c r="I71" t="n">
         <v>27</v>
       </c>
       <c r="J71" t="n">
-        <v>241.96</v>
+        <v>-131.97</v>
       </c>
       <c r="K71" t="n">
-        <v>79.78</v>
+        <v>-92.23999999999999</v>
       </c>
       <c r="L71" t="n">
-        <v>254.77</v>
+        <v>161.01</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:01:03</t>
+          <t>08:52:19</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.45</v>
+        <v>3.12</v>
       </c>
       <c r="F72" t="n">
-        <v>6.19</v>
+        <v>7.11</v>
       </c>
       <c r="G72" t="n">
-        <v>86</v>
+        <v>99.7</v>
       </c>
       <c r="H72" t="n">
-        <v>80.5</v>
+        <v>5.2</v>
       </c>
       <c r="I72" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J72" t="n">
-        <v>230.73</v>
+        <v>198.58</v>
       </c>
       <c r="K72" t="n">
-        <v>-119.93</v>
+        <v>-6.82</v>
       </c>
       <c r="L72" t="n">
-        <v>260.03</v>
+        <v>198.69</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:02:53</t>
+          <t>08:53:57</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.11</v>
+        <v>3.39</v>
       </c>
       <c r="F73" t="n">
         <v>8.970000000000001</v>
       </c>
       <c r="G73" t="n">
-        <v>101.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="H73" t="n">
-        <v>60.2</v>
+        <v>41.2</v>
       </c>
       <c r="I73" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-38.32</v>
+        <v>224.63</v>
       </c>
       <c r="K73" t="n">
-        <v>214.36</v>
+        <v>-77.26000000000001</v>
       </c>
       <c r="L73" t="n">
-        <v>217.75</v>
+        <v>237.54</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:14:29</t>
+          <t>09:03:51</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>3.07</v>
+        <v>2.98</v>
       </c>
       <c r="F74" t="n">
-        <v>3.87</v>
+        <v>6.82</v>
       </c>
       <c r="G74" t="n">
-        <v>95.8</v>
+        <v>94.3</v>
       </c>
       <c r="H74" t="n">
-        <v>36.5</v>
+        <v>49.3</v>
       </c>
       <c r="I74" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J74" t="n">
-        <v>-56.63</v>
+        <v>-54.2</v>
       </c>
       <c r="K74" t="n">
-        <v>-8.81</v>
+        <v>24.49</v>
       </c>
       <c r="L74" t="n">
-        <v>57.31</v>
+        <v>59.48</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:16:14</t>
+          <t>09:05:41</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.28</v>
+        <v>3.33</v>
       </c>
       <c r="F75" t="n">
-        <v>8.970000000000001</v>
+        <v>6.83</v>
       </c>
       <c r="G75" t="n">
-        <v>92.59999999999999</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="H75" t="n">
-        <v>40.8</v>
+        <v>41.8</v>
       </c>
       <c r="I75" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J75" t="n">
-        <v>3.28</v>
+        <v>53.38</v>
       </c>
       <c r="K75" t="n">
-        <v>59.43</v>
+        <v>0.61</v>
       </c>
       <c r="L75" t="n">
-        <v>59.52</v>
+        <v>53.38</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:17:56</t>
+          <t>09:06:35</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.77</v>
+        <v>3.64</v>
       </c>
       <c r="F76" t="n">
-        <v>7.75</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G76" t="n">
-        <v>107.4</v>
+        <v>82.8</v>
       </c>
       <c r="H76" t="n">
-        <v>74.09999999999999</v>
+        <v>40.5</v>
       </c>
       <c r="I76" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>9.529999999999999</v>
+        <v>47.28</v>
       </c>
       <c r="K76" t="n">
-        <v>44.55</v>
+        <v>-51.92</v>
       </c>
       <c r="L76" t="n">
-        <v>45.56</v>
+        <v>70.22</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:23:58</t>
+          <t>09:11:13</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.63</v>
+        <v>4.19</v>
       </c>
       <c r="F77" t="n">
         <v>8.970000000000001</v>
       </c>
       <c r="G77" t="n">
-        <v>106.1</v>
+        <v>93.8</v>
       </c>
       <c r="H77" t="n">
-        <v>54.4</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="J77" t="n">
-        <v>79.13</v>
+        <v>-75.73999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>-47.45</v>
+        <v>-77.17</v>
       </c>
       <c r="L77" t="n">
-        <v>92.27</v>
+        <v>108.12</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:25:07</t>
+          <t>09:13:01</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.01</v>
+        <v>3.19</v>
       </c>
       <c r="F78" t="n">
-        <v>8.970000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="G78" t="n">
-        <v>118.1</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>24.5</v>
+        <v>27</v>
       </c>
       <c r="I78" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>-37.24</v>
+        <v>-42.94</v>
       </c>
       <c r="K78" t="n">
-        <v>40.75</v>
+        <v>37.86</v>
       </c>
       <c r="L78" t="n">
-        <v>55.2</v>
+        <v>57.25</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:27:07</t>
+          <t>09:14:50</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="F79" t="n">
-        <v>7.08</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G79" t="n">
-        <v>92.5</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="H79" t="n">
-        <v>35.3</v>
+        <v>68.2</v>
       </c>
       <c r="I79" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-51.81</v>
+        <v>-88.11</v>
       </c>
       <c r="K79" t="n">
-        <v>-53.97</v>
+        <v>-66.77</v>
       </c>
       <c r="L79" t="n">
-        <v>74.81999999999999</v>
+        <v>110.55</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:30:27</t>
+          <t>09:20:30</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="F80" t="n">
-        <v>8.970000000000001</v>
+        <v>7.61</v>
       </c>
       <c r="G80" t="n">
-        <v>100.9</v>
+        <v>116.7</v>
       </c>
       <c r="H80" t="n">
-        <v>23.4</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J80" t="n">
-        <v>101.86</v>
+        <v>43.99</v>
       </c>
       <c r="K80" t="n">
-        <v>17.1</v>
+        <v>106.11</v>
       </c>
       <c r="L80" t="n">
-        <v>103.29</v>
+        <v>114.87</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:31:46</t>
+          <t>09:22:27</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.83</v>
+        <v>3.16</v>
       </c>
       <c r="F81" t="n">
-        <v>8.82</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G81" t="n">
-        <v>104.5</v>
+        <v>94.8</v>
       </c>
       <c r="H81" t="n">
-        <v>25.9</v>
+        <v>60.5</v>
       </c>
       <c r="I81" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>-71.06</v>
+        <v>60.34</v>
       </c>
       <c r="K81" t="n">
-        <v>-66.91</v>
+        <v>-58.69</v>
       </c>
       <c r="L81" t="n">
-        <v>97.59999999999999</v>
+        <v>84.17</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:33:47</t>
+          <t>09:24:02</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>3.26</v>
+        <v>3.33</v>
       </c>
       <c r="F82" t="n">
         <v>8.970000000000001</v>
       </c>
       <c r="G82" t="n">
-        <v>98.5</v>
+        <v>100.8</v>
       </c>
       <c r="H82" t="n">
-        <v>52.6</v>
+        <v>32.4</v>
       </c>
       <c r="I82" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J82" t="n">
-        <v>-107.76</v>
+        <v>2.84</v>
       </c>
       <c r="K82" t="n">
-        <v>-26.02</v>
+        <v>-118.04</v>
       </c>
       <c r="L82" t="n">
-        <v>110.86</v>
+        <v>118.07</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:39:36</t>
+          <t>09:27:16</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.63</v>
+        <v>3.46</v>
       </c>
       <c r="F83" t="n">
-        <v>8.25</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G83" t="n">
-        <v>88.2</v>
+        <v>94</v>
       </c>
       <c r="H83" t="n">
-        <v>44</v>
+        <v>36.7</v>
       </c>
       <c r="I83" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J83" t="n">
-        <v>-93.62</v>
+        <v>-85.89</v>
       </c>
       <c r="K83" t="n">
-        <v>57.19</v>
+        <v>156.02</v>
       </c>
       <c r="L83" t="n">
-        <v>109.71</v>
+        <v>178.11</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:41:25</t>
+          <t>09:29:51</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>3.3</v>
+        <v>3.06</v>
       </c>
       <c r="F84" t="n">
         <v>8.970000000000001</v>
       </c>
       <c r="G84" t="n">
-        <v>91.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="H84" t="n">
-        <v>56.1</v>
+        <v>62</v>
       </c>
       <c r="I84" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>84.34</v>
+        <v>-75.40000000000001</v>
       </c>
       <c r="K84" t="n">
-        <v>120.53</v>
+        <v>-157.18</v>
       </c>
       <c r="L84" t="n">
-        <v>147.11</v>
+        <v>174.33</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:42:57</t>
+          <t>09:31:55</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>3.45</v>
+        <v>3.31</v>
       </c>
       <c r="F85" t="n">
         <v>8.970000000000001</v>
       </c>
       <c r="G85" t="n">
-        <v>104.8</v>
+        <v>103.4</v>
       </c>
       <c r="H85" t="n">
-        <v>17.6</v>
+        <v>25.7</v>
       </c>
       <c r="I85" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>6.31</v>
+        <v>93.95</v>
       </c>
       <c r="K85" t="n">
-        <v>-224.01</v>
+        <v>-188.54</v>
       </c>
       <c r="L85" t="n">
-        <v>224.1</v>
+        <v>210.65</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:48:26</t>
+          <t>09:37:32</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="F86" t="n">
-        <v>7.48</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G86" t="n">
-        <v>94.3</v>
+        <v>107.2</v>
       </c>
       <c r="H86" t="n">
-        <v>48.4</v>
+        <v>45.7</v>
       </c>
       <c r="I86" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-131.13</v>
+        <v>-57.02</v>
       </c>
       <c r="K86" t="n">
-        <v>-91.86</v>
+        <v>273.44</v>
       </c>
       <c r="L86" t="n">
-        <v>160.11</v>
+        <v>279.32</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:49:41</t>
+          <t>09:39:16</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.34</v>
+        <v>3.31</v>
       </c>
       <c r="F87" t="n">
-        <v>8.970000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="G87" t="n">
-        <v>96.7</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="H87" t="n">
-        <v>32.1</v>
+        <v>37.1</v>
       </c>
       <c r="I87" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J87" t="n">
-        <v>-255.62</v>
+        <v>-151.67</v>
       </c>
       <c r="K87" t="n">
-        <v>83.69</v>
+        <v>206.4</v>
       </c>
       <c r="L87" t="n">
-        <v>268.97</v>
+        <v>256.13</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:50:36</t>
+          <t>09:40:17</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="F88" t="n">
-        <v>8.039999999999999</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="G88" t="n">
-        <v>90.90000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="H88" t="n">
-        <v>57.3</v>
+        <v>52.3</v>
       </c>
       <c r="I88" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J88" t="n">
-        <v>211.03</v>
+        <v>-119.19</v>
       </c>
       <c r="K88" t="n">
-        <v>-101.91</v>
+        <v>172.97</v>
       </c>
       <c r="L88" t="n">
-        <v>234.35</v>
+        <v>210.06</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-08-21.xlsx
+++ b/output/2024-08-21.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>24.15</v>
+        <v>23.36</v>
       </c>
       <c r="K14" t="n">
-        <v>-52.52</v>
+        <v>-50.8</v>
       </c>
       <c r="L14" t="n">
-        <v>57.81</v>
+        <v>55.92</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>50.97</v>
+        <v>45.43</v>
       </c>
       <c r="K15" t="n">
-        <v>77.28</v>
+        <v>68.88</v>
       </c>
       <c r="L15" t="n">
-        <v>92.56999999999999</v>
+        <v>82.51000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>-41.14</v>
+        <v>-41.45</v>
       </c>
       <c r="K16" t="n">
-        <v>18.33</v>
+        <v>18.47</v>
       </c>
       <c r="L16" t="n">
-        <v>45.04</v>
+        <v>45.38</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-5.61</v>
+        <v>-5.96</v>
       </c>
       <c r="K17" t="n">
-        <v>5.71</v>
+        <v>6.07</v>
       </c>
       <c r="L17" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-39.29</v>
+        <v>-44.14</v>
       </c>
       <c r="K18" t="n">
-        <v>30.01</v>
+        <v>33.72</v>
       </c>
       <c r="L18" t="n">
-        <v>49.44</v>
+        <v>55.55</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-56.96</v>
+        <v>-54.25</v>
       </c>
       <c r="K19" t="n">
-        <v>-65.58</v>
+        <v>-62.46</v>
       </c>
       <c r="L19" t="n">
-        <v>86.86</v>
+        <v>82.73</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-94.40000000000001</v>
+        <v>-100.54</v>
       </c>
       <c r="K20" t="n">
-        <v>12.45</v>
+        <v>13.26</v>
       </c>
       <c r="L20" t="n">
-        <v>95.22</v>
+        <v>101.41</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>28</v>
       </c>
       <c r="J21" t="n">
-        <v>-23.28</v>
+        <v>-26.8</v>
       </c>
       <c r="K21" t="n">
-        <v>-56.7</v>
+        <v>-65.27</v>
       </c>
       <c r="L21" t="n">
-        <v>61.29</v>
+        <v>70.56</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>-21.37</v>
+        <v>-21.27</v>
       </c>
       <c r="K22" t="n">
-        <v>122.02</v>
+        <v>121.44</v>
       </c>
       <c r="L22" t="n">
-        <v>123.87</v>
+        <v>123.29</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>66.64</v>
+        <v>71.06</v>
       </c>
       <c r="K23" t="n">
-        <v>96.19</v>
+        <v>102.56</v>
       </c>
       <c r="L23" t="n">
-        <v>117.02</v>
+        <v>124.77</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>-66.90000000000001</v>
+        <v>-72.89</v>
       </c>
       <c r="K24" t="n">
-        <v>99.89</v>
+        <v>108.82</v>
       </c>
       <c r="L24" t="n">
-        <v>120.22</v>
+        <v>130.97</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>55.53</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>83.23</v>
+        <v>100.42</v>
       </c>
       <c r="L25" t="n">
-        <v>100.06</v>
+        <v>120.71</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>139.16</v>
+        <v>161.85</v>
       </c>
       <c r="K26" t="n">
-        <v>62.73</v>
+        <v>72.95</v>
       </c>
       <c r="L26" t="n">
-        <v>152.64</v>
+        <v>177.53</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-180.41</v>
+        <v>-194.92</v>
       </c>
       <c r="K27" t="n">
-        <v>-133.6</v>
+        <v>-144.34</v>
       </c>
       <c r="L27" t="n">
-        <v>224.49</v>
+        <v>242.54</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-123.93</v>
+        <v>-134.72</v>
       </c>
       <c r="K28" t="n">
-        <v>163.39</v>
+        <v>177.62</v>
       </c>
       <c r="L28" t="n">
-        <v>205.08</v>
+        <v>222.93</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-2.63</v>
+        <v>-2.85</v>
       </c>
       <c r="K29" t="n">
-        <v>-11.87</v>
+        <v>-12.88</v>
       </c>
       <c r="L29" t="n">
-        <v>12.16</v>
+        <v>13.19</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>5.23</v>
+        <v>5.73</v>
       </c>
       <c r="K30" t="n">
-        <v>-49.87</v>
+        <v>-54.63</v>
       </c>
       <c r="L30" t="n">
-        <v>50.14</v>
+        <v>54.93</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>14.15</v>
+        <v>13.53</v>
       </c>
       <c r="K31" t="n">
-        <v>66.68000000000001</v>
+        <v>63.74</v>
       </c>
       <c r="L31" t="n">
-        <v>68.17</v>
+        <v>65.16</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>35.7</v>
+        <v>37.86</v>
       </c>
       <c r="K32" t="n">
-        <v>41.22</v>
+        <v>43.71</v>
       </c>
       <c r="L32" t="n">
-        <v>54.53</v>
+        <v>57.83</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>18.64</v>
+        <v>19.28</v>
       </c>
       <c r="K33" t="n">
-        <v>60.99</v>
+        <v>63.08</v>
       </c>
       <c r="L33" t="n">
-        <v>63.77</v>
+        <v>65.95999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>19.19</v>
+        <v>21.67</v>
       </c>
       <c r="K34" t="n">
-        <v>-38.24</v>
+        <v>-43.18</v>
       </c>
       <c r="L34" t="n">
-        <v>42.79</v>
+        <v>48.31</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>77.73999999999999</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>10.82</v>
+        <v>12.21</v>
       </c>
       <c r="L35" t="n">
-        <v>78.48999999999999</v>
+        <v>88.59</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-54.6</v>
+        <v>-54.53</v>
       </c>
       <c r="K36" t="n">
-        <v>113.33</v>
+        <v>113.19</v>
       </c>
       <c r="L36" t="n">
-        <v>125.8</v>
+        <v>125.64</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>19.95</v>
+        <v>19.81</v>
       </c>
       <c r="K37" t="n">
-        <v>130.9</v>
+        <v>129.94</v>
       </c>
       <c r="L37" t="n">
-        <v>132.41</v>
+        <v>131.44</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>-34.07</v>
+        <v>-40.66</v>
       </c>
       <c r="K38" t="n">
-        <v>84.20999999999999</v>
+        <v>100.48</v>
       </c>
       <c r="L38" t="n">
-        <v>90.84</v>
+        <v>108.39</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>69.04000000000001</v>
+        <v>73.16</v>
       </c>
       <c r="K39" t="n">
-        <v>121.21</v>
+        <v>128.45</v>
       </c>
       <c r="L39" t="n">
-        <v>139.5</v>
+        <v>147.82</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>20.82</v>
+        <v>24.8</v>
       </c>
       <c r="K40" t="n">
-        <v>101.65</v>
+        <v>121.08</v>
       </c>
       <c r="L40" t="n">
-        <v>103.76</v>
+        <v>123.59</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.69</v>
+        <v>-10.09</v>
       </c>
       <c r="K41" t="n">
-        <v>156.49</v>
+        <v>181.87</v>
       </c>
       <c r="L41" t="n">
-        <v>156.73</v>
+        <v>182.15</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>-200.9</v>
+        <v>-219.49</v>
       </c>
       <c r="K42" t="n">
-        <v>77.15000000000001</v>
+        <v>84.28</v>
       </c>
       <c r="L42" t="n">
-        <v>215.21</v>
+        <v>235.11</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-26.12</v>
+        <v>-28.79</v>
       </c>
       <c r="K43" t="n">
-        <v>206.43</v>
+        <v>227.49</v>
       </c>
       <c r="L43" t="n">
-        <v>208.08</v>
+        <v>229.31</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>16.77</v>
+        <v>16.15</v>
       </c>
       <c r="K44" t="n">
-        <v>-61.35</v>
+        <v>-59.08</v>
       </c>
       <c r="L44" t="n">
-        <v>63.6</v>
+        <v>61.25</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>8.94</v>
+        <v>8.34</v>
       </c>
       <c r="K45" t="n">
-        <v>77.2</v>
+        <v>72.02</v>
       </c>
       <c r="L45" t="n">
-        <v>77.70999999999999</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>27</v>
       </c>
       <c r="J46" t="n">
-        <v>16.35</v>
+        <v>15.94</v>
       </c>
       <c r="K46" t="n">
-        <v>-58.67</v>
+        <v>-57.18</v>
       </c>
       <c r="L46" t="n">
-        <v>60.91</v>
+        <v>59.36</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-23.14</v>
+        <v>-25.02</v>
       </c>
       <c r="K47" t="n">
-        <v>-46.19</v>
+        <v>-49.95</v>
       </c>
       <c r="L47" t="n">
-        <v>51.66</v>
+        <v>55.87</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>16.15</v>
+        <v>16.01</v>
       </c>
       <c r="K48" t="n">
-        <v>72.81</v>
+        <v>72.19</v>
       </c>
       <c r="L48" t="n">
-        <v>74.58</v>
+        <v>73.94</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>69.40000000000001</v>
+        <v>68.83</v>
       </c>
       <c r="K49" t="n">
-        <v>-37.09</v>
+        <v>-36.79</v>
       </c>
       <c r="L49" t="n">
-        <v>78.69</v>
+        <v>78.05</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>12.25</v>
+        <v>12.18</v>
       </c>
       <c r="K50" t="n">
-        <v>125.84</v>
+        <v>125.11</v>
       </c>
       <c r="L50" t="n">
-        <v>126.43</v>
+        <v>125.7</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-2.44</v>
+        <v>-2.69</v>
       </c>
       <c r="K51" t="n">
-        <v>78.55</v>
+        <v>86.5</v>
       </c>
       <c r="L51" t="n">
-        <v>78.58</v>
+        <v>86.55</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-74.98</v>
+        <v>-84.84</v>
       </c>
       <c r="K52" t="n">
-        <v>-18.48</v>
+        <v>-20.91</v>
       </c>
       <c r="L52" t="n">
-        <v>77.22</v>
+        <v>87.38</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>159.83</v>
+        <v>160.36</v>
       </c>
       <c r="K53" t="n">
-        <v>-75.72</v>
+        <v>-75.97</v>
       </c>
       <c r="L53" t="n">
-        <v>176.86</v>
+        <v>177.45</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-44.33</v>
+        <v>-46.61</v>
       </c>
       <c r="K54" t="n">
-        <v>145.99</v>
+        <v>153.51</v>
       </c>
       <c r="L54" t="n">
-        <v>152.57</v>
+        <v>160.43</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>20.47</v>
+        <v>21.83</v>
       </c>
       <c r="K55" t="n">
-        <v>149.15</v>
+        <v>159.07</v>
       </c>
       <c r="L55" t="n">
-        <v>150.55</v>
+        <v>160.56</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>27</v>
       </c>
       <c r="J56" t="n">
-        <v>131.2</v>
+        <v>155.7</v>
       </c>
       <c r="K56" t="n">
-        <v>11.71</v>
+        <v>13.9</v>
       </c>
       <c r="L56" t="n">
-        <v>131.73</v>
+        <v>156.32</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>154.27</v>
+        <v>186.09</v>
       </c>
       <c r="K57" t="n">
-        <v>30.41</v>
+        <v>36.69</v>
       </c>
       <c r="L57" t="n">
-        <v>157.24</v>
+        <v>189.67</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>224.12</v>
+        <v>233.44</v>
       </c>
       <c r="K58" t="n">
-        <v>-107.38</v>
+        <v>-111.84</v>
       </c>
       <c r="L58" t="n">
-        <v>248.51</v>
+        <v>258.85</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>50.41</v>
+        <v>50.47</v>
       </c>
       <c r="K59" t="n">
-        <v>32.48</v>
+        <v>32.52</v>
       </c>
       <c r="L59" t="n">
-        <v>59.97</v>
+        <v>60.04</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>42.93</v>
+        <v>44.94</v>
       </c>
       <c r="K60" t="n">
-        <v>16.67</v>
+        <v>17.45</v>
       </c>
       <c r="L60" t="n">
-        <v>46.05</v>
+        <v>48.21</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>60.63</v>
+        <v>56.65</v>
       </c>
       <c r="K61" t="n">
-        <v>-34.1</v>
+        <v>-31.87</v>
       </c>
       <c r="L61" t="n">
-        <v>69.56</v>
+        <v>65</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>-89.3</v>
+        <v>-85.55</v>
       </c>
       <c r="K62" t="n">
-        <v>-4.77</v>
+        <v>-4.57</v>
       </c>
       <c r="L62" t="n">
-        <v>89.43000000000001</v>
+        <v>85.67</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>41.33</v>
+        <v>45.9</v>
       </c>
       <c r="K63" t="n">
-        <v>-26.88</v>
+        <v>-29.85</v>
       </c>
       <c r="L63" t="n">
-        <v>49.3</v>
+        <v>54.75</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-11.85</v>
+        <v>-12.95</v>
       </c>
       <c r="K64" t="n">
-        <v>-53.31</v>
+        <v>-58.23</v>
       </c>
       <c r="L64" t="n">
-        <v>54.62</v>
+        <v>59.65</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-49.76</v>
+        <v>-55.03</v>
       </c>
       <c r="K65" t="n">
-        <v>-66.76000000000001</v>
+        <v>-73.83</v>
       </c>
       <c r="L65" t="n">
-        <v>83.27</v>
+        <v>92.08</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>91.23999999999999</v>
+        <v>92.08</v>
       </c>
       <c r="K66" t="n">
-        <v>-64.90000000000001</v>
+        <v>-65.5</v>
       </c>
       <c r="L66" t="n">
-        <v>111.97</v>
+        <v>113</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>27</v>
       </c>
       <c r="J67" t="n">
-        <v>-72.14</v>
+        <v>-77.78</v>
       </c>
       <c r="K67" t="n">
-        <v>27.9</v>
+        <v>30.08</v>
       </c>
       <c r="L67" t="n">
-        <v>77.34999999999999</v>
+        <v>83.39</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>25.07</v>
+        <v>26.7</v>
       </c>
       <c r="K68" t="n">
-        <v>-151.01</v>
+        <v>-160.83</v>
       </c>
       <c r="L68" t="n">
-        <v>153.08</v>
+        <v>163.03</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>58.46</v>
+        <v>67.37</v>
       </c>
       <c r="K69" t="n">
-        <v>82.29000000000001</v>
+        <v>94.83</v>
       </c>
       <c r="L69" t="n">
-        <v>100.94</v>
+        <v>116.32</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-10.4</v>
+        <v>-11.49</v>
       </c>
       <c r="K70" t="n">
-        <v>-106.55</v>
+        <v>-117.69</v>
       </c>
       <c r="L70" t="n">
-        <v>107.06</v>
+        <v>118.25</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>-26.66</v>
+        <v>-28.77</v>
       </c>
       <c r="K71" t="n">
-        <v>-201.6</v>
+        <v>-217.53</v>
       </c>
       <c r="L71" t="n">
-        <v>203.36</v>
+        <v>219.43</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>-152.66</v>
+        <v>-168.95</v>
       </c>
       <c r="K72" t="n">
-        <v>91.25</v>
+        <v>100.99</v>
       </c>
       <c r="L72" t="n">
-        <v>177.85</v>
+        <v>196.84</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-26.66</v>
+        <v>-30.47</v>
       </c>
       <c r="K73" t="n">
-        <v>-275.51</v>
+        <v>-314.9</v>
       </c>
       <c r="L73" t="n">
-        <v>276.8</v>
+        <v>316.37</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>-17.33</v>
+        <v>-16.88</v>
       </c>
       <c r="K74" t="n">
-        <v>66.56</v>
+        <v>64.83</v>
       </c>
       <c r="L74" t="n">
-        <v>68.78</v>
+        <v>66.98999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>48.57</v>
+        <v>45.77</v>
       </c>
       <c r="K75" t="n">
-        <v>-42</v>
+        <v>-39.58</v>
       </c>
       <c r="L75" t="n">
-        <v>64.20999999999999</v>
+        <v>60.51</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>28.28</v>
+        <v>29.07</v>
       </c>
       <c r="K76" t="n">
-        <v>-38.67</v>
+        <v>-39.75</v>
       </c>
       <c r="L76" t="n">
-        <v>47.91</v>
+        <v>49.25</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-59.48</v>
+        <v>-56.28</v>
       </c>
       <c r="K77" t="n">
-        <v>70.79000000000001</v>
+        <v>66.97</v>
       </c>
       <c r="L77" t="n">
-        <v>92.45999999999999</v>
+        <v>87.47</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>49.77</v>
+        <v>52.53</v>
       </c>
       <c r="K78" t="n">
-        <v>30.69</v>
+        <v>32.39</v>
       </c>
       <c r="L78" t="n">
-        <v>58.48</v>
+        <v>61.71</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-53.65</v>
+        <v>-55.39</v>
       </c>
       <c r="K79" t="n">
-        <v>-52.95</v>
+        <v>-54.66</v>
       </c>
       <c r="L79" t="n">
-        <v>75.38</v>
+        <v>77.81999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>-92.48</v>
+        <v>-99</v>
       </c>
       <c r="K80" t="n">
-        <v>-21.91</v>
+        <v>-23.46</v>
       </c>
       <c r="L80" t="n">
-        <v>95.04000000000001</v>
+        <v>101.74</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>79.16</v>
+        <v>83.92</v>
       </c>
       <c r="K81" t="n">
-        <v>49.78</v>
+        <v>52.77</v>
       </c>
       <c r="L81" t="n">
-        <v>93.51000000000001</v>
+        <v>99.13</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>27</v>
       </c>
       <c r="J82" t="n">
-        <v>126.71</v>
+        <v>127.88</v>
       </c>
       <c r="K82" t="n">
-        <v>-11.19</v>
+        <v>-11.29</v>
       </c>
       <c r="L82" t="n">
-        <v>127.21</v>
+        <v>128.38</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>28</v>
       </c>
       <c r="J83" t="n">
-        <v>82.61</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="K83" t="n">
-        <v>56.95</v>
+        <v>67.88</v>
       </c>
       <c r="L83" t="n">
-        <v>100.33</v>
+        <v>119.59</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>24</v>
       </c>
       <c r="J84" t="n">
-        <v>-86.41</v>
+        <v>-98.78</v>
       </c>
       <c r="K84" t="n">
-        <v>-89.37</v>
+        <v>-102.15</v>
       </c>
       <c r="L84" t="n">
-        <v>124.31</v>
+        <v>142.1</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>30.22</v>
+        <v>32.84</v>
       </c>
       <c r="K85" t="n">
-        <v>-148.11</v>
+        <v>-160.91</v>
       </c>
       <c r="L85" t="n">
-        <v>151.16</v>
+        <v>164.23</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>221.26</v>
+        <v>247.54</v>
       </c>
       <c r="K86" t="n">
-        <v>33.32</v>
+        <v>37.28</v>
       </c>
       <c r="L86" t="n">
-        <v>223.75</v>
+        <v>250.33</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>28</v>
       </c>
       <c r="J87" t="n">
-        <v>135.15</v>
+        <v>152.76</v>
       </c>
       <c r="K87" t="n">
-        <v>92.69</v>
+        <v>104.77</v>
       </c>
       <c r="L87" t="n">
-        <v>163.88</v>
+        <v>185.24</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>101.8</v>
+        <v>111.4</v>
       </c>
       <c r="K88" t="n">
-        <v>204.07</v>
+        <v>223.31</v>
       </c>
       <c r="L88" t="n">
-        <v>228.05</v>
+        <v>249.56</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-08-21.xlsx
+++ b/output/2024-08-21.xlsx
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-44.14</v>
+        <v>-46.83</v>
       </c>
       <c r="K18" t="n">
-        <v>33.72</v>
+        <v>35.78</v>
       </c>
       <c r="L18" t="n">
-        <v>55.55</v>
+        <v>58.93</v>
       </c>
     </row>
     <row r="19">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-2.85</v>
+        <v>-2.92</v>
       </c>
       <c r="K29" t="n">
-        <v>-12.88</v>
+        <v>-13.18</v>
       </c>
       <c r="L29" t="n">
-        <v>13.19</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>5.73</v>
+        <v>6.1</v>
       </c>
       <c r="K30" t="n">
-        <v>-54.63</v>
+        <v>-58.15</v>
       </c>
       <c r="L30" t="n">
-        <v>54.93</v>
+        <v>58.47</v>
       </c>
     </row>
     <row r="31">
@@ -1480,13 +1480,13 @@
         <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>21.67</v>
+        <v>21.87</v>
       </c>
       <c r="K34" t="n">
-        <v>-43.18</v>
+        <v>-43.58</v>
       </c>
       <c r="L34" t="n">
-        <v>48.31</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="35">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>16.15</v>
+        <v>16.58</v>
       </c>
       <c r="K44" t="n">
-        <v>-59.08</v>
+        <v>-60.63</v>
       </c>
       <c r="L44" t="n">
-        <v>61.25</v>
+        <v>62.86</v>
       </c>
     </row>
     <row r="45">
@@ -1984,13 +1984,13 @@
         <v>27</v>
       </c>
       <c r="J46" t="n">
-        <v>15.94</v>
+        <v>16.07</v>
       </c>
       <c r="K46" t="n">
-        <v>-57.18</v>
+        <v>-57.67</v>
       </c>
       <c r="L46" t="n">
-        <v>59.36</v>
+        <v>59.86</v>
       </c>
     </row>
     <row r="47">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>68.83</v>
+        <v>70.47</v>
       </c>
       <c r="K49" t="n">
-        <v>-36.79</v>
+        <v>-37.67</v>
       </c>
       <c r="L49" t="n">
-        <v>78.05</v>
+        <v>79.91</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>50.47</v>
+        <v>50.83</v>
       </c>
       <c r="K59" t="n">
-        <v>32.52</v>
+        <v>32.75</v>
       </c>
       <c r="L59" t="n">
-        <v>60.04</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="60">
@@ -2740,13 +2740,13 @@
         <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-12.95</v>
+        <v>-13.62</v>
       </c>
       <c r="K64" t="n">
-        <v>-58.23</v>
+        <v>-61.25</v>
       </c>
       <c r="L64" t="n">
-        <v>59.65</v>
+        <v>62.75</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>-16.88</v>
+        <v>-17.05</v>
       </c>
       <c r="K74" t="n">
-        <v>64.83</v>
+        <v>65.48</v>
       </c>
       <c r="L74" t="n">
-        <v>66.98999999999999</v>
+        <v>67.66</v>
       </c>
     </row>
     <row r="75">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-56.28</v>
+        <v>-58.38</v>
       </c>
       <c r="K77" t="n">
-        <v>66.97</v>
+        <v>69.48</v>
       </c>
       <c r="L77" t="n">
-        <v>87.47</v>
+        <v>90.75</v>
       </c>
     </row>
     <row r="78">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-55.39</v>
+        <v>-58.77</v>
       </c>
       <c r="K79" t="n">
-        <v>-54.66</v>
+        <v>-58</v>
       </c>
       <c r="L79" t="n">
-        <v>77.81999999999999</v>
+        <v>82.56999999999999</v>
       </c>
     </row>
     <row r="80">
